--- a/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE1D175-82AE-4600-A757-773122E0C4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95A34FD-0BA3-41CE-B27D-1316D5F8A52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$134</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1061,9 +1066,6 @@
     <t xml:space="preserve">ARBA - Impuesto inmobiliario partida 025024270-0 </t>
   </si>
   <si>
-    <t>M4rz0</t>
-  </si>
-  <si>
     <t>ABONADO POR PROPIETARIO</t>
   </si>
   <si>
@@ -1299,6 +1301,9 @@
   </si>
   <si>
     <t>Transf 22/07</t>
+  </si>
+  <si>
+    <t>En Jul1o deben subir a 949.849,3</t>
   </si>
 </sst>
 </file>
@@ -2395,6 +2400,12 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2505,6 +2516,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2626,28 +2643,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2670,6 +2666,27 @@
     </xf>
     <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2698,18 +2715,6 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2791,9 +2796,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2831,9 +2836,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2866,9 +2871,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2901,9 +2923,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3078,24 +3117,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="82"/>
       <c r="B1" s="91"/>
       <c r="C1" s="98" t="s">
@@ -3109,7 +3148,7 @@
       <c r="I1" s="80"/>
       <c r="J1" s="81"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="83"/>
       <c r="B2" s="92"/>
       <c r="C2" s="92" t="s">
@@ -3123,7 +3162,7 @@
       <c r="I2" s="93"/>
       <c r="J2" s="79"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="83"/>
       <c r="B3" s="92"/>
       <c r="C3" s="92" t="s">
@@ -3139,7 +3178,7 @@
       <c r="I3" s="93"/>
       <c r="J3" s="79"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="83"/>
       <c r="B4" s="92"/>
       <c r="C4" s="92" t="s">
@@ -3153,11 +3192,11 @@
       <c r="I4" s="93"/>
       <c r="J4" s="79"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="87"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="92" t="s">
@@ -3169,7 +3208,7 @@
       <c r="I5" s="92"/>
       <c r="J5" s="88"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="87"/>
       <c r="B6" s="92"/>
       <c r="C6" s="92" t="s">
@@ -3183,7 +3222,7 @@
       <c r="I6" s="92"/>
       <c r="J6" s="88"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="89"/>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -3195,118 +3234,118 @@
       <c r="I7" s="90"/>
       <c r="J7" s="94"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="328" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="332" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="328"/>
-      <c r="C14" s="328"/>
-      <c r="D14" s="328"/>
-      <c r="E14" s="328"/>
-      <c r="F14" s="328"/>
-      <c r="G14" s="328"/>
-      <c r="H14" s="328"/>
-      <c r="I14" s="328"/>
-      <c r="J14" s="328"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="328"/>
-      <c r="B15" s="328"/>
-      <c r="C15" s="328"/>
-      <c r="D15" s="328"/>
-      <c r="E15" s="328"/>
-      <c r="F15" s="328"/>
-      <c r="G15" s="328"/>
-      <c r="H15" s="328"/>
-      <c r="I15" s="328"/>
-      <c r="J15" s="328"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="328"/>
-      <c r="B16" s="328"/>
-      <c r="C16" s="328"/>
-      <c r="D16" s="328"/>
-      <c r="E16" s="328"/>
-      <c r="F16" s="328"/>
-      <c r="G16" s="328"/>
-      <c r="H16" s="328"/>
-      <c r="I16" s="328"/>
-      <c r="J16" s="328"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="328"/>
-      <c r="B17" s="328"/>
-      <c r="C17" s="328"/>
-      <c r="D17" s="328"/>
-      <c r="E17" s="328"/>
-      <c r="F17" s="328"/>
-      <c r="G17" s="328"/>
-      <c r="H17" s="328"/>
-      <c r="I17" s="328"/>
-      <c r="J17" s="328"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="328"/>
-      <c r="B18" s="328"/>
-      <c r="C18" s="328"/>
-      <c r="D18" s="328"/>
-      <c r="E18" s="328"/>
-      <c r="F18" s="328"/>
-      <c r="G18" s="328"/>
-      <c r="H18" s="328"/>
-      <c r="I18" s="328"/>
-      <c r="J18" s="328"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="332"/>
+      <c r="C14" s="332"/>
+      <c r="D14" s="332"/>
+      <c r="E14" s="332"/>
+      <c r="F14" s="332"/>
+      <c r="G14" s="332"/>
+      <c r="H14" s="332"/>
+      <c r="I14" s="332"/>
+      <c r="J14" s="332"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="332"/>
+      <c r="B15" s="332"/>
+      <c r="C15" s="332"/>
+      <c r="D15" s="332"/>
+      <c r="E15" s="332"/>
+      <c r="F15" s="332"/>
+      <c r="G15" s="332"/>
+      <c r="H15" s="332"/>
+      <c r="I15" s="332"/>
+      <c r="J15" s="332"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="332"/>
+      <c r="B16" s="332"/>
+      <c r="C16" s="332"/>
+      <c r="D16" s="332"/>
+      <c r="E16" s="332"/>
+      <c r="F16" s="332"/>
+      <c r="G16" s="332"/>
+      <c r="H16" s="332"/>
+      <c r="I16" s="332"/>
+      <c r="J16" s="332"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="332"/>
+      <c r="B17" s="332"/>
+      <c r="C17" s="332"/>
+      <c r="D17" s="332"/>
+      <c r="E17" s="332"/>
+      <c r="F17" s="332"/>
+      <c r="G17" s="332"/>
+      <c r="H17" s="332"/>
+      <c r="I17" s="332"/>
+      <c r="J17" s="332"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="332"/>
+      <c r="B18" s="332"/>
+      <c r="C18" s="332"/>
+      <c r="D18" s="332"/>
+      <c r="E18" s="332"/>
+      <c r="F18" s="332"/>
+      <c r="G18" s="332"/>
+      <c r="H18" s="332"/>
+      <c r="I18" s="332"/>
+      <c r="J18" s="332"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="329" t="s">
-        <v>398</v>
-      </c>
-      <c r="B20" s="329"/>
-      <c r="C20" s="329"/>
-      <c r="D20" s="329"/>
-      <c r="E20" s="329"/>
-      <c r="F20" s="329"/>
-      <c r="G20" s="329"/>
-      <c r="H20" s="329"/>
-      <c r="I20" s="329"/>
-      <c r="J20" s="329"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="329"/>
-      <c r="B21" s="329"/>
-      <c r="C21" s="329"/>
-      <c r="D21" s="329"/>
-      <c r="E21" s="329"/>
-      <c r="F21" s="329"/>
-      <c r="G21" s="329"/>
-      <c r="H21" s="329"/>
-      <c r="I21" s="329"/>
-      <c r="J21" s="329"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="329"/>
-      <c r="B22" s="329"/>
-      <c r="C22" s="329"/>
-      <c r="D22" s="329"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="329"/>
-      <c r="G22" s="329"/>
-      <c r="H22" s="329"/>
-      <c r="I22" s="329"/>
-      <c r="J22" s="329"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="333" t="s">
+        <v>397</v>
+      </c>
+      <c r="B20" s="333"/>
+      <c r="C20" s="333"/>
+      <c r="D20" s="333"/>
+      <c r="E20" s="333"/>
+      <c r="F20" s="333"/>
+      <c r="G20" s="333"/>
+      <c r="H20" s="333"/>
+      <c r="I20" s="333"/>
+      <c r="J20" s="333"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="333"/>
+      <c r="B21" s="333"/>
+      <c r="C21" s="333"/>
+      <c r="D21" s="333"/>
+      <c r="E21" s="333"/>
+      <c r="F21" s="333"/>
+      <c r="G21" s="333"/>
+      <c r="H21" s="333"/>
+      <c r="I21" s="333"/>
+      <c r="J21" s="333"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="333"/>
+      <c r="B22" s="333"/>
+      <c r="C22" s="333"/>
+      <c r="D22" s="333"/>
+      <c r="E22" s="333"/>
+      <c r="F22" s="333"/>
+      <c r="G22" s="333"/>
+      <c r="H22" s="333"/>
+      <c r="I22" s="333"/>
+      <c r="J22" s="333"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="200" t="s">
         <v>18</v>
       </c>
@@ -3332,7 +3371,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="205" t="s">
         <v>339</v>
       </c>
@@ -3347,13 +3386,13 @@
       <c r="J25" s="44"/>
       <c r="L25" s="50"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="207" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B26" s="175"/>
       <c r="C26" s="175" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D26" s="173">
         <v>250000</v>
@@ -3366,15 +3405,15 @@
       <c r="J26" s="44"/>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="207" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B27" s="175" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C27" s="175" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D27" s="173">
         <v>3000000</v>
@@ -3387,7 +3426,7 @@
       <c r="J27" s="3"/>
       <c r="L27" s="50"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="208" t="s">
         <v>35</v>
       </c>
@@ -3430,7 +3469,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="207" t="s">
         <v>234</v>
       </c>
@@ -3445,7 +3484,7 @@
       <c r="J29" s="44"/>
       <c r="L29" s="50"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="207"/>
       <c r="B30" s="175"/>
       <c r="C30" s="175"/>
@@ -3458,7 +3497,7 @@
       <c r="J30" s="44"/>
       <c r="L30" s="50"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="208" t="s">
         <v>16</v>
       </c>
@@ -3486,7 +3525,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="207" t="s">
         <v>230</v>
       </c>
@@ -3501,13 +3540,13 @@
       <c r="J32" s="38"/>
       <c r="L32" s="50"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="136" t="s">
         <v>340</v>
       </c>
       <c r="B33" s="136"/>
       <c r="C33" s="211"/>
-      <c r="D33" s="400">
+      <c r="D33" s="297">
         <v>36320.199999999997</v>
       </c>
       <c r="E33" s="210"/>
@@ -3518,15 +3557,15 @@
       <c r="J33" s="38"/>
       <c r="L33" s="50"/>
     </row>
-    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="136" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B34" s="136" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C34" s="253" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D34" s="173">
         <v>0</v>
@@ -3539,15 +3578,15 @@
       <c r="J34" s="38"/>
       <c r="L34" s="50"/>
     </row>
-    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="136" t="s">
         <v>233</v>
       </c>
       <c r="B35" s="136" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C35" s="253" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D35" s="173">
         <v>0</v>
@@ -3560,7 +3599,7 @@
       <c r="J35" s="38"/>
       <c r="L35" s="50"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="136"/>
       <c r="B36" s="136"/>
       <c r="C36" s="136"/>
@@ -3573,7 +3612,7 @@
       <c r="J36" s="38"/>
       <c r="L36" s="50"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="208" t="s">
         <v>232</v>
       </c>
@@ -3616,7 +3655,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="207" t="s">
         <v>1</v>
       </c>
@@ -3631,7 +3670,7 @@
       <c r="J38" s="3"/>
       <c r="L38" s="50"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="175"/>
       <c r="B39" s="175"/>
       <c r="C39" s="175"/>
@@ -3644,7 +3683,7 @@
       <c r="J39" s="3"/>
       <c r="L39" s="50"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="175"/>
       <c r="B40" s="175"/>
       <c r="C40" s="175"/>
@@ -3657,7 +3696,7 @@
       <c r="J40" s="3"/>
       <c r="L40" s="50"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="175"/>
       <c r="B41" s="175"/>
       <c r="C41" s="214"/>
@@ -3670,7 +3709,7 @@
       <c r="J41" s="3"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="208" t="s">
         <v>231</v>
       </c>
@@ -3713,7 +3752,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="207" t="s">
         <v>222</v>
       </c>
@@ -3728,7 +3767,7 @@
       <c r="J43" s="25"/>
       <c r="L43" s="50"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="175" t="s">
         <v>226</v>
       </c>
@@ -3769,9 +3808,9 @@
       </c>
       <c r="L44" s="50"/>
     </row>
-    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="306"/>
-      <c r="B45" s="307"/>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="310"/>
+      <c r="B45" s="311"/>
       <c r="C45" s="175"/>
       <c r="D45" s="33"/>
       <c r="E45" s="206"/>
@@ -3783,7 +3822,7 @@
       <c r="K45" s="32"/>
       <c r="L45" s="50"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="208" t="s">
         <v>2</v>
       </c>
@@ -3826,7 +3865,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="207" t="s">
         <v>3</v>
       </c>
@@ -3841,15 +3880,15 @@
       <c r="J47" s="3"/>
       <c r="L47" s="50"/>
     </row>
-    <row r="48" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="218" t="s">
         <v>227</v>
       </c>
       <c r="B48" s="175"/>
       <c r="C48" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D48" s="397">
+        <v>410</v>
+      </c>
+      <c r="D48" s="296">
         <v>204572.35</v>
       </c>
       <c r="E48" s="219">
@@ -3887,13 +3926,13 @@
       <c r="M48" s="64"/>
       <c r="N48" s="64"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="175" t="s">
         <v>228</v>
       </c>
       <c r="B49" s="175"/>
       <c r="C49" s="214"/>
-      <c r="D49" s="397">
+      <c r="D49" s="296">
         <v>9643953.0899999999</v>
       </c>
       <c r="E49" s="219">
@@ -3931,13 +3970,13 @@
       <c r="M49" s="64"/>
       <c r="N49" s="64"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="175" t="s">
         <v>229</v>
       </c>
       <c r="B50" s="175"/>
       <c r="C50" s="175" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D50" s="33">
         <v>158988.79999999999</v>
@@ -3968,15 +4007,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="175" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B51" s="175"/>
       <c r="C51" s="175" t="s">
-        <v>411</v>
-      </c>
-      <c r="D51" s="395">
+        <v>410</v>
+      </c>
+      <c r="D51" s="294">
         <v>234537.5</v>
       </c>
       <c r="E51" s="219"/>
@@ -3990,15 +4029,15 @@
       <c r="M51" s="64"/>
       <c r="N51" s="64"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="218" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B52" s="175"/>
       <c r="C52" s="253" t="s">
-        <v>378</v>
-      </c>
-      <c r="D52" s="395">
+        <v>377</v>
+      </c>
+      <c r="D52" s="294">
         <v>513636.37</v>
       </c>
       <c r="E52" s="219">
@@ -4021,15 +4060,15 @@
       <c r="M52" s="64"/>
       <c r="N52" s="64"/>
     </row>
-    <row r="53" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="294" t="s">
-        <v>403</v>
-      </c>
-      <c r="B53" s="330"/>
+    <row r="53" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="298" t="s">
+        <v>402</v>
+      </c>
+      <c r="B53" s="334"/>
       <c r="C53" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D53" s="395">
+        <v>410</v>
+      </c>
+      <c r="D53" s="294">
         <v>55000</v>
       </c>
       <c r="E53" s="219">
@@ -4058,15 +4097,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="136" t="s">
         <v>259</v>
       </c>
       <c r="B54" s="243"/>
       <c r="C54" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D54" s="395">
+        <v>410</v>
+      </c>
+      <c r="D54" s="294">
         <v>6757.82</v>
       </c>
       <c r="E54" s="219">
@@ -4086,15 +4125,15 @@
       <c r="M54" s="64"/>
       <c r="N54" s="64"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="136" t="s">
         <v>259</v>
       </c>
       <c r="B55" s="136"/>
       <c r="C55" s="214" t="s">
-        <v>409</v>
-      </c>
-      <c r="D55" s="395">
+        <v>408</v>
+      </c>
+      <c r="D55" s="294">
         <v>29933.48</v>
       </c>
       <c r="E55" s="219">
@@ -4123,15 +4162,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="136" t="s">
         <v>260</v>
       </c>
       <c r="B56" s="136"/>
       <c r="C56" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D56" s="395">
+        <v>410</v>
+      </c>
+      <c r="D56" s="294">
         <v>1195477.76</v>
       </c>
       <c r="E56" s="219">
@@ -4175,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="220" t="s">
         <v>258</v>
       </c>
@@ -4210,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="208" t="s">
         <v>4</v>
       </c>
@@ -4257,7 +4296,7 @@
         <v>234537.49999999814</v>
       </c>
     </row>
-    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="175"/>
       <c r="B59" s="175"/>
       <c r="C59" s="175"/>
@@ -4270,7 +4309,7 @@
       <c r="J59" s="3"/>
       <c r="L59" s="50"/>
     </row>
-    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="175"/>
       <c r="B60" s="175"/>
       <c r="C60" s="175"/>
@@ -4283,7 +4322,7 @@
       <c r="J60" s="3"/>
       <c r="L60" s="50"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="207" t="s">
         <v>223</v>
       </c>
@@ -4298,13 +4337,13 @@
       <c r="J61" s="3"/>
       <c r="L61" s="50"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="212" t="s">
         <v>338</v>
       </c>
       <c r="B62" s="222"/>
       <c r="C62" s="136" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D62" s="33">
         <v>200000</v>
@@ -4327,15 +4366,15 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="398" t="s">
+    <row r="63" spans="1:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="335" t="s">
+        <v>414</v>
+      </c>
+      <c r="B63" s="336"/>
+      <c r="C63" s="136" t="s">
         <v>415</v>
       </c>
-      <c r="B63" s="399"/>
-      <c r="C63" s="136" t="s">
-        <v>416</v>
-      </c>
-      <c r="D63" s="395">
+      <c r="D63" s="294">
         <v>175700</v>
       </c>
       <c r="E63" s="219"/>
@@ -4347,15 +4386,15 @@
       <c r="K63" s="32"/>
       <c r="L63" s="54"/>
     </row>
-    <row r="64" spans="1:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="398" t="s">
-        <v>417</v>
-      </c>
-      <c r="B64" s="399"/>
+    <row r="64" spans="1:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="335" t="s">
+        <v>416</v>
+      </c>
+      <c r="B64" s="336"/>
       <c r="C64" s="136" t="s">
-        <v>416</v>
-      </c>
-      <c r="D64" s="395">
+        <v>415</v>
+      </c>
+      <c r="D64" s="294">
         <v>206000</v>
       </c>
       <c r="E64" s="219"/>
@@ -4367,15 +4406,15 @@
       <c r="K64" s="32"/>
       <c r="L64" s="54"/>
     </row>
-    <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="294" t="s">
+    <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="298" t="s">
+        <v>412</v>
+      </c>
+      <c r="B65" s="334"/>
+      <c r="C65" s="33" t="s">
         <v>413</v>
       </c>
-      <c r="B65" s="330"/>
-      <c r="C65" s="33" t="s">
-        <v>414</v>
-      </c>
-      <c r="D65" s="395">
+      <c r="D65" s="294">
         <v>150000</v>
       </c>
       <c r="E65" s="219">
@@ -4390,15 +4429,15 @@
       <c r="K65" s="32"/>
       <c r="L65" s="54"/>
     </row>
-    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="396" t="s">
-        <v>418</v>
+    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="295" t="s">
+        <v>417</v>
       </c>
       <c r="B66" s="243"/>
       <c r="C66" s="33" t="s">
-        <v>419</v>
-      </c>
-      <c r="D66" s="395">
+        <v>418</v>
+      </c>
+      <c r="D66" s="294">
         <v>150000</v>
       </c>
       <c r="E66" s="219"/>
@@ -4410,13 +4449,13 @@
       <c r="K66" s="32"/>
       <c r="L66" s="54"/>
     </row>
-    <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="285" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B67" s="243"/>
       <c r="C67" s="33"/>
-      <c r="D67" s="395">
+      <c r="D67" s="294">
         <v>242000</v>
       </c>
       <c r="E67" s="219"/>
@@ -4428,15 +4467,15 @@
       <c r="K67" s="32"/>
       <c r="L67" s="54"/>
     </row>
-    <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="396" t="s">
-        <v>412</v>
+    <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="295" t="s">
+        <v>411</v>
       </c>
       <c r="B68" s="243"/>
       <c r="C68" s="33" t="s">
-        <v>411</v>
-      </c>
-      <c r="D68" s="395">
+        <v>410</v>
+      </c>
+      <c r="D68" s="294">
         <v>120000</v>
       </c>
       <c r="E68" s="219"/>
@@ -4448,15 +4487,15 @@
       <c r="K68" s="32"/>
       <c r="L68" s="54"/>
     </row>
-    <row r="69" spans="1:14" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="306" t="s">
+    <row r="69" spans="1:14" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="310" t="s">
+        <v>405</v>
+      </c>
+      <c r="B69" s="311"/>
+      <c r="C69" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="B69" s="307"/>
-      <c r="C69" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D69" s="395">
+      <c r="D69" s="294">
         <v>190000</v>
       </c>
       <c r="E69" s="219">
@@ -4492,15 +4531,15 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="251" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B70" s="252"/>
       <c r="C70" s="33" t="s">
-        <v>420</v>
-      </c>
-      <c r="D70" s="395">
+        <v>419</v>
+      </c>
+      <c r="D70" s="294">
         <v>396093.5</v>
       </c>
       <c r="E70" s="219">
@@ -4530,7 +4569,7 @@
       <c r="K70" s="32"/>
       <c r="L70" s="54"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="208" t="s">
         <v>224</v>
       </c>
@@ -4574,7 +4613,7 @@
       </c>
       <c r="N71" s="32"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="207" t="s">
         <v>5</v>
       </c>
@@ -4589,15 +4628,15 @@
       <c r="J72" s="3"/>
       <c r="L72" s="50"/>
     </row>
-    <row r="73" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="223" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="175" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C73" s="175" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D73" s="33">
         <v>860560</v>
@@ -4626,11 +4665,12 @@
         <f>D73*1.74%</f>
         <v>14973.743999999999</v>
       </c>
+      <c r="K73" s="12"/>
       <c r="L73" s="50" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="207"/>
       <c r="B74" s="175"/>
       <c r="C74" s="175"/>
@@ -4662,7 +4702,7 @@
       <c r="L74" s="50"/>
       <c r="N74" s="33"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="175"/>
       <c r="B75" s="175"/>
       <c r="C75" s="175"/>
@@ -4676,7 +4716,7 @@
       <c r="L75" s="50"/>
       <c r="N75" s="32"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="208" t="s">
         <v>7</v>
       </c>
@@ -4720,7 +4760,7 @@
       </c>
       <c r="N76" s="32"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="175" t="s">
         <v>26</v>
       </c>
@@ -4756,7 +4796,7 @@
       </c>
       <c r="L77" s="50"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="175" t="s">
         <v>27</v>
       </c>
@@ -4791,7 +4831,7 @@
       </c>
       <c r="L78" s="50"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="208" t="s">
         <v>225</v>
       </c>
@@ -4834,7 +4874,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="73"/>
       <c r="B80" s="73"/>
       <c r="C80" s="73"/>
@@ -4847,7 +4887,7 @@
       <c r="J80" s="72"/>
       <c r="L80" s="50"/>
     </row>
-    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="227" t="s">
         <v>292</v>
       </c>
@@ -4889,7 +4929,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="230"/>
       <c r="B82" s="231"/>
       <c r="C82" s="231"/>
@@ -4903,7 +4943,7 @@
       <c r="K82" s="32"/>
       <c r="L82" s="50"/>
     </row>
-    <row r="83" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="232" t="s">
         <v>28</v>
       </c>
@@ -4950,7 +4990,7 @@
         <v>1128237.5000000037</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="65"/>
       <c r="B84" s="65"/>
       <c r="C84" s="65"/>
@@ -4961,7 +5001,7 @@
       <c r="H84" s="32"/>
       <c r="I84" s="32"/>
     </row>
-    <row r="85" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="236" t="s">
         <v>36</v>
       </c>
@@ -4974,9 +5014,9 @@
       <c r="H85" s="32"/>
       <c r="I85" s="32"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="238" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B86" s="65"/>
       <c r="C86" s="255">
@@ -4989,9 +5029,9 @@
       <c r="H86" s="32"/>
       <c r="I86" s="32"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="238" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B87" s="65"/>
       <c r="C87" s="255">
@@ -5004,9 +5044,9 @@
       <c r="H87" s="32"/>
       <c r="I87" s="32"/>
     </row>
-    <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="238" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B88" s="65"/>
       <c r="C88" s="255">
@@ -5019,9 +5059,9 @@
       <c r="H88" s="32"/>
       <c r="I88" s="32"/>
     </row>
-    <row r="89" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="238" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B89" s="65"/>
       <c r="C89" s="255">
@@ -5034,7 +5074,7 @@
       <c r="H89" s="32"/>
       <c r="I89" s="32"/>
     </row>
-    <row r="90" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="239" t="s">
         <v>16</v>
       </c>
@@ -5050,7 +5090,7 @@
       <c r="H90" s="32"/>
       <c r="I90" s="32"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="65"/>
       <c r="B91" s="65"/>
       <c r="C91" s="65"/>
@@ -5061,7 +5101,7 @@
       <c r="H91" s="32"/>
       <c r="I91" s="32"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="65"/>
       <c r="B92" s="65"/>
       <c r="C92" s="65"/>
@@ -5072,13 +5112,13 @@
       <c r="H92" s="46"/>
       <c r="I92" s="46"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="315" t="s">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="319" t="s">
         <v>32</v>
       </c>
-      <c r="B93" s="316"/>
-      <c r="C93" s="316"/>
-      <c r="D93" s="316"/>
+      <c r="B93" s="320"/>
+      <c r="C93" s="320"/>
+      <c r="D93" s="320"/>
       <c r="E93" s="60" t="s">
         <v>10</v>
       </c>
@@ -5098,9 +5138,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="294"/>
-      <c r="B94" s="295"/>
+    <row r="94" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="298"/>
+      <c r="B94" s="299"/>
       <c r="C94" s="243"/>
       <c r="D94" s="33"/>
       <c r="E94" s="219">
@@ -5113,9 +5153,9 @@
       <c r="I94" s="49"/>
       <c r="J94" s="44"/>
     </row>
-    <row r="95" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="317"/>
-      <c r="B95" s="318"/>
+    <row r="95" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="321"/>
+      <c r="B95" s="322"/>
       <c r="C95" s="62"/>
       <c r="D95" s="33"/>
       <c r="E95" s="49"/>
@@ -5125,12 +5165,12 @@
       <c r="I95" s="49"/>
       <c r="J95" s="44"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A96" s="312" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="316" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="313"/>
-      <c r="C96" s="314"/>
+      <c r="B96" s="317"/>
+      <c r="C96" s="318"/>
       <c r="D96" s="59">
         <f>SUM(D94:D95)</f>
         <v>0</v>
@@ -5156,14 +5196,14 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E98" s="32"/>
       <c r="F98" s="32"/>
       <c r="G98" s="32"/>
       <c r="H98" s="32"/>
       <c r="I98" s="32"/>
     </row>
-    <row r="99" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="27" t="s">
         <v>29</v>
       </c>
@@ -5172,7 +5212,7 @@
         <v>23539011.560000002</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="29" t="s">
         <v>31</v>
       </c>
@@ -5180,45 +5220,45 @@
         <f>D83-D81</f>
         <v>18539011.560000002</v>
       </c>
-      <c r="D100" s="296" t="s">
+      <c r="D100" s="300" t="s">
         <v>284</v>
       </c>
-      <c r="E100" s="296"/>
-      <c r="F100" s="296"/>
-      <c r="G100" s="296"/>
-      <c r="H100" s="296"/>
-      <c r="I100" s="296"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D101" s="296"/>
-      <c r="E101" s="296"/>
-      <c r="F101" s="296"/>
-      <c r="G101" s="296"/>
-      <c r="H101" s="296"/>
-      <c r="I101" s="296"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D102" s="296"/>
-      <c r="E102" s="296"/>
-      <c r="F102" s="296"/>
-      <c r="G102" s="296"/>
-      <c r="H102" s="296"/>
-      <c r="I102" s="296"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E100" s="300"/>
+      <c r="F100" s="300"/>
+      <c r="G100" s="300"/>
+      <c r="H100" s="300"/>
+      <c r="I100" s="300"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D101" s="300"/>
+      <c r="E101" s="300"/>
+      <c r="F101" s="300"/>
+      <c r="G101" s="300"/>
+      <c r="H101" s="300"/>
+      <c r="I101" s="300"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D102" s="300"/>
+      <c r="E102" s="300"/>
+      <c r="F102" s="300"/>
+      <c r="G102" s="300"/>
+      <c r="H102" s="300"/>
+      <c r="I102" s="300"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B103" s="9"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="296"/>
-      <c r="E103" s="296"/>
-      <c r="F103" s="296"/>
-      <c r="G103" s="296"/>
-      <c r="H103" s="296"/>
-      <c r="I103" s="296"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D103" s="300"/>
+      <c r="E103" s="300"/>
+      <c r="F103" s="300"/>
+      <c r="G103" s="300"/>
+      <c r="H103" s="300"/>
+      <c r="I103" s="300"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>20</v>
       </c>
@@ -5226,14 +5266,14 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C104" s="12"/>
-      <c r="D104" s="296"/>
-      <c r="E104" s="296"/>
-      <c r="F104" s="296"/>
-      <c r="G104" s="296"/>
-      <c r="H104" s="296"/>
-      <c r="I104" s="296"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D104" s="300"/>
+      <c r="E104" s="300"/>
+      <c r="F104" s="300"/>
+      <c r="G104" s="300"/>
+      <c r="H104" s="300"/>
+      <c r="I104" s="300"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
         <v>21</v>
       </c>
@@ -5244,30 +5284,30 @@
       <c r="C105" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D105" s="296"/>
-      <c r="E105" s="296"/>
-      <c r="F105" s="296"/>
-      <c r="G105" s="296"/>
-      <c r="H105" s="296"/>
-      <c r="I105" s="296"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D105" s="300"/>
+      <c r="E105" s="300"/>
+      <c r="F105" s="300"/>
+      <c r="G105" s="300"/>
+      <c r="H105" s="300"/>
+      <c r="I105" s="300"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B106" s="22">
         <f>ARBA!L82</f>
         <v>912822.36</v>
       </c>
       <c r="C106" s="12"/>
-      <c r="D106" s="296"/>
-      <c r="E106" s="296"/>
-      <c r="F106" s="296"/>
-      <c r="G106" s="296"/>
-      <c r="H106" s="296"/>
-      <c r="I106" s="296"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D106" s="300"/>
+      <c r="E106" s="300"/>
+      <c r="F106" s="300"/>
+      <c r="G106" s="300"/>
+      <c r="H106" s="300"/>
+      <c r="I106" s="300"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>34</v>
       </c>
@@ -5276,15 +5316,15 @@
         <v>-18539011.560000002</v>
       </c>
       <c r="C107" s="10"/>
-      <c r="D107" s="296"/>
-      <c r="E107" s="296"/>
-      <c r="F107" s="296"/>
-      <c r="G107" s="296"/>
-      <c r="H107" s="296"/>
-      <c r="I107" s="296"/>
+      <c r="D107" s="300"/>
+      <c r="E107" s="300"/>
+      <c r="F107" s="300"/>
+      <c r="G107" s="300"/>
+      <c r="H107" s="300"/>
+      <c r="I107" s="300"/>
       <c r="K107" s="33"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>33</v>
       </c>
@@ -5293,15 +5333,15 @@
         <v>0</v>
       </c>
       <c r="C108" s="10"/>
-      <c r="D108" s="296"/>
-      <c r="E108" s="296"/>
-      <c r="F108" s="296"/>
-      <c r="G108" s="296"/>
-      <c r="H108" s="296"/>
-      <c r="I108" s="296"/>
+      <c r="D108" s="300"/>
+      <c r="E108" s="300"/>
+      <c r="F108" s="300"/>
+      <c r="G108" s="300"/>
+      <c r="H108" s="300"/>
+      <c r="I108" s="300"/>
       <c r="K108" s="39"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>274</v>
       </c>
@@ -5310,31 +5350,31 @@
         <v>94985.93</v>
       </c>
       <c r="C109" s="10"/>
-      <c r="D109" s="296"/>
-      <c r="E109" s="296"/>
-      <c r="F109" s="296"/>
-      <c r="G109" s="296"/>
-      <c r="H109" s="296"/>
-      <c r="I109" s="296"/>
+      <c r="D109" s="300"/>
+      <c r="E109" s="300"/>
+      <c r="F109" s="300"/>
+      <c r="G109" s="300"/>
+      <c r="H109" s="300"/>
+      <c r="I109" s="300"/>
       <c r="K109" s="39"/>
     </row>
-    <row r="110" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="188" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B110" s="22">
         <v>46200</v>
       </c>
       <c r="C110" s="10"/>
-      <c r="D110" s="296"/>
-      <c r="E110" s="296"/>
-      <c r="F110" s="296"/>
-      <c r="G110" s="296"/>
-      <c r="H110" s="296"/>
-      <c r="I110" s="296"/>
+      <c r="D110" s="300"/>
+      <c r="E110" s="300"/>
+      <c r="F110" s="300"/>
+      <c r="G110" s="300"/>
+      <c r="H110" s="300"/>
+      <c r="I110" s="300"/>
       <c r="K110" s="39"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
         <v>30</v>
       </c>
@@ -5343,14 +5383,14 @@
         <v>-100000</v>
       </c>
       <c r="C111" s="14"/>
-      <c r="D111" s="296"/>
-      <c r="E111" s="296"/>
-      <c r="F111" s="296"/>
-      <c r="G111" s="296"/>
-      <c r="H111" s="296"/>
-      <c r="I111" s="296"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D111" s="300"/>
+      <c r="E111" s="300"/>
+      <c r="F111" s="300"/>
+      <c r="G111" s="300"/>
+      <c r="H111" s="300"/>
+      <c r="I111" s="300"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>36</v>
       </c>
@@ -5359,14 +5399,14 @@
         <v>-384244</v>
       </c>
       <c r="C112" s="14"/>
-      <c r="D112" s="296"/>
-      <c r="E112" s="296"/>
-      <c r="F112" s="296"/>
-      <c r="G112" s="296"/>
-      <c r="H112" s="296"/>
-      <c r="I112" s="296"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D112" s="300"/>
+      <c r="E112" s="300"/>
+      <c r="F112" s="300"/>
+      <c r="G112" s="300"/>
+      <c r="H112" s="300"/>
+      <c r="I112" s="300"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>23</v>
       </c>
@@ -5375,39 +5415,39 @@
         <v>-961359.12963389955</v>
       </c>
       <c r="C113" s="51"/>
-      <c r="D113" s="296"/>
-      <c r="E113" s="296"/>
-      <c r="F113" s="296"/>
-      <c r="G113" s="296"/>
-      <c r="H113" s="296"/>
-      <c r="I113" s="296"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D113" s="300"/>
+      <c r="E113" s="300"/>
+      <c r="F113" s="300"/>
+      <c r="G113" s="300"/>
+      <c r="H113" s="300"/>
+      <c r="I113" s="300"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
       <c r="C114" s="10"/>
-      <c r="D114" s="296"/>
-      <c r="E114" s="296"/>
-      <c r="F114" s="296"/>
-      <c r="G114" s="296"/>
-      <c r="H114" s="296"/>
-      <c r="I114" s="296"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D114" s="300"/>
+      <c r="E114" s="300"/>
+      <c r="F114" s="300"/>
+      <c r="G114" s="300"/>
+      <c r="H114" s="300"/>
+      <c r="I114" s="300"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>273</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="10"/>
-      <c r="D115" s="296"/>
-      <c r="E115" s="296"/>
-      <c r="F115" s="296"/>
-      <c r="G115" s="296"/>
-      <c r="H115" s="296"/>
-      <c r="I115" s="296"/>
-    </row>
-    <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D115" s="300"/>
+      <c r="E115" s="300"/>
+      <c r="F115" s="300"/>
+      <c r="G115" s="300"/>
+      <c r="H115" s="300"/>
+      <c r="I115" s="300"/>
+    </row>
+    <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="196" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B116" s="22">
         <v>94985.93</v>
@@ -5416,7 +5456,7 @@
       <c r="D116" s="17"/>
       <c r="E116" s="17"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="25" t="s">
         <v>16</v>
       </c>
@@ -5427,17 +5467,17 @@
       <c r="C117" s="10"/>
       <c r="E117" s="17"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
       <c r="C118" s="10"/>
       <c r="D118" s="17"/>
     </row>
-    <row r="119" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14"/>
       <c r="C119" s="10"/>
       <c r="D119" s="17"/>
     </row>
-    <row r="120" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>19</v>
       </c>
@@ -5445,47 +5485,47 @@
         <v>106182.28</v>
       </c>
       <c r="C120" s="10"/>
-      <c r="D120" s="319" t="s">
-        <v>389</v>
-      </c>
-      <c r="E120" s="320"/>
-      <c r="F120" s="320"/>
-      <c r="G120" s="320"/>
-      <c r="H120" s="320"/>
-      <c r="I120" s="321"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D120" s="323" t="s">
+        <v>388</v>
+      </c>
+      <c r="E120" s="324"/>
+      <c r="F120" s="324"/>
+      <c r="G120" s="324"/>
+      <c r="H120" s="324"/>
+      <c r="I120" s="325"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B121" s="23">
         <v>-60000</v>
       </c>
       <c r="C121" s="10"/>
-      <c r="D121" s="322"/>
-      <c r="E121" s="323"/>
-      <c r="F121" s="323"/>
-      <c r="G121" s="323"/>
-      <c r="H121" s="323"/>
-      <c r="I121" s="324"/>
-    </row>
-    <row r="122" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D121" s="326"/>
+      <c r="E121" s="327"/>
+      <c r="F121" s="327"/>
+      <c r="G121" s="327"/>
+      <c r="H121" s="327"/>
+      <c r="I121" s="328"/>
+    </row>
+    <row r="122" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="199" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B122" s="23">
         <f>-24000*3</f>
         <v>-72000</v>
       </c>
       <c r="C122" s="10"/>
-      <c r="D122" s="322"/>
-      <c r="E122" s="323"/>
-      <c r="F122" s="323"/>
-      <c r="G122" s="323"/>
-      <c r="H122" s="323"/>
-      <c r="I122" s="324"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D122" s="326"/>
+      <c r="E122" s="327"/>
+      <c r="F122" s="327"/>
+      <c r="G122" s="327"/>
+      <c r="H122" s="327"/>
+      <c r="I122" s="328"/>
+    </row>
+    <row r="123" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="25" t="s">
         <v>16</v>
       </c>
@@ -5494,49 +5534,49 @@
         <v>-25817.72</v>
       </c>
       <c r="C123" s="10"/>
-      <c r="D123" s="325"/>
-      <c r="E123" s="326"/>
-      <c r="F123" s="326"/>
-      <c r="G123" s="326"/>
-      <c r="H123" s="326"/>
-      <c r="I123" s="327"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D123" s="329"/>
+      <c r="E123" s="330"/>
+      <c r="F123" s="330"/>
+      <c r="G123" s="330"/>
+      <c r="H123" s="330"/>
+      <c r="I123" s="331"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="14"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="14"/>
       <c r="F125" s="53"/>
       <c r="G125" s="53"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="14"/>
       <c r="F126" s="53"/>
       <c r="G126" s="53"/>
     </row>
-    <row r="127" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H127" s="64"/>
       <c r="I127" s="64"/>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B128" s="5">
         <v>498840</v>
       </c>
       <c r="C128" s="16"/>
-      <c r="D128" s="297" t="s">
-        <v>405</v>
-      </c>
-      <c r="E128" s="298"/>
-      <c r="F128" s="298"/>
-      <c r="G128" s="298"/>
-      <c r="H128" s="298"/>
-      <c r="I128" s="298"/>
-      <c r="J128" s="299"/>
-    </row>
-    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D128" s="301" t="s">
+        <v>404</v>
+      </c>
+      <c r="E128" s="302"/>
+      <c r="F128" s="302"/>
+      <c r="G128" s="302"/>
+      <c r="H128" s="302"/>
+      <c r="I128" s="302"/>
+      <c r="J128" s="303"/>
+    </row>
+    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>240</v>
       </c>
@@ -5544,29 +5584,29 @@
         <v>100000</v>
       </c>
       <c r="C129" s="16"/>
-      <c r="D129" s="300"/>
-      <c r="E129" s="301"/>
-      <c r="F129" s="301"/>
-      <c r="G129" s="301"/>
-      <c r="H129" s="301"/>
-      <c r="I129" s="301"/>
-      <c r="J129" s="302"/>
-    </row>
-    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D129" s="304"/>
+      <c r="E129" s="305"/>
+      <c r="F129" s="305"/>
+      <c r="G129" s="305"/>
+      <c r="H129" s="305"/>
+      <c r="I129" s="305"/>
+      <c r="J129" s="306"/>
+    </row>
+    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11"/>
       <c r="B130" s="63">
         <v>0</v>
       </c>
       <c r="C130" s="16"/>
-      <c r="D130" s="300"/>
-      <c r="E130" s="301"/>
-      <c r="F130" s="301"/>
-      <c r="G130" s="301"/>
-      <c r="H130" s="301"/>
-      <c r="I130" s="301"/>
-      <c r="J130" s="302"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D130" s="304"/>
+      <c r="E130" s="305"/>
+      <c r="F130" s="305"/>
+      <c r="G130" s="305"/>
+      <c r="H130" s="305"/>
+      <c r="I130" s="305"/>
+      <c r="J130" s="306"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="25" t="s">
         <v>16</v>
       </c>
@@ -5575,69 +5615,69 @@
         <v>598840</v>
       </c>
       <c r="C131" s="16"/>
-      <c r="D131" s="300"/>
-      <c r="E131" s="301"/>
-      <c r="F131" s="301"/>
-      <c r="G131" s="301"/>
-      <c r="H131" s="301"/>
-      <c r="I131" s="301"/>
-      <c r="J131" s="302"/>
-    </row>
-    <row r="132" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D131" s="304"/>
+      <c r="E131" s="305"/>
+      <c r="F131" s="305"/>
+      <c r="G131" s="305"/>
+      <c r="H131" s="305"/>
+      <c r="I131" s="305"/>
+      <c r="J131" s="306"/>
+    </row>
+    <row r="132" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C132" s="17"/>
-      <c r="D132" s="300"/>
-      <c r="E132" s="301"/>
-      <c r="F132" s="301"/>
-      <c r="G132" s="301"/>
-      <c r="H132" s="301"/>
-      <c r="I132" s="301"/>
-      <c r="J132" s="302"/>
-    </row>
-    <row r="133" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="308" t="s">
-        <v>362</v>
-      </c>
-      <c r="B133" s="310">
+      <c r="D132" s="304"/>
+      <c r="E132" s="305"/>
+      <c r="F132" s="305"/>
+      <c r="G132" s="305"/>
+      <c r="H132" s="305"/>
+      <c r="I132" s="305"/>
+      <c r="J132" s="306"/>
+    </row>
+    <row r="133" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="312" t="s">
+        <v>361</v>
+      </c>
+      <c r="B133" s="314">
         <f>B131+B113+B123</f>
         <v>-388336.84963389952</v>
       </c>
       <c r="C133" s="10"/>
-      <c r="D133" s="300"/>
-      <c r="E133" s="301"/>
-      <c r="F133" s="301"/>
-      <c r="G133" s="301"/>
-      <c r="H133" s="301"/>
-      <c r="I133" s="301"/>
-      <c r="J133" s="302"/>
-    </row>
-    <row r="134" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="309"/>
-      <c r="B134" s="311"/>
-      <c r="D134" s="303"/>
-      <c r="E134" s="304"/>
-      <c r="F134" s="304"/>
-      <c r="G134" s="304"/>
-      <c r="H134" s="304"/>
-      <c r="I134" s="304"/>
-      <c r="J134" s="305"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D133" s="304"/>
+      <c r="E133" s="305"/>
+      <c r="F133" s="305"/>
+      <c r="G133" s="305"/>
+      <c r="H133" s="305"/>
+      <c r="I133" s="305"/>
+      <c r="J133" s="306"/>
+    </row>
+    <row r="134" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="313"/>
+      <c r="B134" s="315"/>
+      <c r="D134" s="307"/>
+      <c r="E134" s="308"/>
+      <c r="F134" s="308"/>
+      <c r="G134" s="308"/>
+      <c r="H134" s="308"/>
+      <c r="I134" s="308"/>
+      <c r="J134" s="309"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D140" s="53"/>
       <c r="E140" s="53"/>
       <c r="F140" s="53"/>
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D141" s="256" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E141" s="53"/>
       <c r="F141" s="53"/>
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D142" s="256"/>
       <c r="E142" s="53"/>
       <c r="F142" s="53"/>
@@ -5673,37 +5713,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="365" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="371" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="366"/>
-      <c r="C1" s="366"/>
-      <c r="D1" s="366"/>
-      <c r="E1" s="366"/>
+      <c r="B1" s="372"/>
+      <c r="C1" s="372"/>
+      <c r="D1" s="372"/>
+      <c r="E1" s="372"/>
       <c r="F1" s="120" t="s">
         <v>276</v>
       </c>
@@ -5715,20 +5755,20 @@
       <c r="L1" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="343">
+      <c r="M1" s="349">
         <f>RESUMEN!D83-N3</f>
         <v>17532713.560000002</v>
       </c>
-      <c r="N1" s="344"/>
+      <c r="N1" s="350"/>
       <c r="O1" s="121"/>
       <c r="P1" s="45"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="367"/>
-      <c r="B2" s="368"/>
-      <c r="C2" s="368"/>
-      <c r="D2" s="368"/>
-      <c r="E2" s="368"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="373"/>
+      <c r="B2" s="374"/>
+      <c r="C2" s="374"/>
+      <c r="D2" s="374"/>
+      <c r="E2" s="374"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5747,12 +5787,12 @@
       <c r="O2" s="122"/>
       <c r="P2" s="45"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="367"/>
-      <c r="B3" s="368"/>
-      <c r="C3" s="368"/>
-      <c r="D3" s="368"/>
-      <c r="E3" s="368"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="373"/>
+      <c r="B3" s="374"/>
+      <c r="C3" s="374"/>
+      <c r="D3" s="374"/>
+      <c r="E3" s="374"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5762,7 +5802,7 @@
       <c r="J3" s="123"/>
       <c r="K3" s="123"/>
       <c r="L3" s="150" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="177">
@@ -5771,12 +5811,12 @@
       <c r="O3" s="124"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="369"/>
-      <c r="B4" s="370"/>
-      <c r="C4" s="370"/>
-      <c r="D4" s="370"/>
-      <c r="E4" s="370"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="375"/>
+      <c r="B4" s="376"/>
+      <c r="C4" s="376"/>
+      <c r="D4" s="376"/>
+      <c r="E4" s="376"/>
       <c r="F4" s="125"/>
       <c r="G4" s="125"/>
       <c r="H4" s="125"/>
@@ -5789,98 +5829,98 @@
       <c r="O4" s="128"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="350" t="s">
-        <v>386</v>
-      </c>
-      <c r="D5" s="351"/>
-      <c r="E5" s="351"/>
-      <c r="F5" s="351"/>
-      <c r="G5" s="351"/>
-      <c r="H5" s="351"/>
-      <c r="I5" s="351"/>
-      <c r="J5" s="351"/>
-      <c r="K5" s="351"/>
-      <c r="L5" s="351"/>
-      <c r="M5" s="351"/>
-      <c r="N5" s="351"/>
-      <c r="O5" s="352"/>
+      <c r="C5" s="356" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" s="357"/>
+      <c r="E5" s="357"/>
+      <c r="F5" s="357"/>
+      <c r="G5" s="357"/>
+      <c r="H5" s="357"/>
+      <c r="I5" s="357"/>
+      <c r="J5" s="357"/>
+      <c r="K5" s="357"/>
+      <c r="L5" s="357"/>
+      <c r="M5" s="357"/>
+      <c r="N5" s="357"/>
+      <c r="O5" s="358"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="353"/>
-      <c r="D6" s="354"/>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
-      <c r="G6" s="354"/>
-      <c r="H6" s="354"/>
-      <c r="I6" s="354"/>
-      <c r="J6" s="354"/>
-      <c r="K6" s="354"/>
-      <c r="L6" s="354"/>
-      <c r="M6" s="354"/>
-      <c r="N6" s="354"/>
-      <c r="O6" s="355"/>
+      <c r="C6" s="359"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="360"/>
+      <c r="F6" s="360"/>
+      <c r="G6" s="360"/>
+      <c r="H6" s="360"/>
+      <c r="I6" s="360"/>
+      <c r="J6" s="360"/>
+      <c r="K6" s="360"/>
+      <c r="L6" s="360"/>
+      <c r="M6" s="360"/>
+      <c r="N6" s="360"/>
+      <c r="O6" s="361"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="353"/>
-      <c r="D7" s="354"/>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
-      <c r="G7" s="354"/>
-      <c r="H7" s="354"/>
-      <c r="I7" s="354"/>
-      <c r="J7" s="354"/>
-      <c r="K7" s="354"/>
-      <c r="L7" s="354"/>
-      <c r="M7" s="354"/>
-      <c r="N7" s="354"/>
-      <c r="O7" s="355"/>
+      <c r="C7" s="359"/>
+      <c r="D7" s="360"/>
+      <c r="E7" s="360"/>
+      <c r="F7" s="360"/>
+      <c r="G7" s="360"/>
+      <c r="H7" s="360"/>
+      <c r="I7" s="360"/>
+      <c r="J7" s="360"/>
+      <c r="K7" s="360"/>
+      <c r="L7" s="360"/>
+      <c r="M7" s="360"/>
+      <c r="N7" s="360"/>
+      <c r="O7" s="361"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="356"/>
-      <c r="D8" s="357"/>
-      <c r="E8" s="357"/>
-      <c r="F8" s="357"/>
-      <c r="G8" s="357"/>
-      <c r="H8" s="357"/>
-      <c r="I8" s="357"/>
-      <c r="J8" s="357"/>
-      <c r="K8" s="357"/>
-      <c r="L8" s="357"/>
-      <c r="M8" s="357"/>
-      <c r="N8" s="357"/>
-      <c r="O8" s="358"/>
+      <c r="C8" s="362"/>
+      <c r="D8" s="363"/>
+      <c r="E8" s="363"/>
+      <c r="F8" s="363"/>
+      <c r="G8" s="363"/>
+      <c r="H8" s="363"/>
+      <c r="I8" s="363"/>
+      <c r="J8" s="363"/>
+      <c r="K8" s="363"/>
+      <c r="L8" s="363"/>
+      <c r="M8" s="363"/>
+      <c r="N8" s="363"/>
+      <c r="O8" s="364"/>
       <c r="Q8" s="64"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="359" t="s">
+      <c r="C9" s="365" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="360"/>
-      <c r="E9" s="360"/>
-      <c r="F9" s="360"/>
-      <c r="G9" s="360"/>
-      <c r="H9" s="360"/>
-      <c r="I9" s="360"/>
-      <c r="J9" s="360"/>
-      <c r="K9" s="360"/>
-      <c r="L9" s="360"/>
-      <c r="M9" s="360"/>
-      <c r="N9" s="360"/>
-      <c r="O9" s="361"/>
+      <c r="D9" s="366"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
+      <c r="G9" s="366"/>
+      <c r="H9" s="366"/>
+      <c r="I9" s="366"/>
+      <c r="J9" s="366"/>
+      <c r="K9" s="366"/>
+      <c r="L9" s="366"/>
+      <c r="M9" s="366"/>
+      <c r="N9" s="366"/>
+      <c r="O9" s="367"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -5889,22 +5929,22 @@
         <v>230001.74197199999</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="362"/>
-      <c r="D10" s="363"/>
-      <c r="E10" s="363"/>
-      <c r="F10" s="363"/>
-      <c r="G10" s="363"/>
-      <c r="H10" s="363"/>
-      <c r="I10" s="363"/>
-      <c r="J10" s="363"/>
-      <c r="K10" s="363"/>
-      <c r="L10" s="363"/>
-      <c r="M10" s="363"/>
-      <c r="N10" s="363"/>
-      <c r="O10" s="364"/>
+      <c r="C10" s="368"/>
+      <c r="D10" s="369"/>
+      <c r="E10" s="369"/>
+      <c r="F10" s="369"/>
+      <c r="G10" s="369"/>
+      <c r="H10" s="369"/>
+      <c r="I10" s="369"/>
+      <c r="J10" s="369"/>
+      <c r="K10" s="369"/>
+      <c r="L10" s="369"/>
+      <c r="M10" s="369"/>
+      <c r="N10" s="369"/>
+      <c r="O10" s="370"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -5913,50 +5953,50 @@
         <v>272594.657152</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="334" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="340" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="336" t="s">
+      <c r="B11" s="342" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="334" t="s">
+      <c r="C11" s="340" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="338" t="s">
+      <c r="D11" s="344" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="338" t="s">
+      <c r="E11" s="344" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="334" t="s">
+      <c r="F11" s="340" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="334" t="s">
+      <c r="G11" s="340" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="334" t="s">
+      <c r="H11" s="340" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="345" t="s">
+      <c r="I11" s="351" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="331" t="s">
+      <c r="J11" s="337" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="331" t="s">
-        <v>372</v>
-      </c>
-      <c r="L11" s="331" t="s">
+      <c r="K11" s="337" t="s">
+        <v>371</v>
+      </c>
+      <c r="L11" s="337" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="347" t="s">
+      <c r="M11" s="353" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="331" t="s">
+      <c r="N11" s="337" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="331" t="s">
+      <c r="O11" s="337" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -5967,22 +6007,22 @@
         <v>257687.13683900001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="335"/>
-      <c r="B12" s="337"/>
-      <c r="C12" s="335"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="335"/>
-      <c r="G12" s="335"/>
-      <c r="H12" s="335"/>
-      <c r="I12" s="346"/>
-      <c r="J12" s="332"/>
-      <c r="K12" s="332"/>
-      <c r="L12" s="332"/>
-      <c r="M12" s="348"/>
-      <c r="N12" s="332"/>
-      <c r="O12" s="332"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="341"/>
+      <c r="B12" s="343"/>
+      <c r="C12" s="341"/>
+      <c r="D12" s="345"/>
+      <c r="E12" s="345"/>
+      <c r="F12" s="341"/>
+      <c r="G12" s="341"/>
+      <c r="H12" s="341"/>
+      <c r="I12" s="352"/>
+      <c r="J12" s="338"/>
+      <c r="K12" s="338"/>
+      <c r="L12" s="338"/>
+      <c r="M12" s="354"/>
+      <c r="N12" s="338"/>
+      <c r="O12" s="338"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -5991,20 +6031,20 @@
         <v>317317.21809099999</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="335"/>
-      <c r="B13" s="337"/>
-      <c r="C13" s="335"/>
-      <c r="D13" s="339"/>
-      <c r="E13" s="339"/>
-      <c r="F13" s="335"/>
-      <c r="G13" s="335"/>
-      <c r="H13" s="335"/>
-      <c r="I13" s="346"/>
-      <c r="J13" s="332"/>
-      <c r="K13" s="333"/>
-      <c r="L13" s="333"/>
-      <c r="M13" s="348"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="341"/>
+      <c r="B13" s="343"/>
+      <c r="C13" s="341"/>
+      <c r="D13" s="345"/>
+      <c r="E13" s="345"/>
+      <c r="F13" s="341"/>
+      <c r="G13" s="341"/>
+      <c r="H13" s="341"/>
+      <c r="I13" s="352"/>
+      <c r="J13" s="338"/>
+      <c r="K13" s="339"/>
+      <c r="L13" s="339"/>
+      <c r="M13" s="354"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/08</v>
@@ -6021,7 +6061,7 @@
         <v>370558.36206599994</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="195" t="s">
         <v>114</v>
       </c>
@@ -6071,12 +6111,12 @@
         <v>279722.56363456004</v>
       </c>
       <c r="P14" s="85" t="s">
-        <v>348</v>
-      </c>
-      <c r="R14" s="340"/>
-      <c r="S14" s="340"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+      <c r="R14" s="346"/>
+      <c r="S14" s="346"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="24" t="s">
@@ -6121,12 +6161,12 @@
         <v>555069.33031720005</v>
       </c>
       <c r="P15" s="85" t="s">
-        <v>347</v>
-      </c>
-      <c r="R15" s="340"/>
-      <c r="S15" s="340"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+      <c r="R15" s="346"/>
+      <c r="S15" s="346"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -6178,7 +6218,7 @@
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6225,7 +6265,7 @@
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6272,7 +6312,7 @@
       <c r="P18" s="85"/>
       <c r="S18" s="32"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
         <v>116</v>
       </c>
@@ -6326,7 +6366,7 @@
       </c>
       <c r="S19" s="32"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
         <v>117</v>
       </c>
@@ -6381,7 +6421,7 @@
       </c>
       <c r="S20" s="32"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>116</v>
       </c>
@@ -6434,7 +6474,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>118</v>
       </c>
@@ -6492,7 +6532,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>118</v>
       </c>
@@ -6548,7 +6588,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>118</v>
       </c>
@@ -6604,7 +6644,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>116</v>
       </c>
@@ -6660,7 +6700,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
         <v>117</v>
       </c>
@@ -6714,7 +6754,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="78" t="s">
         <v>116</v>
       </c>
@@ -6769,7 +6809,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="78" t="s">
         <v>118</v>
       </c>
@@ -6823,7 +6863,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="78" t="s">
         <v>118</v>
       </c>
@@ -6877,7 +6917,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="78" t="s">
         <v>118</v>
       </c>
@@ -6929,7 +6969,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="78" t="s">
         <v>116</v>
       </c>
@@ -6983,7 +7023,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>117</v>
       </c>
@@ -7039,7 +7079,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>116</v>
       </c>
@@ -7093,7 +7133,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A34" s="108" t="s">
         <v>118</v>
       </c>
@@ -7149,7 +7189,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>118</v>
       </c>
@@ -7158,7 +7198,7 @@
         <v>56</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E35" s="104" t="s">
         <v>272</v>
@@ -7205,7 +7245,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>118</v>
       </c>
@@ -7257,7 +7297,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>116</v>
       </c>
@@ -7316,7 +7356,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>117</v>
       </c>
@@ -7370,7 +7410,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78" t="s">
         <v>116</v>
       </c>
@@ -7522,7 +7562,7 @@
       <c r="DI39" s="53"/>
       <c r="DJ39" s="53"/>
     </row>
-    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78" t="s">
         <v>118</v>
       </c>
@@ -7676,7 +7716,7 @@
       <c r="DI40" s="53"/>
       <c r="DJ40" s="53"/>
     </row>
-    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="78" t="s">
         <v>118</v>
       </c>
@@ -7685,7 +7725,7 @@
         <v>62</v>
       </c>
       <c r="D41" s="78" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E41" s="104"/>
       <c r="F41" s="105">
@@ -7830,7 +7870,7 @@
       <c r="DI41" s="53"/>
       <c r="DJ41" s="53"/>
     </row>
-    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="78" t="s">
         <v>118</v>
       </c>
@@ -7982,7 +8022,7 @@
       <c r="DI42" s="53"/>
       <c r="DJ42" s="53"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
         <v>116</v>
       </c>
@@ -8035,7 +8075,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
         <v>117</v>
       </c>
@@ -8091,7 +8131,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>116</v>
       </c>
@@ -8151,7 +8191,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="132" t="s">
         <v>118</v>
       </c>
@@ -8205,7 +8245,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
         <v>118</v>
       </c>
@@ -8261,7 +8301,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
         <v>118</v>
       </c>
@@ -8315,7 +8355,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
         <v>116</v>
       </c>
@@ -8369,7 +8409,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
         <v>117</v>
       </c>
@@ -8424,7 +8464,7 @@
       </c>
       <c r="Q50" s="32"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="43" t="s">
         <v>116</v>
       </c>
@@ -8479,7 +8519,7 @@
       </c>
       <c r="Q51" s="32"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>118</v>
       </c>
@@ -8491,7 +8531,7 @@
         <v>267</v>
       </c>
       <c r="E52" s="104" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F52" s="105">
         <v>9.4000000000000004E-3</v>
@@ -8535,10 +8575,10 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="Q52" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>118</v>
       </c>
@@ -8592,7 +8632,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="43" t="s">
         <v>118</v>
       </c>
@@ -8645,7 +8685,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>116</v>
       </c>
@@ -8700,7 +8740,7 @@
       </c>
       <c r="R55" s="45"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="43" t="s">
         <v>117</v>
       </c>
@@ -8756,7 +8796,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>116</v>
       </c>
@@ -8810,7 +8850,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>118</v>
       </c>
@@ -8866,7 +8906,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="78" t="s">
         <v>118</v>
       </c>
@@ -8923,7 +8963,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="78" t="s">
         <v>118</v>
       </c>
@@ -8980,7 +9020,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="78" t="s">
         <v>116</v>
       </c>
@@ -9034,7 +9074,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
         <v>117</v>
       </c>
@@ -9088,7 +9128,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>116</v>
       </c>
@@ -9142,7 +9182,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>118</v>
       </c>
@@ -9154,7 +9194,7 @@
         <v>197</v>
       </c>
       <c r="E64" s="104" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F64" s="105">
         <v>9.4000000000000004E-3</v>
@@ -9197,7 +9237,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>118</v>
       </c>
@@ -9250,7 +9290,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>118</v>
       </c>
@@ -9305,7 +9345,7 @@
       </c>
       <c r="S66" s="142"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>116</v>
       </c>
@@ -9360,7 +9400,7 @@
       </c>
       <c r="S67" s="32"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="108" t="s">
         <v>117</v>
       </c>
@@ -9369,7 +9409,7 @@
         <v>89</v>
       </c>
       <c r="D68" s="78" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E68" s="104"/>
       <c r="F68" s="105">
@@ -9414,7 +9454,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>116</v>
       </c>
@@ -9467,7 +9507,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>118</v>
       </c>
@@ -9521,7 +9561,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>118</v>
       </c>
@@ -9575,10 +9615,10 @@
         <v>0.53000000000000025</v>
       </c>
       <c r="R71" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>118</v>
       </c>
@@ -9629,7 +9669,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>119</v>
       </c>
@@ -9684,7 +9724,7 @@
       </c>
       <c r="Q73" s="53"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
         <v>116</v>
       </c>
@@ -9738,7 +9778,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
         <v>118</v>
       </c>
@@ -9792,7 +9832,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>118</v>
       </c>
@@ -9848,7 +9888,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="78" t="s">
         <v>118</v>
       </c>
@@ -9902,7 +9942,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="78" t="s">
         <v>119</v>
       </c>
@@ -9956,7 +9996,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>116</v>
       </c>
@@ -10010,7 +10050,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
         <v>118</v>
       </c>
@@ -10063,7 +10103,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
         <v>118</v>
       </c>
@@ -10119,7 +10159,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>118</v>
       </c>
@@ -10173,7 +10213,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="43" t="s">
         <v>119</v>
       </c>
@@ -10227,7 +10267,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>116</v>
       </c>
@@ -10280,7 +10320,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>118</v>
       </c>
@@ -10334,7 +10374,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>118</v>
       </c>
@@ -10388,7 +10428,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="78" t="s">
         <v>118</v>
       </c>
@@ -10442,7 +10482,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="78"/>
       <c r="B88" s="24"/>
       <c r="C88" s="24" t="s">
@@ -10494,7 +10534,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="78"/>
       <c r="B89" s="24"/>
       <c r="C89" s="24" t="s">
@@ -10546,7 +10586,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="78"/>
       <c r="B90" s="24"/>
       <c r="C90" s="24" t="s">
@@ -10598,7 +10638,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="78"/>
       <c r="B91" s="24"/>
       <c r="C91" s="24" t="s">
@@ -10650,7 +10690,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="78"/>
       <c r="B92" s="24"/>
       <c r="C92" s="136" t="s">
@@ -10705,7 +10745,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="78"/>
       <c r="B93" s="24"/>
       <c r="C93" s="24" t="s">
@@ -10757,7 +10797,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="78"/>
       <c r="B94" s="24"/>
       <c r="C94" s="24" t="s">
@@ -10809,7 +10849,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="78"/>
       <c r="B95" s="24"/>
       <c r="C95" s="24" t="s">
@@ -10861,7 +10901,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="78"/>
       <c r="B96" s="24"/>
       <c r="C96" s="24" t="s">
@@ -10913,7 +10953,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="78"/>
       <c r="B97" s="24"/>
       <c r="C97" s="267" t="s">
@@ -10962,7 +11002,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="78"/>
       <c r="B98" s="24"/>
       <c r="C98" s="24" t="s">
@@ -11014,7 +11054,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="78"/>
       <c r="B99" s="24"/>
       <c r="C99" s="24" t="s">
@@ -11065,7 +11105,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="78"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24" t="s">
@@ -11117,7 +11157,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="78"/>
       <c r="B101" s="24"/>
       <c r="C101" s="267" t="s">
@@ -11166,7 +11206,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="78"/>
       <c r="B102" s="24"/>
       <c r="C102" s="24" t="s">
@@ -11218,7 +11258,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="78"/>
       <c r="B103" s="24"/>
       <c r="C103" s="24" t="s">
@@ -11270,7 +11310,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="78"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24" t="s">
@@ -11319,7 +11359,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="78"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24" t="s">
@@ -11371,7 +11411,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="78"/>
       <c r="B106" s="24"/>
       <c r="C106" s="24" t="s">
@@ -11422,7 +11462,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="78"/>
       <c r="B107" s="24"/>
       <c r="C107" s="24" t="s">
@@ -11473,7 +11513,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="78"/>
       <c r="B108" s="24"/>
       <c r="C108" s="24" t="s">
@@ -11525,7 +11565,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="78"/>
       <c r="B109" s="24"/>
       <c r="C109" s="24" t="s">
@@ -11576,7 +11616,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="78"/>
       <c r="B110" s="24"/>
       <c r="C110" s="267" t="s">
@@ -11627,7 +11667,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="78"/>
       <c r="B111" s="24"/>
       <c r="C111" s="24" t="s">
@@ -11679,7 +11719,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="78"/>
       <c r="B112" s="24"/>
       <c r="C112" s="24" t="s">
@@ -11731,7 +11771,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="78"/>
       <c r="B113" s="24"/>
       <c r="C113" s="24" t="s">
@@ -11783,7 +11823,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="78"/>
       <c r="B114" s="24"/>
       <c r="C114" s="24" t="s">
@@ -11835,7 +11875,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="78"/>
       <c r="B115" s="24"/>
       <c r="C115" s="24" t="s">
@@ -11886,7 +11926,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="78"/>
       <c r="B116" s="24"/>
       <c r="C116" s="24" t="s">
@@ -11940,7 +11980,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="78"/>
       <c r="B117" s="24"/>
       <c r="C117" s="24" t="s">
@@ -11950,7 +11990,7 @@
         <v>177</v>
       </c>
       <c r="E117" s="78" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F117" s="110">
         <v>2.3E-3</v>
@@ -11991,7 +12031,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="78"/>
       <c r="B118" s="24"/>
       <c r="C118" s="24" t="s">
@@ -12001,7 +12041,7 @@
         <v>178</v>
       </c>
       <c r="E118" s="104" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F118" s="110">
         <v>2.3E-3</v>
@@ -12048,7 +12088,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="97"/>
       <c r="B119" s="24"/>
       <c r="C119" s="24" t="s">
@@ -12100,7 +12140,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="97"/>
       <c r="B120" s="24"/>
       <c r="C120" s="24" t="s">
@@ -12152,7 +12192,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="97"/>
       <c r="B121" s="24"/>
       <c r="C121" s="24" t="s">
@@ -12162,7 +12202,7 @@
         <v>177</v>
       </c>
       <c r="E121" s="78" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F121" s="110">
         <v>2.3E-3</v>
@@ -12205,7 +12245,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="97"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
@@ -12256,7 +12296,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="97"/>
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
@@ -12308,7 +12348,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="97"/>
       <c r="B124" s="24"/>
       <c r="C124" s="24" t="s">
@@ -12363,7 +12403,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="135"/>
       <c r="B125" s="130"/>
       <c r="C125" s="24" t="s">
@@ -12417,7 +12457,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="135"/>
       <c r="B126" s="130"/>
       <c r="C126" s="24" t="s">
@@ -12469,7 +12509,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="97"/>
       <c r="B127" s="24"/>
       <c r="C127" s="24" t="s">
@@ -12521,7 +12561,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="97"/>
       <c r="B128" s="24"/>
       <c r="C128" s="24" t="s">
@@ -12573,7 +12613,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="97"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24" t="s">
@@ -12625,7 +12665,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="97" t="s">
         <v>24</v>
       </c>
@@ -12679,7 +12719,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="97" t="s">
         <v>24</v>
       </c>
@@ -12732,7 +12772,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="40" t="s">
         <v>24</v>
       </c>
@@ -12751,7 +12791,7 @@
       <c r="N132" s="2"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -12793,43 +12833,43 @@
       </c>
       <c r="Q133" s="45"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L134" s="47">
         <f>L133-M1</f>
         <v>-3002976.0931200404</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="342"/>
-      <c r="D135" s="342"/>
-      <c r="E135" s="342"/>
-      <c r="F135" s="342"/>
-      <c r="G135" s="342"/>
-      <c r="H135" s="342"/>
-      <c r="I135" s="342"/>
-      <c r="J135" s="342"/>
-      <c r="K135" s="342"/>
-      <c r="L135" s="342"/>
-      <c r="M135" s="342"/>
-      <c r="N135" s="342"/>
-      <c r="O135" s="342"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="342"/>
-      <c r="D136" s="342"/>
-      <c r="E136" s="342"/>
-      <c r="F136" s="342"/>
-      <c r="G136" s="342"/>
-      <c r="H136" s="342"/>
-      <c r="I136" s="342"/>
-      <c r="J136" s="342"/>
-      <c r="K136" s="342"/>
-      <c r="L136" s="342"/>
-      <c r="M136" s="342"/>
-      <c r="N136" s="342"/>
-      <c r="O136" s="342"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="348"/>
+      <c r="D135" s="348"/>
+      <c r="E135" s="348"/>
+      <c r="F135" s="348"/>
+      <c r="G135" s="348"/>
+      <c r="H135" s="348"/>
+      <c r="I135" s="348"/>
+      <c r="J135" s="348"/>
+      <c r="K135" s="348"/>
+      <c r="L135" s="348"/>
+      <c r="M135" s="348"/>
+      <c r="N135" s="348"/>
+      <c r="O135" s="348"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="348"/>
+      <c r="D136" s="348"/>
+      <c r="E136" s="348"/>
+      <c r="F136" s="348"/>
+      <c r="G136" s="348"/>
+      <c r="H136" s="348"/>
+      <c r="I136" s="348"/>
+      <c r="J136" s="348"/>
+      <c r="K136" s="348"/>
+      <c r="L136" s="348"/>
+      <c r="M136" s="348"/>
+      <c r="N136" s="348"/>
+      <c r="O136" s="348"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
       <c r="D137" s="57"/>
       <c r="E137" s="57"/>
@@ -12844,129 +12884,129 @@
       <c r="N137" s="57"/>
       <c r="O137" s="57"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C138" s="349" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C138" s="355" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="349"/>
-      <c r="E138" s="349"/>
-      <c r="F138" s="349"/>
-      <c r="G138" s="349"/>
-      <c r="H138" s="349"/>
-      <c r="I138" s="349"/>
-      <c r="J138" s="349"/>
-      <c r="K138" s="349"/>
-      <c r="L138" s="349"/>
-      <c r="M138" s="349"/>
-      <c r="N138" s="349"/>
-      <c r="O138" s="349"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="349"/>
-      <c r="D139" s="349"/>
-      <c r="E139" s="349"/>
-      <c r="F139" s="349"/>
-      <c r="G139" s="349"/>
-      <c r="H139" s="349"/>
-      <c r="I139" s="349"/>
-      <c r="J139" s="349"/>
-      <c r="K139" s="349"/>
-      <c r="L139" s="349"/>
-      <c r="M139" s="349"/>
-      <c r="N139" s="349"/>
-      <c r="O139" s="349"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="349"/>
-      <c r="D140" s="349"/>
-      <c r="E140" s="349"/>
-      <c r="F140" s="349"/>
-      <c r="G140" s="349"/>
-      <c r="H140" s="349"/>
-      <c r="I140" s="349"/>
-      <c r="J140" s="349"/>
-      <c r="K140" s="349"/>
-      <c r="L140" s="349"/>
-      <c r="M140" s="349"/>
-      <c r="N140" s="349"/>
-      <c r="O140" s="349"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="349"/>
-      <c r="D141" s="349"/>
-      <c r="E141" s="349"/>
-      <c r="F141" s="349"/>
-      <c r="G141" s="349"/>
-      <c r="H141" s="349"/>
-      <c r="I141" s="349"/>
-      <c r="J141" s="349"/>
-      <c r="K141" s="349"/>
-      <c r="L141" s="349"/>
-      <c r="M141" s="349"/>
-      <c r="N141" s="349"/>
-      <c r="O141" s="349"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="349"/>
-      <c r="D142" s="349"/>
-      <c r="E142" s="349"/>
-      <c r="F142" s="349"/>
-      <c r="G142" s="349"/>
-      <c r="H142" s="349"/>
-      <c r="I142" s="349"/>
-      <c r="J142" s="349"/>
-      <c r="K142" s="349"/>
-      <c r="L142" s="349"/>
-      <c r="M142" s="349"/>
-      <c r="N142" s="349"/>
-      <c r="O142" s="349"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="349"/>
-      <c r="D143" s="349"/>
-      <c r="E143" s="349"/>
-      <c r="F143" s="349"/>
-      <c r="G143" s="349"/>
-      <c r="H143" s="349"/>
-      <c r="I143" s="349"/>
-      <c r="J143" s="349"/>
-      <c r="K143" s="349"/>
-      <c r="L143" s="349"/>
-      <c r="M143" s="349"/>
-      <c r="N143" s="349"/>
-      <c r="O143" s="349"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="349"/>
-      <c r="D144" s="349"/>
-      <c r="E144" s="349"/>
-      <c r="F144" s="349"/>
-      <c r="G144" s="349"/>
-      <c r="H144" s="349"/>
-      <c r="I144" s="349"/>
-      <c r="J144" s="349"/>
-      <c r="K144" s="349"/>
-      <c r="L144" s="349"/>
-      <c r="M144" s="349"/>
-      <c r="N144" s="349"/>
-      <c r="O144" s="349"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="349"/>
-      <c r="D145" s="349"/>
-      <c r="E145" s="349"/>
-      <c r="F145" s="349"/>
-      <c r="G145" s="349"/>
-      <c r="H145" s="349"/>
-      <c r="I145" s="349"/>
-      <c r="J145" s="349"/>
-      <c r="K145" s="349"/>
-      <c r="L145" s="349"/>
-      <c r="M145" s="349"/>
-      <c r="N145" s="349"/>
-      <c r="O145" s="349"/>
-    </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D138" s="355"/>
+      <c r="E138" s="355"/>
+      <c r="F138" s="355"/>
+      <c r="G138" s="355"/>
+      <c r="H138" s="355"/>
+      <c r="I138" s="355"/>
+      <c r="J138" s="355"/>
+      <c r="K138" s="355"/>
+      <c r="L138" s="355"/>
+      <c r="M138" s="355"/>
+      <c r="N138" s="355"/>
+      <c r="O138" s="355"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C139" s="355"/>
+      <c r="D139" s="355"/>
+      <c r="E139" s="355"/>
+      <c r="F139" s="355"/>
+      <c r="G139" s="355"/>
+      <c r="H139" s="355"/>
+      <c r="I139" s="355"/>
+      <c r="J139" s="355"/>
+      <c r="K139" s="355"/>
+      <c r="L139" s="355"/>
+      <c r="M139" s="355"/>
+      <c r="N139" s="355"/>
+      <c r="O139" s="355"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C140" s="355"/>
+      <c r="D140" s="355"/>
+      <c r="E140" s="355"/>
+      <c r="F140" s="355"/>
+      <c r="G140" s="355"/>
+      <c r="H140" s="355"/>
+      <c r="I140" s="355"/>
+      <c r="J140" s="355"/>
+      <c r="K140" s="355"/>
+      <c r="L140" s="355"/>
+      <c r="M140" s="355"/>
+      <c r="N140" s="355"/>
+      <c r="O140" s="355"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C141" s="355"/>
+      <c r="D141" s="355"/>
+      <c r="E141" s="355"/>
+      <c r="F141" s="355"/>
+      <c r="G141" s="355"/>
+      <c r="H141" s="355"/>
+      <c r="I141" s="355"/>
+      <c r="J141" s="355"/>
+      <c r="K141" s="355"/>
+      <c r="L141" s="355"/>
+      <c r="M141" s="355"/>
+      <c r="N141" s="355"/>
+      <c r="O141" s="355"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C142" s="355"/>
+      <c r="D142" s="355"/>
+      <c r="E142" s="355"/>
+      <c r="F142" s="355"/>
+      <c r="G142" s="355"/>
+      <c r="H142" s="355"/>
+      <c r="I142" s="355"/>
+      <c r="J142" s="355"/>
+      <c r="K142" s="355"/>
+      <c r="L142" s="355"/>
+      <c r="M142" s="355"/>
+      <c r="N142" s="355"/>
+      <c r="O142" s="355"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C143" s="355"/>
+      <c r="D143" s="355"/>
+      <c r="E143" s="355"/>
+      <c r="F143" s="355"/>
+      <c r="G143" s="355"/>
+      <c r="H143" s="355"/>
+      <c r="I143" s="355"/>
+      <c r="J143" s="355"/>
+      <c r="K143" s="355"/>
+      <c r="L143" s="355"/>
+      <c r="M143" s="355"/>
+      <c r="N143" s="355"/>
+      <c r="O143" s="355"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C144" s="355"/>
+      <c r="D144" s="355"/>
+      <c r="E144" s="355"/>
+      <c r="F144" s="355"/>
+      <c r="G144" s="355"/>
+      <c r="H144" s="355"/>
+      <c r="I144" s="355"/>
+      <c r="J144" s="355"/>
+      <c r="K144" s="355"/>
+      <c r="L144" s="355"/>
+      <c r="M144" s="355"/>
+      <c r="N144" s="355"/>
+      <c r="O144" s="355"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C145" s="355"/>
+      <c r="D145" s="355"/>
+      <c r="E145" s="355"/>
+      <c r="F145" s="355"/>
+      <c r="G145" s="355"/>
+      <c r="H145" s="355"/>
+      <c r="I145" s="355"/>
+      <c r="J145" s="355"/>
+      <c r="K145" s="355"/>
+      <c r="L145" s="355"/>
+      <c r="M145" s="355"/>
+      <c r="N145" s="355"/>
+      <c r="O145" s="355"/>
+    </row>
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="E146" s="57"/>
@@ -12981,7 +13021,7 @@
       <c r="N146" s="57"/>
       <c r="O146" s="57"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="57"/>
       <c r="D147" s="57"/>
       <c r="E147" s="57"/>
@@ -12996,116 +13036,116 @@
       <c r="N147" s="57"/>
       <c r="O147" s="57"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="341" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C148" s="347" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="341"/>
-      <c r="E148" s="341"/>
-      <c r="F148" s="341"/>
-      <c r="G148" s="341"/>
-      <c r="H148" s="341"/>
-      <c r="I148" s="341"/>
-      <c r="J148" s="341"/>
-      <c r="K148" s="341"/>
-      <c r="L148" s="341"/>
-      <c r="M148" s="341"/>
-      <c r="N148" s="341"/>
-      <c r="O148" s="341"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="341"/>
-      <c r="D149" s="341"/>
-      <c r="E149" s="341"/>
-      <c r="F149" s="341"/>
-      <c r="G149" s="341"/>
-      <c r="H149" s="341"/>
-      <c r="I149" s="341"/>
-      <c r="J149" s="341"/>
-      <c r="K149" s="341"/>
-      <c r="L149" s="341"/>
-      <c r="M149" s="341"/>
-      <c r="N149" s="341"/>
-      <c r="O149" s="341"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="341"/>
-      <c r="D150" s="341"/>
-      <c r="E150" s="341"/>
-      <c r="F150" s="341"/>
-      <c r="G150" s="341"/>
-      <c r="H150" s="341"/>
-      <c r="I150" s="341"/>
-      <c r="J150" s="341"/>
-      <c r="K150" s="341"/>
-      <c r="L150" s="341"/>
-      <c r="M150" s="341"/>
-      <c r="N150" s="341"/>
-      <c r="O150" s="341"/>
+      <c r="D148" s="347"/>
+      <c r="E148" s="347"/>
+      <c r="F148" s="347"/>
+      <c r="G148" s="347"/>
+      <c r="H148" s="347"/>
+      <c r="I148" s="347"/>
+      <c r="J148" s="347"/>
+      <c r="K148" s="347"/>
+      <c r="L148" s="347"/>
+      <c r="M148" s="347"/>
+      <c r="N148" s="347"/>
+      <c r="O148" s="347"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C149" s="347"/>
+      <c r="D149" s="347"/>
+      <c r="E149" s="347"/>
+      <c r="F149" s="347"/>
+      <c r="G149" s="347"/>
+      <c r="H149" s="347"/>
+      <c r="I149" s="347"/>
+      <c r="J149" s="347"/>
+      <c r="K149" s="347"/>
+      <c r="L149" s="347"/>
+      <c r="M149" s="347"/>
+      <c r="N149" s="347"/>
+      <c r="O149" s="347"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C150" s="347"/>
+      <c r="D150" s="347"/>
+      <c r="E150" s="347"/>
+      <c r="F150" s="347"/>
+      <c r="G150" s="347"/>
+      <c r="H150" s="347"/>
+      <c r="I150" s="347"/>
+      <c r="J150" s="347"/>
+      <c r="K150" s="347"/>
+      <c r="L150" s="347"/>
+      <c r="M150" s="347"/>
+      <c r="N150" s="347"/>
+      <c r="O150" s="347"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>3002976.0931200404</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="341"/>
-      <c r="D151" s="341"/>
-      <c r="E151" s="341"/>
-      <c r="F151" s="341"/>
-      <c r="G151" s="341"/>
-      <c r="H151" s="341"/>
-      <c r="I151" s="341"/>
-      <c r="J151" s="341"/>
-      <c r="K151" s="341"/>
-      <c r="L151" s="341"/>
-      <c r="M151" s="341"/>
-      <c r="N151" s="341"/>
-      <c r="O151" s="341"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="341"/>
-      <c r="D152" s="341"/>
-      <c r="E152" s="341"/>
-      <c r="F152" s="341"/>
-      <c r="G152" s="341"/>
-      <c r="H152" s="341"/>
-      <c r="I152" s="341"/>
-      <c r="J152" s="341"/>
-      <c r="K152" s="341"/>
-      <c r="L152" s="341"/>
-      <c r="M152" s="341"/>
-      <c r="N152" s="341"/>
-      <c r="O152" s="341"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
-      <c r="G153" s="341"/>
-      <c r="H153" s="341"/>
-      <c r="I153" s="341"/>
-      <c r="J153" s="341"/>
-      <c r="K153" s="341"/>
-      <c r="L153" s="341"/>
-      <c r="M153" s="341"/>
-      <c r="N153" s="341"/>
-      <c r="O153" s="341"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="341"/>
-      <c r="D154" s="341"/>
-      <c r="E154" s="341"/>
-      <c r="F154" s="341"/>
-      <c r="G154" s="341"/>
-      <c r="H154" s="341"/>
-      <c r="I154" s="341"/>
-      <c r="J154" s="341"/>
-      <c r="K154" s="341"/>
-      <c r="L154" s="341"/>
-      <c r="M154" s="341"/>
-      <c r="N154" s="341"/>
-      <c r="O154" s="341"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="347"/>
+      <c r="D151" s="347"/>
+      <c r="E151" s="347"/>
+      <c r="F151" s="347"/>
+      <c r="G151" s="347"/>
+      <c r="H151" s="347"/>
+      <c r="I151" s="347"/>
+      <c r="J151" s="347"/>
+      <c r="K151" s="347"/>
+      <c r="L151" s="347"/>
+      <c r="M151" s="347"/>
+      <c r="N151" s="347"/>
+      <c r="O151" s="347"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="347"/>
+      <c r="D152" s="347"/>
+      <c r="E152" s="347"/>
+      <c r="F152" s="347"/>
+      <c r="G152" s="347"/>
+      <c r="H152" s="347"/>
+      <c r="I152" s="347"/>
+      <c r="J152" s="347"/>
+      <c r="K152" s="347"/>
+      <c r="L152" s="347"/>
+      <c r="M152" s="347"/>
+      <c r="N152" s="347"/>
+      <c r="O152" s="347"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="347"/>
+      <c r="D153" s="347"/>
+      <c r="E153" s="347"/>
+      <c r="F153" s="347"/>
+      <c r="G153" s="347"/>
+      <c r="H153" s="347"/>
+      <c r="I153" s="347"/>
+      <c r="J153" s="347"/>
+      <c r="K153" s="347"/>
+      <c r="L153" s="347"/>
+      <c r="M153" s="347"/>
+      <c r="N153" s="347"/>
+      <c r="O153" s="347"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="347"/>
+      <c r="D154" s="347"/>
+      <c r="E154" s="347"/>
+      <c r="F154" s="347"/>
+      <c r="G154" s="347"/>
+      <c r="H154" s="347"/>
+      <c r="I154" s="347"/>
+      <c r="J154" s="347"/>
+      <c r="K154" s="347"/>
+      <c r="L154" s="347"/>
+      <c r="M154" s="347"/>
+      <c r="N154" s="347"/>
+      <c r="O154" s="347"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -13142,84 +13182,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
-    <col min="15" max="15" width="19.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="382" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="381" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="382"/>
-      <c r="C1" s="382"/>
-      <c r="D1" s="382"/>
-      <c r="E1" s="382"/>
-      <c r="F1" s="382"/>
-      <c r="G1" s="382"/>
-      <c r="H1" s="382"/>
-      <c r="I1" s="382"/>
-      <c r="J1" s="382"/>
-      <c r="K1" s="382"/>
-      <c r="L1" s="382"/>
-      <c r="M1" s="382"/>
-      <c r="N1" s="382"/>
-      <c r="O1" s="383"/>
+      <c r="B1" s="381"/>
+      <c r="C1" s="381"/>
+      <c r="D1" s="381"/>
+      <c r="E1" s="381"/>
+      <c r="F1" s="381"/>
+      <c r="G1" s="381"/>
+      <c r="H1" s="381"/>
+      <c r="I1" s="381"/>
+      <c r="J1" s="381"/>
+      <c r="K1" s="381"/>
+      <c r="L1" s="381"/>
+      <c r="M1" s="381"/>
+      <c r="N1" s="381"/>
+      <c r="O1" s="382"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="384"/>
-      <c r="B2" s="384"/>
-      <c r="C2" s="384"/>
-      <c r="D2" s="384"/>
-      <c r="E2" s="384"/>
-      <c r="F2" s="384"/>
-      <c r="G2" s="384"/>
-      <c r="H2" s="384"/>
-      <c r="I2" s="384"/>
-      <c r="J2" s="384"/>
-      <c r="K2" s="384"/>
-      <c r="L2" s="384"/>
-      <c r="M2" s="384"/>
-      <c r="N2" s="384"/>
-      <c r="O2" s="385"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="383"/>
+      <c r="B2" s="383"/>
+      <c r="C2" s="383"/>
+      <c r="D2" s="383"/>
+      <c r="E2" s="383"/>
+      <c r="F2" s="383"/>
+      <c r="G2" s="383"/>
+      <c r="H2" s="383"/>
+      <c r="I2" s="383"/>
+      <c r="J2" s="383"/>
+      <c r="K2" s="383"/>
+      <c r="L2" s="383"/>
+      <c r="M2" s="383"/>
+      <c r="N2" s="383"/>
+      <c r="O2" s="384"/>
       <c r="R2" s="32"/>
     </row>
-    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="379" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380"/>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
-      <c r="H3" s="380"/>
-      <c r="I3" s="380"/>
-      <c r="J3" s="380"/>
-      <c r="K3" s="380"/>
-      <c r="L3" s="380"/>
-      <c r="M3" s="380"/>
-      <c r="N3" s="380"/>
-      <c r="O3" s="381"/>
+    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="378" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="379"/>
+      <c r="C3" s="379"/>
+      <c r="D3" s="379"/>
+      <c r="E3" s="379"/>
+      <c r="F3" s="379"/>
+      <c r="G3" s="379"/>
+      <c r="H3" s="379"/>
+      <c r="I3" s="379"/>
+      <c r="J3" s="379"/>
+      <c r="K3" s="379"/>
+      <c r="L3" s="379"/>
+      <c r="M3" s="379"/>
+      <c r="N3" s="379"/>
+      <c r="O3" s="380"/>
       <c r="P3" s="185"/>
       <c r="Q3" s="185"/>
       <c r="R3" s="185"/>
@@ -13233,89 +13273,89 @@
       <c r="Z3" s="185"/>
       <c r="AA3" s="185"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="334" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="340" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="334" t="s">
+      <c r="B4" s="340" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="334" t="s">
+      <c r="C4" s="340" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="334" t="s">
+      <c r="D4" s="340" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="331" t="s">
+      <c r="E4" s="337" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="331" t="s">
+      <c r="F4" s="337" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="331" t="s">
+      <c r="G4" s="337" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="331" t="s">
+      <c r="H4" s="337" t="s">
         <v>336</v>
       </c>
-      <c r="I4" s="331" t="s">
-        <v>345</v>
-      </c>
-      <c r="J4" s="371" t="s">
+      <c r="I4" s="337" t="s">
+        <v>344</v>
+      </c>
+      <c r="J4" s="385" t="s">
         <v>332</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="376" t="s">
+      <c r="L4" s="389" t="s">
+        <v>341</v>
+      </c>
+      <c r="M4" s="337" t="s">
         <v>342</v>
       </c>
-      <c r="M4" s="331" t="s">
-        <v>343</v>
-      </c>
-      <c r="N4" s="331" t="s">
+      <c r="N4" s="337" t="s">
         <v>333</v>
       </c>
-      <c r="O4" s="331" t="s">
+      <c r="O4" s="337" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="335"/>
-      <c r="B5" s="335"/>
-      <c r="C5" s="335"/>
-      <c r="D5" s="335"/>
-      <c r="E5" s="332"/>
-      <c r="F5" s="332"/>
-      <c r="G5" s="332"/>
-      <c r="H5" s="332"/>
-      <c r="I5" s="332"/>
-      <c r="J5" s="372"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="341"/>
+      <c r="B5" s="341"/>
+      <c r="C5" s="341"/>
+      <c r="D5" s="341"/>
+      <c r="E5" s="338"/>
+      <c r="F5" s="338"/>
+      <c r="G5" s="338"/>
+      <c r="H5" s="338"/>
+      <c r="I5" s="338"/>
+      <c r="J5" s="386"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="377"/>
-      <c r="M5" s="332"/>
-      <c r="N5" s="332"/>
-      <c r="O5" s="332"/>
+      <c r="L5" s="390"/>
+      <c r="M5" s="338"/>
+      <c r="N5" s="338"/>
+      <c r="O5" s="338"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="375"/>
-      <c r="B6" s="375"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="375"/>
-      <c r="E6" s="374"/>
-      <c r="F6" s="374"/>
-      <c r="G6" s="374"/>
-      <c r="H6" s="374"/>
-      <c r="I6" s="374"/>
-      <c r="J6" s="373"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="388"/>
+      <c r="B6" s="388"/>
+      <c r="C6" s="388"/>
+      <c r="D6" s="388"/>
+      <c r="E6" s="377"/>
+      <c r="F6" s="377"/>
+      <c r="G6" s="377"/>
+      <c r="H6" s="377"/>
+      <c r="I6" s="377"/>
+      <c r="J6" s="387"/>
       <c r="K6" s="154"/>
-      <c r="L6" s="378"/>
-      <c r="M6" s="374"/>
-      <c r="N6" s="374"/>
-      <c r="O6" s="374"/>
+      <c r="L6" s="391"/>
+      <c r="M6" s="377"/>
+      <c r="N6" s="377"/>
+      <c r="O6" s="377"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="155" t="s">
         <v>109</v>
       </c>
@@ -13367,10 +13407,10 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="340"/>
-      <c r="S7" s="340"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R7" s="346"/>
+      <c r="S7" s="346"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="155" t="s">
         <v>312</v>
       </c>
@@ -13422,10 +13462,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="340"/>
-      <c r="S8" s="340"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R8" s="346"/>
+      <c r="S8" s="346"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="155" t="s">
         <v>110</v>
       </c>
@@ -13479,7 +13519,7 @@
       </c>
       <c r="S9" s="32"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="155" t="s">
         <v>111</v>
       </c>
@@ -13534,7 +13574,7 @@
       </c>
       <c r="S10" s="32"/>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="159" t="s">
         <v>112</v>
       </c>
@@ -13589,7 +13629,7 @@
       </c>
       <c r="S11" s="32"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="162" t="s">
         <v>40</v>
       </c>
@@ -13645,7 +13685,7 @@
       </c>
       <c r="S12" s="32"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="155" t="s">
         <v>41</v>
       </c>
@@ -13698,7 +13738,7 @@
       </c>
       <c r="S13" s="32"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="155" t="s">
         <v>42</v>
       </c>
@@ -13752,7 +13792,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="155" t="s">
         <v>43</v>
       </c>
@@ -13806,7 +13846,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="155" t="s">
         <v>44</v>
       </c>
@@ -13858,7 +13898,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A17" s="155" t="s">
         <v>45</v>
       </c>
@@ -13912,7 +13952,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A18" s="155" t="s">
         <v>46</v>
       </c>
@@ -13966,7 +14006,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A19" s="155" t="s">
         <v>47</v>
       </c>
@@ -14018,7 +14058,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A20" s="155" t="s">
         <v>48</v>
       </c>
@@ -14070,7 +14110,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A21" s="155" t="s">
         <v>49</v>
       </c>
@@ -14122,7 +14162,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A22" s="155" t="s">
         <v>50</v>
       </c>
@@ -14174,7 +14214,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A23" s="155" t="s">
         <v>51</v>
       </c>
@@ -14229,7 +14269,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A24" s="155" t="s">
         <v>52</v>
       </c>
@@ -14281,7 +14321,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A25" s="155" t="s">
         <v>53</v>
       </c>
@@ -14333,7 +14373,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A26" s="155" t="s">
         <v>54</v>
       </c>
@@ -14387,7 +14427,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A27" s="155" t="s">
         <v>55</v>
       </c>
@@ -14443,7 +14483,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A28" s="155" t="s">
         <v>56</v>
       </c>
@@ -14495,7 +14535,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A29" s="155" t="s">
         <v>57</v>
       </c>
@@ -14548,7 +14588,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A30" s="155" t="s">
         <v>58</v>
       </c>
@@ -14603,7 +14643,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A31" s="155" t="s">
         <v>59</v>
       </c>
@@ -14657,7 +14697,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="155" t="s">
         <v>60</v>
       </c>
@@ -14810,7 +14850,7 @@
       <c r="DI32" s="53"/>
       <c r="DJ32" s="53"/>
     </row>
-    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="155" t="s">
         <v>61</v>
       </c>
@@ -14964,7 +15004,7 @@
       <c r="DI33" s="53"/>
       <c r="DJ33" s="53"/>
     </row>
-    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="155" t="s">
         <v>62</v>
       </c>
@@ -15118,7 +15158,7 @@
       <c r="DI34" s="53"/>
       <c r="DJ34" s="53"/>
     </row>
-    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="155" t="s">
         <v>63</v>
       </c>
@@ -15269,7 +15309,7 @@
       <c r="DI35" s="53"/>
       <c r="DJ35" s="53"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="155" t="s">
         <v>64</v>
       </c>
@@ -15323,7 +15363,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="155" t="s">
         <v>65</v>
       </c>
@@ -15377,7 +15417,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="155" t="s">
         <v>66</v>
       </c>
@@ -15437,7 +15477,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A39" s="155" t="s">
         <v>67</v>
       </c>
@@ -15491,7 +15531,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A40" s="155" t="s">
         <v>68</v>
       </c>
@@ -15543,7 +15583,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A41" s="155" t="s">
         <v>69</v>
       </c>
@@ -15595,7 +15635,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A42" s="155" t="s">
         <v>70</v>
       </c>
@@ -15649,7 +15689,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="155" t="s">
         <v>71</v>
       </c>
@@ -15704,7 +15744,7 @@
       </c>
       <c r="Q43" s="32"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="155" t="s">
         <v>72</v>
       </c>
@@ -15759,7 +15799,7 @@
       </c>
       <c r="Q44" s="32"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="155" t="s">
         <v>73</v>
       </c>
@@ -15816,7 +15856,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="155" t="s">
         <v>74</v>
       </c>
@@ -15868,7 +15908,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="155" t="s">
         <v>75</v>
       </c>
@@ -15920,7 +15960,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="155" t="s">
         <v>76</v>
       </c>
@@ -15975,7 +16015,7 @@
       </c>
       <c r="R48" s="45"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="155" t="s">
         <v>77</v>
       </c>
@@ -16027,7 +16067,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="155" t="s">
         <v>78</v>
       </c>
@@ -16082,7 +16122,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="155" t="s">
         <v>79</v>
       </c>
@@ -16134,13 +16174,13 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="155" t="s">
         <v>80</v>
       </c>
       <c r="B52" s="156"/>
       <c r="C52" s="78" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D52" s="105">
         <v>8.6999999999999994E-3</v>
@@ -16189,7 +16229,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="155" t="s">
         <v>81</v>
       </c>
@@ -16246,7 +16286,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="155" t="s">
         <v>82</v>
       </c>
@@ -16300,7 +16340,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="155" t="s">
         <v>83</v>
       </c>
@@ -16352,7 +16392,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="155" t="s">
         <v>84</v>
       </c>
@@ -16406,7 +16446,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="155" t="s">
         <v>85</v>
       </c>
@@ -16460,7 +16500,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="155" t="s">
         <v>86</v>
       </c>
@@ -16514,7 +16554,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="155" t="s">
         <v>87</v>
       </c>
@@ -16573,7 +16613,7 @@
       </c>
       <c r="S59" s="142"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="155" t="s">
         <v>88</v>
       </c>
@@ -16628,7 +16668,7 @@
       </c>
       <c r="S60" s="32"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="155" t="s">
         <v>89</v>
       </c>
@@ -16681,7 +16721,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="155" t="s">
         <v>90</v>
       </c>
@@ -16735,7 +16775,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="155" t="s">
         <v>91</v>
       </c>
@@ -16787,7 +16827,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="155" t="s">
         <v>92</v>
       </c>
@@ -16842,7 +16882,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="155" t="s">
         <v>93</v>
       </c>
@@ -16897,7 +16937,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="155" t="s">
         <v>94</v>
       </c>
@@ -16952,7 +16992,7 @@
       </c>
       <c r="Q66" s="53"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="155" t="s">
         <v>95</v>
       </c>
@@ -17006,7 +17046,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="155" t="s">
         <v>96</v>
       </c>
@@ -17050,7 +17090,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="155" t="s">
         <v>97</v>
       </c>
@@ -17103,7 +17143,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="155" t="s">
         <v>98</v>
       </c>
@@ -17157,7 +17197,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="155" t="s">
         <v>99</v>
       </c>
@@ -17211,7 +17251,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="155" t="s">
         <v>100</v>
       </c>
@@ -17265,7 +17305,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="155" t="s">
         <v>101</v>
       </c>
@@ -17318,7 +17358,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="155" t="s">
         <v>102</v>
       </c>
@@ -17372,7 +17412,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="155" t="s">
         <v>103</v>
       </c>
@@ -17424,7 +17464,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="155" t="s">
         <v>104</v>
       </c>
@@ -17478,7 +17518,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="155" t="s">
         <v>105</v>
       </c>
@@ -17533,7 +17573,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="155" t="s">
         <v>106</v>
       </c>
@@ -17587,7 +17627,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="155" t="s">
         <v>107</v>
       </c>
@@ -17641,7 +17681,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="155" t="s">
         <v>108</v>
       </c>
@@ -17697,7 +17737,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="24"/>
       <c r="B81" s="24"/>
       <c r="C81" s="78"/>
@@ -17714,7 +17754,7 @@
       <c r="N81" s="113"/>
       <c r="O81" s="114"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -17755,6 +17795,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
@@ -17770,8 +17812,6 @@
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17781,16 +17821,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="C1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K1" s="53"/>
       <c r="L1" s="53"/>
       <c r="M1" s="53"/>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C2" s="245" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D2" s="246">
         <v>1</v>
@@ -17805,9 +17845,9 @@
       <c r="L2" s="53"/>
       <c r="M2" s="53"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C3" s="247" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D3" s="248"/>
       <c r="E3" s="249">
@@ -17815,7 +17855,7 @@
       </c>
       <c r="F3" s="53"/>
       <c r="G3" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H3" s="191"/>
       <c r="I3" s="192"/>
@@ -17824,22 +17864,22 @@
       <c r="L3" s="250"/>
       <c r="M3" s="250"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" s="247" t="s">
+        <v>351</v>
+      </c>
+      <c r="D4" s="248" t="s">
         <v>352</v>
       </c>
-      <c r="D4" s="248" t="s">
+      <c r="E4" s="248" t="s">
         <v>353</v>
-      </c>
-      <c r="E4" s="248" t="s">
-        <v>354</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H4" s="53" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I4" s="192"/>
       <c r="J4" s="193"/>
@@ -17847,9 +17887,9 @@
       <c r="L4" s="250"/>
       <c r="M4" s="250"/>
     </row>
-    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="186" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D5" s="53"/>
       <c r="E5" s="53"/>
@@ -17862,60 +17902,60 @@
       <c r="L5" s="250"/>
       <c r="M5" s="250"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="386" t="s">
-        <v>394</v>
-      </c>
-      <c r="D6" s="387"/>
-      <c r="E6" s="387"/>
-      <c r="F6" s="387"/>
-      <c r="G6" s="387"/>
-      <c r="H6" s="387"/>
-      <c r="I6" s="387"/>
-      <c r="J6" s="388"/>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="392" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="393"/>
+      <c r="E6" s="393"/>
+      <c r="F6" s="393"/>
+      <c r="G6" s="393"/>
+      <c r="H6" s="393"/>
+      <c r="I6" s="393"/>
+      <c r="J6" s="394"/>
       <c r="K6" s="53"/>
       <c r="L6" s="53"/>
       <c r="M6" s="53"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="389"/>
-      <c r="D7" s="390"/>
-      <c r="E7" s="390"/>
-      <c r="F7" s="390"/>
-      <c r="G7" s="390"/>
-      <c r="H7" s="390"/>
-      <c r="I7" s="390"/>
-      <c r="J7" s="391"/>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="395"/>
+      <c r="D7" s="396"/>
+      <c r="E7" s="396"/>
+      <c r="F7" s="396"/>
+      <c r="G7" s="396"/>
+      <c r="H7" s="396"/>
+      <c r="I7" s="396"/>
+      <c r="J7" s="397"/>
       <c r="K7" s="53"/>
       <c r="L7" s="53"/>
       <c r="M7" s="53"/>
     </row>
-    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="392"/>
-      <c r="D8" s="393"/>
-      <c r="E8" s="393"/>
-      <c r="F8" s="393"/>
-      <c r="G8" s="393"/>
-      <c r="H8" s="393"/>
-      <c r="I8" s="393"/>
-      <c r="J8" s="394"/>
+    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="398"/>
+      <c r="D8" s="399"/>
+      <c r="E8" s="399"/>
+      <c r="F8" s="399"/>
+      <c r="G8" s="399"/>
+      <c r="H8" s="399"/>
+      <c r="I8" s="399"/>
+      <c r="J8" s="400"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="K9" s="53"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
     </row>
-    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K10" s="53"/>
       <c r="L10" s="53"/>
       <c r="M10" s="53"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D11" s="290">
         <f>D2+1</f>
@@ -17928,9 +17968,9 @@
       <c r="I11" s="189"/>
       <c r="J11" s="190"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="291" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D12" s="292"/>
       <c r="E12" s="293">
@@ -17938,35 +17978,35 @@
       </c>
       <c r="F12" s="53"/>
       <c r="G12" s="53" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H12" s="191"/>
       <c r="I12" s="192"/>
       <c r="J12" s="193"/>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="291" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" s="292" t="s">
         <v>352</v>
       </c>
-      <c r="D13" s="292" t="s">
+      <c r="E13" s="292" t="s">
         <v>353</v>
-      </c>
-      <c r="E13" s="292" t="s">
-        <v>354</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I13" s="192"/>
       <c r="J13" s="193"/>
     </row>
-    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="186" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D14" s="53"/>
       <c r="E14" s="53"/>
@@ -17976,37 +18016,37 @@
       <c r="I14" s="53"/>
       <c r="J14" s="194"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="386" t="s">
-        <v>395</v>
-      </c>
-      <c r="D15" s="387"/>
-      <c r="E15" s="387"/>
-      <c r="F15" s="387"/>
-      <c r="G15" s="387"/>
-      <c r="H15" s="387"/>
-      <c r="I15" s="387"/>
-      <c r="J15" s="388"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="389"/>
-      <c r="D16" s="390"/>
-      <c r="E16" s="390"/>
-      <c r="F16" s="390"/>
-      <c r="G16" s="390"/>
-      <c r="H16" s="390"/>
-      <c r="I16" s="390"/>
-      <c r="J16" s="391"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="392"/>
-      <c r="D17" s="393"/>
-      <c r="E17" s="393"/>
-      <c r="F17" s="393"/>
-      <c r="G17" s="393"/>
-      <c r="H17" s="393"/>
-      <c r="I17" s="393"/>
-      <c r="J17" s="394"/>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="392" t="s">
+        <v>394</v>
+      </c>
+      <c r="D15" s="393"/>
+      <c r="E15" s="393"/>
+      <c r="F15" s="393"/>
+      <c r="G15" s="393"/>
+      <c r="H15" s="393"/>
+      <c r="I15" s="393"/>
+      <c r="J15" s="394"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="395"/>
+      <c r="D16" s="396"/>
+      <c r="E16" s="396"/>
+      <c r="F16" s="396"/>
+      <c r="G16" s="396"/>
+      <c r="H16" s="396"/>
+      <c r="I16" s="396"/>
+      <c r="J16" s="397"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="398"/>
+      <c r="D17" s="399"/>
+      <c r="E17" s="399"/>
+      <c r="F17" s="399"/>
+      <c r="G17" s="399"/>
+      <c r="H17" s="399"/>
+      <c r="I17" s="399"/>
+      <c r="J17" s="400"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95A34FD-0BA3-41CE-B27D-1316D5F8A52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2FB4D6-0003-4097-9426-1AD7AC737F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2406,8 +2406,29 @@
     </xf>
     <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="12" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2440,12 +2461,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2508,50 +2523,14 @@
     <xf numFmtId="164" fontId="28" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2570,6 +2549,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2643,6 +2631,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2678,15 +2687,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3128,7 +3128,7 @@
     <col min="10" max="10" width="14.7109375" customWidth="1"/>
     <col min="11" max="11" width="18.140625" customWidth="1"/>
     <col min="12" max="12" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="17" width="18.28515625" customWidth="1"/>
@@ -3239,108 +3239,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="332" t="s">
+      <c r="A14" s="298" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="332"/>
-      <c r="C14" s="332"/>
-      <c r="D14" s="332"/>
-      <c r="E14" s="332"/>
-      <c r="F14" s="332"/>
-      <c r="G14" s="332"/>
-      <c r="H14" s="332"/>
-      <c r="I14" s="332"/>
-      <c r="J14" s="332"/>
+      <c r="B14" s="298"/>
+      <c r="C14" s="298"/>
+      <c r="D14" s="298"/>
+      <c r="E14" s="298"/>
+      <c r="F14" s="298"/>
+      <c r="G14" s="298"/>
+      <c r="H14" s="298"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="298"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="332"/>
-      <c r="B15" s="332"/>
-      <c r="C15" s="332"/>
-      <c r="D15" s="332"/>
-      <c r="E15" s="332"/>
-      <c r="F15" s="332"/>
-      <c r="G15" s="332"/>
-      <c r="H15" s="332"/>
-      <c r="I15" s="332"/>
-      <c r="J15" s="332"/>
+      <c r="A15" s="298"/>
+      <c r="B15" s="298"/>
+      <c r="C15" s="298"/>
+      <c r="D15" s="298"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="298"/>
+      <c r="G15" s="298"/>
+      <c r="H15" s="298"/>
+      <c r="I15" s="298"/>
+      <c r="J15" s="298"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="332"/>
-      <c r="B16" s="332"/>
-      <c r="C16" s="332"/>
-      <c r="D16" s="332"/>
-      <c r="E16" s="332"/>
-      <c r="F16" s="332"/>
-      <c r="G16" s="332"/>
-      <c r="H16" s="332"/>
-      <c r="I16" s="332"/>
-      <c r="J16" s="332"/>
+      <c r="A16" s="298"/>
+      <c r="B16" s="298"/>
+      <c r="C16" s="298"/>
+      <c r="D16" s="298"/>
+      <c r="E16" s="298"/>
+      <c r="F16" s="298"/>
+      <c r="G16" s="298"/>
+      <c r="H16" s="298"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="298"/>
     </row>
     <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="332"/>
-      <c r="B17" s="332"/>
-      <c r="C17" s="332"/>
-      <c r="D17" s="332"/>
-      <c r="E17" s="332"/>
-      <c r="F17" s="332"/>
-      <c r="G17" s="332"/>
-      <c r="H17" s="332"/>
-      <c r="I17" s="332"/>
-      <c r="J17" s="332"/>
+      <c r="A17" s="298"/>
+      <c r="B17" s="298"/>
+      <c r="C17" s="298"/>
+      <c r="D17" s="298"/>
+      <c r="E17" s="298"/>
+      <c r="F17" s="298"/>
+      <c r="G17" s="298"/>
+      <c r="H17" s="298"/>
+      <c r="I17" s="298"/>
+      <c r="J17" s="298"/>
     </row>
     <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="332"/>
-      <c r="B18" s="332"/>
-      <c r="C18" s="332"/>
-      <c r="D18" s="332"/>
-      <c r="E18" s="332"/>
-      <c r="F18" s="332"/>
-      <c r="G18" s="332"/>
-      <c r="H18" s="332"/>
-      <c r="I18" s="332"/>
-      <c r="J18" s="332"/>
+      <c r="A18" s="298"/>
+      <c r="B18" s="298"/>
+      <c r="C18" s="298"/>
+      <c r="D18" s="298"/>
+      <c r="E18" s="298"/>
+      <c r="F18" s="298"/>
+      <c r="G18" s="298"/>
+      <c r="H18" s="298"/>
+      <c r="I18" s="298"/>
+      <c r="J18" s="298"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="333" t="s">
+      <c r="A20" s="299" t="s">
         <v>397</v>
       </c>
-      <c r="B20" s="333"/>
-      <c r="C20" s="333"/>
-      <c r="D20" s="333"/>
-      <c r="E20" s="333"/>
-      <c r="F20" s="333"/>
-      <c r="G20" s="333"/>
-      <c r="H20" s="333"/>
-      <c r="I20" s="333"/>
-      <c r="J20" s="333"/>
+      <c r="B20" s="299"/>
+      <c r="C20" s="299"/>
+      <c r="D20" s="299"/>
+      <c r="E20" s="299"/>
+      <c r="F20" s="299"/>
+      <c r="G20" s="299"/>
+      <c r="H20" s="299"/>
+      <c r="I20" s="299"/>
+      <c r="J20" s="299"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="333"/>
-      <c r="B21" s="333"/>
-      <c r="C21" s="333"/>
-      <c r="D21" s="333"/>
-      <c r="E21" s="333"/>
-      <c r="F21" s="333"/>
-      <c r="G21" s="333"/>
-      <c r="H21" s="333"/>
-      <c r="I21" s="333"/>
-      <c r="J21" s="333"/>
+      <c r="A21" s="299"/>
+      <c r="B21" s="299"/>
+      <c r="C21" s="299"/>
+      <c r="D21" s="299"/>
+      <c r="E21" s="299"/>
+      <c r="F21" s="299"/>
+      <c r="G21" s="299"/>
+      <c r="H21" s="299"/>
+      <c r="I21" s="299"/>
+      <c r="J21" s="299"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="333"/>
-      <c r="B22" s="333"/>
-      <c r="C22" s="333"/>
-      <c r="D22" s="333"/>
-      <c r="E22" s="333"/>
-      <c r="F22" s="333"/>
-      <c r="G22" s="333"/>
-      <c r="H22" s="333"/>
-      <c r="I22" s="333"/>
-      <c r="J22" s="333"/>
+      <c r="A22" s="299"/>
+      <c r="B22" s="299"/>
+      <c r="C22" s="299"/>
+      <c r="D22" s="299"/>
+      <c r="E22" s="299"/>
+      <c r="F22" s="299"/>
+      <c r="G22" s="299"/>
+      <c r="H22" s="299"/>
+      <c r="I22" s="299"/>
+      <c r="J22" s="299"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
@@ -3809,8 +3809,8 @@
       <c r="L44" s="50"/>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="310"/>
-      <c r="B45" s="311"/>
+      <c r="A45" s="300"/>
+      <c r="B45" s="301"/>
       <c r="C45" s="175"/>
       <c r="D45" s="33"/>
       <c r="E45" s="206"/>
@@ -4061,10 +4061,10 @@
       <c r="N52" s="64"/>
     </row>
     <row r="53" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="298" t="s">
+      <c r="A53" s="302" t="s">
         <v>402</v>
       </c>
-      <c r="B53" s="334"/>
+      <c r="B53" s="303"/>
       <c r="C53" s="33" t="s">
         <v>410</v>
       </c>
@@ -4367,10 +4367,10 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="335" t="s">
+      <c r="A63" s="304" t="s">
         <v>414</v>
       </c>
-      <c r="B63" s="336"/>
+      <c r="B63" s="305"/>
       <c r="C63" s="136" t="s">
         <v>415</v>
       </c>
@@ -4383,14 +4383,20 @@
       <c r="H63" s="55"/>
       <c r="I63" s="55"/>
       <c r="J63" s="44"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="54"/>
+      <c r="K63" s="32">
+        <f t="shared" si="13"/>
+        <v>175700</v>
+      </c>
+      <c r="L63" s="54">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="335" t="s">
+      <c r="A64" s="304" t="s">
         <v>416</v>
       </c>
-      <c r="B64" s="336"/>
+      <c r="B64" s="305"/>
       <c r="C64" s="136" t="s">
         <v>415</v>
       </c>
@@ -4403,14 +4409,20 @@
       <c r="H64" s="55"/>
       <c r="I64" s="55"/>
       <c r="J64" s="44"/>
-      <c r="K64" s="32"/>
-      <c r="L64" s="54"/>
+      <c r="K64" s="32">
+        <f t="shared" si="13"/>
+        <v>206000</v>
+      </c>
+      <c r="L64" s="54">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="298" t="s">
+      <c r="A65" s="302" t="s">
         <v>412</v>
       </c>
-      <c r="B65" s="334"/>
+      <c r="B65" s="303"/>
       <c r="C65" s="33" t="s">
         <v>413</v>
       </c>
@@ -4426,8 +4438,14 @@
       <c r="H65" s="44"/>
       <c r="I65" s="44"/>
       <c r="J65" s="44"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="54"/>
+      <c r="K65" s="32">
+        <f t="shared" si="13"/>
+        <v>150000</v>
+      </c>
+      <c r="L65" s="54">
+        <f t="shared" si="14"/>
+        <v>150000</v>
+      </c>
     </row>
     <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="295" t="s">
@@ -4446,8 +4464,14 @@
       <c r="H66" s="44"/>
       <c r="I66" s="44"/>
       <c r="J66" s="44"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="54"/>
+      <c r="K66" s="32">
+        <f t="shared" si="13"/>
+        <v>150000</v>
+      </c>
+      <c r="L66" s="54">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="285" t="s">
@@ -4464,8 +4488,14 @@
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
       <c r="J67" s="44"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="54"/>
+      <c r="K67" s="32">
+        <f t="shared" si="13"/>
+        <v>242000</v>
+      </c>
+      <c r="L67" s="54">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="295" t="s">
@@ -4484,14 +4514,20 @@
       <c r="H68" s="44"/>
       <c r="I68" s="44"/>
       <c r="J68" s="44"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="54"/>
+      <c r="K68" s="32">
+        <f t="shared" si="13"/>
+        <v>120000</v>
+      </c>
+      <c r="L68" s="54">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:14" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="310" t="s">
+      <c r="A69" s="300" t="s">
         <v>405</v>
       </c>
-      <c r="B69" s="311"/>
+      <c r="B69" s="301"/>
       <c r="C69" s="33" t="s">
         <v>406</v>
       </c>
@@ -5113,12 +5149,12 @@
       <c r="I92" s="46"/>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="319" t="s">
+      <c r="A93" s="324" t="s">
         <v>32</v>
       </c>
-      <c r="B93" s="320"/>
-      <c r="C93" s="320"/>
-      <c r="D93" s="320"/>
+      <c r="B93" s="325"/>
+      <c r="C93" s="325"/>
+      <c r="D93" s="325"/>
       <c r="E93" s="60" t="s">
         <v>10</v>
       </c>
@@ -5139,8 +5175,8 @@
       </c>
     </row>
     <row r="94" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="298"/>
-      <c r="B94" s="299"/>
+      <c r="A94" s="302"/>
+      <c r="B94" s="306"/>
       <c r="C94" s="243"/>
       <c r="D94" s="33"/>
       <c r="E94" s="219">
@@ -5154,8 +5190,8 @@
       <c r="J94" s="44"/>
     </row>
     <row r="95" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="321"/>
-      <c r="B95" s="322"/>
+      <c r="A95" s="326"/>
+      <c r="B95" s="327"/>
       <c r="C95" s="62"/>
       <c r="D95" s="33"/>
       <c r="E95" s="49"/>
@@ -5166,11 +5202,11 @@
       <c r="J95" s="44"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="316" t="s">
+      <c r="A96" s="321" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="317"/>
-      <c r="C96" s="318"/>
+      <c r="B96" s="322"/>
+      <c r="C96" s="323"/>
       <c r="D96" s="59">
         <f>SUM(D94:D95)</f>
         <v>0</v>
@@ -5220,30 +5256,30 @@
         <f>D83-D81</f>
         <v>18539011.560000002</v>
       </c>
-      <c r="D100" s="300" t="s">
+      <c r="D100" s="307" t="s">
         <v>284</v>
       </c>
-      <c r="E100" s="300"/>
-      <c r="F100" s="300"/>
-      <c r="G100" s="300"/>
-      <c r="H100" s="300"/>
-      <c r="I100" s="300"/>
+      <c r="E100" s="307"/>
+      <c r="F100" s="307"/>
+      <c r="G100" s="307"/>
+      <c r="H100" s="307"/>
+      <c r="I100" s="307"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D101" s="300"/>
-      <c r="E101" s="300"/>
-      <c r="F101" s="300"/>
-      <c r="G101" s="300"/>
-      <c r="H101" s="300"/>
-      <c r="I101" s="300"/>
+      <c r="D101" s="307"/>
+      <c r="E101" s="307"/>
+      <c r="F101" s="307"/>
+      <c r="G101" s="307"/>
+      <c r="H101" s="307"/>
+      <c r="I101" s="307"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D102" s="300"/>
-      <c r="E102" s="300"/>
-      <c r="F102" s="300"/>
-      <c r="G102" s="300"/>
-      <c r="H102" s="300"/>
-      <c r="I102" s="300"/>
+      <c r="D102" s="307"/>
+      <c r="E102" s="307"/>
+      <c r="F102" s="307"/>
+      <c r="G102" s="307"/>
+      <c r="H102" s="307"/>
+      <c r="I102" s="307"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
@@ -5251,12 +5287,12 @@
       </c>
       <c r="B103" s="9"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="300"/>
-      <c r="E103" s="300"/>
-      <c r="F103" s="300"/>
-      <c r="G103" s="300"/>
-      <c r="H103" s="300"/>
-      <c r="I103" s="300"/>
+      <c r="D103" s="307"/>
+      <c r="E103" s="307"/>
+      <c r="F103" s="307"/>
+      <c r="G103" s="307"/>
+      <c r="H103" s="307"/>
+      <c r="I103" s="307"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
@@ -5266,12 +5302,12 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C104" s="12"/>
-      <c r="D104" s="300"/>
-      <c r="E104" s="300"/>
-      <c r="F104" s="300"/>
-      <c r="G104" s="300"/>
-      <c r="H104" s="300"/>
-      <c r="I104" s="300"/>
+      <c r="D104" s="307"/>
+      <c r="E104" s="307"/>
+      <c r="F104" s="307"/>
+      <c r="G104" s="307"/>
+      <c r="H104" s="307"/>
+      <c r="I104" s="307"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
@@ -5284,12 +5320,12 @@
       <c r="C105" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D105" s="300"/>
-      <c r="E105" s="300"/>
-      <c r="F105" s="300"/>
-      <c r="G105" s="300"/>
-      <c r="H105" s="300"/>
-      <c r="I105" s="300"/>
+      <c r="D105" s="307"/>
+      <c r="E105" s="307"/>
+      <c r="F105" s="307"/>
+      <c r="G105" s="307"/>
+      <c r="H105" s="307"/>
+      <c r="I105" s="307"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
@@ -5300,12 +5336,12 @@
         <v>912822.36</v>
       </c>
       <c r="C106" s="12"/>
-      <c r="D106" s="300"/>
-      <c r="E106" s="300"/>
-      <c r="F106" s="300"/>
-      <c r="G106" s="300"/>
-      <c r="H106" s="300"/>
-      <c r="I106" s="300"/>
+      <c r="D106" s="307"/>
+      <c r="E106" s="307"/>
+      <c r="F106" s="307"/>
+      <c r="G106" s="307"/>
+      <c r="H106" s="307"/>
+      <c r="I106" s="307"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
@@ -5316,12 +5352,12 @@
         <v>-18539011.560000002</v>
       </c>
       <c r="C107" s="10"/>
-      <c r="D107" s="300"/>
-      <c r="E107" s="300"/>
-      <c r="F107" s="300"/>
-      <c r="G107" s="300"/>
-      <c r="H107" s="300"/>
-      <c r="I107" s="300"/>
+      <c r="D107" s="307"/>
+      <c r="E107" s="307"/>
+      <c r="F107" s="307"/>
+      <c r="G107" s="307"/>
+      <c r="H107" s="307"/>
+      <c r="I107" s="307"/>
       <c r="K107" s="33"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -5333,12 +5369,12 @@
         <v>0</v>
       </c>
       <c r="C108" s="10"/>
-      <c r="D108" s="300"/>
-      <c r="E108" s="300"/>
-      <c r="F108" s="300"/>
-      <c r="G108" s="300"/>
-      <c r="H108" s="300"/>
-      <c r="I108" s="300"/>
+      <c r="D108" s="307"/>
+      <c r="E108" s="307"/>
+      <c r="F108" s="307"/>
+      <c r="G108" s="307"/>
+      <c r="H108" s="307"/>
+      <c r="I108" s="307"/>
       <c r="K108" s="39"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -5350,12 +5386,12 @@
         <v>94985.93</v>
       </c>
       <c r="C109" s="10"/>
-      <c r="D109" s="300"/>
-      <c r="E109" s="300"/>
-      <c r="F109" s="300"/>
-      <c r="G109" s="300"/>
-      <c r="H109" s="300"/>
-      <c r="I109" s="300"/>
+      <c r="D109" s="307"/>
+      <c r="E109" s="307"/>
+      <c r="F109" s="307"/>
+      <c r="G109" s="307"/>
+      <c r="H109" s="307"/>
+      <c r="I109" s="307"/>
       <c r="K109" s="39"/>
     </row>
     <row r="110" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5366,12 +5402,12 @@
         <v>46200</v>
       </c>
       <c r="C110" s="10"/>
-      <c r="D110" s="300"/>
-      <c r="E110" s="300"/>
-      <c r="F110" s="300"/>
-      <c r="G110" s="300"/>
-      <c r="H110" s="300"/>
-      <c r="I110" s="300"/>
+      <c r="D110" s="307"/>
+      <c r="E110" s="307"/>
+      <c r="F110" s="307"/>
+      <c r="G110" s="307"/>
+      <c r="H110" s="307"/>
+      <c r="I110" s="307"/>
       <c r="K110" s="39"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -5383,12 +5419,12 @@
         <v>-100000</v>
       </c>
       <c r="C111" s="14"/>
-      <c r="D111" s="300"/>
-      <c r="E111" s="300"/>
-      <c r="F111" s="300"/>
-      <c r="G111" s="300"/>
-      <c r="H111" s="300"/>
-      <c r="I111" s="300"/>
+      <c r="D111" s="307"/>
+      <c r="E111" s="307"/>
+      <c r="F111" s="307"/>
+      <c r="G111" s="307"/>
+      <c r="H111" s="307"/>
+      <c r="I111" s="307"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
@@ -5399,12 +5435,12 @@
         <v>-384244</v>
       </c>
       <c r="C112" s="14"/>
-      <c r="D112" s="300"/>
-      <c r="E112" s="300"/>
-      <c r="F112" s="300"/>
-      <c r="G112" s="300"/>
-      <c r="H112" s="300"/>
-      <c r="I112" s="300"/>
+      <c r="D112" s="307"/>
+      <c r="E112" s="307"/>
+      <c r="F112" s="307"/>
+      <c r="G112" s="307"/>
+      <c r="H112" s="307"/>
+      <c r="I112" s="307"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
@@ -5415,22 +5451,22 @@
         <v>-961359.12963389955</v>
       </c>
       <c r="C113" s="51"/>
-      <c r="D113" s="300"/>
-      <c r="E113" s="300"/>
-      <c r="F113" s="300"/>
-      <c r="G113" s="300"/>
-      <c r="H113" s="300"/>
-      <c r="I113" s="300"/>
+      <c r="D113" s="307"/>
+      <c r="E113" s="307"/>
+      <c r="F113" s="307"/>
+      <c r="G113" s="307"/>
+      <c r="H113" s="307"/>
+      <c r="I113" s="307"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="14"/>
       <c r="C114" s="10"/>
-      <c r="D114" s="300"/>
-      <c r="E114" s="300"/>
-      <c r="F114" s="300"/>
-      <c r="G114" s="300"/>
-      <c r="H114" s="300"/>
-      <c r="I114" s="300"/>
+      <c r="D114" s="307"/>
+      <c r="E114" s="307"/>
+      <c r="F114" s="307"/>
+      <c r="G114" s="307"/>
+      <c r="H114" s="307"/>
+      <c r="I114" s="307"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
@@ -5438,12 +5474,12 @@
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="10"/>
-      <c r="D115" s="300"/>
-      <c r="E115" s="300"/>
-      <c r="F115" s="300"/>
-      <c r="G115" s="300"/>
-      <c r="H115" s="300"/>
-      <c r="I115" s="300"/>
+      <c r="D115" s="307"/>
+      <c r="E115" s="307"/>
+      <c r="F115" s="307"/>
+      <c r="G115" s="307"/>
+      <c r="H115" s="307"/>
+      <c r="I115" s="307"/>
     </row>
     <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="196" t="s">
@@ -5485,14 +5521,14 @@
         <v>106182.28</v>
       </c>
       <c r="C120" s="10"/>
-      <c r="D120" s="323" t="s">
+      <c r="D120" s="328" t="s">
         <v>388</v>
       </c>
-      <c r="E120" s="324"/>
-      <c r="F120" s="324"/>
-      <c r="G120" s="324"/>
-      <c r="H120" s="324"/>
-      <c r="I120" s="325"/>
+      <c r="E120" s="329"/>
+      <c r="F120" s="329"/>
+      <c r="G120" s="329"/>
+      <c r="H120" s="329"/>
+      <c r="I120" s="330"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
@@ -5502,12 +5538,12 @@
         <v>-60000</v>
       </c>
       <c r="C121" s="10"/>
-      <c r="D121" s="326"/>
-      <c r="E121" s="327"/>
-      <c r="F121" s="327"/>
-      <c r="G121" s="327"/>
-      <c r="H121" s="327"/>
-      <c r="I121" s="328"/>
+      <c r="D121" s="331"/>
+      <c r="E121" s="332"/>
+      <c r="F121" s="332"/>
+      <c r="G121" s="332"/>
+      <c r="H121" s="332"/>
+      <c r="I121" s="333"/>
     </row>
     <row r="122" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="199" t="s">
@@ -5518,12 +5554,12 @@
         <v>-72000</v>
       </c>
       <c r="C122" s="10"/>
-      <c r="D122" s="326"/>
-      <c r="E122" s="327"/>
-      <c r="F122" s="327"/>
-      <c r="G122" s="327"/>
-      <c r="H122" s="327"/>
-      <c r="I122" s="328"/>
+      <c r="D122" s="331"/>
+      <c r="E122" s="332"/>
+      <c r="F122" s="332"/>
+      <c r="G122" s="332"/>
+      <c r="H122" s="332"/>
+      <c r="I122" s="333"/>
     </row>
     <row r="123" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="25" t="s">
@@ -5534,12 +5570,12 @@
         <v>-25817.72</v>
       </c>
       <c r="C123" s="10"/>
-      <c r="D123" s="329"/>
-      <c r="E123" s="330"/>
-      <c r="F123" s="330"/>
-      <c r="G123" s="330"/>
-      <c r="H123" s="330"/>
-      <c r="I123" s="331"/>
+      <c r="D123" s="334"/>
+      <c r="E123" s="335"/>
+      <c r="F123" s="335"/>
+      <c r="G123" s="335"/>
+      <c r="H123" s="335"/>
+      <c r="I123" s="336"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="14"/>
@@ -5566,15 +5602,15 @@
         <v>498840</v>
       </c>
       <c r="C128" s="16"/>
-      <c r="D128" s="301" t="s">
+      <c r="D128" s="308" t="s">
         <v>404</v>
       </c>
-      <c r="E128" s="302"/>
-      <c r="F128" s="302"/>
-      <c r="G128" s="302"/>
-      <c r="H128" s="302"/>
-      <c r="I128" s="302"/>
-      <c r="J128" s="303"/>
+      <c r="E128" s="309"/>
+      <c r="F128" s="309"/>
+      <c r="G128" s="309"/>
+      <c r="H128" s="309"/>
+      <c r="I128" s="309"/>
+      <c r="J128" s="310"/>
     </row>
     <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
@@ -5584,13 +5620,13 @@
         <v>100000</v>
       </c>
       <c r="C129" s="16"/>
-      <c r="D129" s="304"/>
-      <c r="E129" s="305"/>
-      <c r="F129" s="305"/>
-      <c r="G129" s="305"/>
-      <c r="H129" s="305"/>
-      <c r="I129" s="305"/>
-      <c r="J129" s="306"/>
+      <c r="D129" s="311"/>
+      <c r="E129" s="312"/>
+      <c r="F129" s="312"/>
+      <c r="G129" s="312"/>
+      <c r="H129" s="312"/>
+      <c r="I129" s="312"/>
+      <c r="J129" s="313"/>
     </row>
     <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11"/>
@@ -5598,13 +5634,13 @@
         <v>0</v>
       </c>
       <c r="C130" s="16"/>
-      <c r="D130" s="304"/>
-      <c r="E130" s="305"/>
-      <c r="F130" s="305"/>
-      <c r="G130" s="305"/>
-      <c r="H130" s="305"/>
-      <c r="I130" s="305"/>
-      <c r="J130" s="306"/>
+      <c r="D130" s="311"/>
+      <c r="E130" s="312"/>
+      <c r="F130" s="312"/>
+      <c r="G130" s="312"/>
+      <c r="H130" s="312"/>
+      <c r="I130" s="312"/>
+      <c r="J130" s="313"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="25" t="s">
@@ -5615,51 +5651,51 @@
         <v>598840</v>
       </c>
       <c r="C131" s="16"/>
-      <c r="D131" s="304"/>
-      <c r="E131" s="305"/>
-      <c r="F131" s="305"/>
-      <c r="G131" s="305"/>
-      <c r="H131" s="305"/>
-      <c r="I131" s="305"/>
-      <c r="J131" s="306"/>
+      <c r="D131" s="311"/>
+      <c r="E131" s="312"/>
+      <c r="F131" s="312"/>
+      <c r="G131" s="312"/>
+      <c r="H131" s="312"/>
+      <c r="I131" s="312"/>
+      <c r="J131" s="313"/>
     </row>
     <row r="132" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C132" s="17"/>
-      <c r="D132" s="304"/>
-      <c r="E132" s="305"/>
-      <c r="F132" s="305"/>
-      <c r="G132" s="305"/>
-      <c r="H132" s="305"/>
-      <c r="I132" s="305"/>
-      <c r="J132" s="306"/>
+      <c r="D132" s="311"/>
+      <c r="E132" s="312"/>
+      <c r="F132" s="312"/>
+      <c r="G132" s="312"/>
+      <c r="H132" s="312"/>
+      <c r="I132" s="312"/>
+      <c r="J132" s="313"/>
     </row>
     <row r="133" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="312" t="s">
+      <c r="A133" s="317" t="s">
         <v>361</v>
       </c>
-      <c r="B133" s="314">
+      <c r="B133" s="319">
         <f>B131+B113+B123</f>
         <v>-388336.84963389952</v>
       </c>
       <c r="C133" s="10"/>
-      <c r="D133" s="304"/>
-      <c r="E133" s="305"/>
-      <c r="F133" s="305"/>
-      <c r="G133" s="305"/>
-      <c r="H133" s="305"/>
-      <c r="I133" s="305"/>
-      <c r="J133" s="306"/>
+      <c r="D133" s="311"/>
+      <c r="E133" s="312"/>
+      <c r="F133" s="312"/>
+      <c r="G133" s="312"/>
+      <c r="H133" s="312"/>
+      <c r="I133" s="312"/>
+      <c r="J133" s="313"/>
     </row>
     <row r="134" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="313"/>
-      <c r="B134" s="315"/>
-      <c r="D134" s="307"/>
-      <c r="E134" s="308"/>
-      <c r="F134" s="308"/>
-      <c r="G134" s="308"/>
-      <c r="H134" s="308"/>
-      <c r="I134" s="308"/>
-      <c r="J134" s="309"/>
+      <c r="A134" s="318"/>
+      <c r="B134" s="320"/>
+      <c r="D134" s="314"/>
+      <c r="E134" s="315"/>
+      <c r="F134" s="315"/>
+      <c r="G134" s="315"/>
+      <c r="H134" s="315"/>
+      <c r="I134" s="315"/>
+      <c r="J134" s="316"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D140" s="53"/>
@@ -5686,13 +5722,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="D100:I115"/>
     <mergeCell ref="D128:J134"/>
@@ -5703,6 +5732,13 @@
     <mergeCell ref="A93:D93"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="D120:I123"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5737,13 +5773,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="371" t="s">
+      <c r="A1" s="367" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="372"/>
-      <c r="C1" s="372"/>
-      <c r="D1" s="372"/>
-      <c r="E1" s="372"/>
+      <c r="B1" s="368"/>
+      <c r="C1" s="368"/>
+      <c r="D1" s="368"/>
+      <c r="E1" s="368"/>
       <c r="F1" s="120" t="s">
         <v>276</v>
       </c>
@@ -5755,20 +5791,20 @@
       <c r="L1" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="349">
+      <c r="M1" s="342">
         <f>RESUMEN!D83-N3</f>
         <v>17532713.560000002</v>
       </c>
-      <c r="N1" s="350"/>
+      <c r="N1" s="343"/>
       <c r="O1" s="121"/>
       <c r="P1" s="45"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="373"/>
-      <c r="B2" s="374"/>
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="374"/>
+      <c r="A2" s="369"/>
+      <c r="B2" s="370"/>
+      <c r="C2" s="370"/>
+      <c r="D2" s="370"/>
+      <c r="E2" s="370"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5788,11 +5824,11 @@
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="373"/>
-      <c r="B3" s="374"/>
-      <c r="C3" s="374"/>
-      <c r="D3" s="374"/>
-      <c r="E3" s="374"/>
+      <c r="A3" s="369"/>
+      <c r="B3" s="370"/>
+      <c r="C3" s="370"/>
+      <c r="D3" s="370"/>
+      <c r="E3" s="370"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5812,11 +5848,11 @@
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="375"/>
-      <c r="B4" s="376"/>
-      <c r="C4" s="376"/>
-      <c r="D4" s="376"/>
-      <c r="E4" s="376"/>
+      <c r="A4" s="371"/>
+      <c r="B4" s="372"/>
+      <c r="C4" s="372"/>
+      <c r="D4" s="372"/>
+      <c r="E4" s="372"/>
       <c r="F4" s="125"/>
       <c r="G4" s="125"/>
       <c r="H4" s="125"/>
@@ -5832,95 +5868,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="356" t="s">
+      <c r="C5" s="352" t="s">
         <v>385</v>
       </c>
-      <c r="D5" s="357"/>
-      <c r="E5" s="357"/>
-      <c r="F5" s="357"/>
-      <c r="G5" s="357"/>
-      <c r="H5" s="357"/>
-      <c r="I5" s="357"/>
-      <c r="J5" s="357"/>
-      <c r="K5" s="357"/>
-      <c r="L5" s="357"/>
-      <c r="M5" s="357"/>
-      <c r="N5" s="357"/>
-      <c r="O5" s="358"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="353"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="353"/>
+      <c r="L5" s="353"/>
+      <c r="M5" s="353"/>
+      <c r="N5" s="353"/>
+      <c r="O5" s="354"/>
       <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="359"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="360"/>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
-      <c r="H6" s="360"/>
-      <c r="I6" s="360"/>
-      <c r="J6" s="360"/>
-      <c r="K6" s="360"/>
-      <c r="L6" s="360"/>
-      <c r="M6" s="360"/>
-      <c r="N6" s="360"/>
-      <c r="O6" s="361"/>
+      <c r="C6" s="355"/>
+      <c r="D6" s="356"/>
+      <c r="E6" s="356"/>
+      <c r="F6" s="356"/>
+      <c r="G6" s="356"/>
+      <c r="H6" s="356"/>
+      <c r="I6" s="356"/>
+      <c r="J6" s="356"/>
+      <c r="K6" s="356"/>
+      <c r="L6" s="356"/>
+      <c r="M6" s="356"/>
+      <c r="N6" s="356"/>
+      <c r="O6" s="357"/>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="359"/>
-      <c r="D7" s="360"/>
-      <c r="E7" s="360"/>
-      <c r="F7" s="360"/>
-      <c r="G7" s="360"/>
-      <c r="H7" s="360"/>
-      <c r="I7" s="360"/>
-      <c r="J7" s="360"/>
-      <c r="K7" s="360"/>
-      <c r="L7" s="360"/>
-      <c r="M7" s="360"/>
-      <c r="N7" s="360"/>
-      <c r="O7" s="361"/>
+      <c r="C7" s="355"/>
+      <c r="D7" s="356"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
+      <c r="G7" s="356"/>
+      <c r="H7" s="356"/>
+      <c r="I7" s="356"/>
+      <c r="J7" s="356"/>
+      <c r="K7" s="356"/>
+      <c r="L7" s="356"/>
+      <c r="M7" s="356"/>
+      <c r="N7" s="356"/>
+      <c r="O7" s="357"/>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="362"/>
-      <c r="D8" s="363"/>
-      <c r="E8" s="363"/>
-      <c r="F8" s="363"/>
-      <c r="G8" s="363"/>
-      <c r="H8" s="363"/>
-      <c r="I8" s="363"/>
-      <c r="J8" s="363"/>
-      <c r="K8" s="363"/>
-      <c r="L8" s="363"/>
-      <c r="M8" s="363"/>
-      <c r="N8" s="363"/>
-      <c r="O8" s="364"/>
+      <c r="C8" s="358"/>
+      <c r="D8" s="359"/>
+      <c r="E8" s="359"/>
+      <c r="F8" s="359"/>
+      <c r="G8" s="359"/>
+      <c r="H8" s="359"/>
+      <c r="I8" s="359"/>
+      <c r="J8" s="359"/>
+      <c r="K8" s="359"/>
+      <c r="L8" s="359"/>
+      <c r="M8" s="359"/>
+      <c r="N8" s="359"/>
+      <c r="O8" s="360"/>
       <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="365" t="s">
+      <c r="C9" s="361" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="366"/>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
-      <c r="G9" s="366"/>
-      <c r="H9" s="366"/>
-      <c r="I9" s="366"/>
-      <c r="J9" s="366"/>
-      <c r="K9" s="366"/>
-      <c r="L9" s="366"/>
-      <c r="M9" s="366"/>
-      <c r="N9" s="366"/>
-      <c r="O9" s="367"/>
+      <c r="D9" s="362"/>
+      <c r="E9" s="362"/>
+      <c r="F9" s="362"/>
+      <c r="G9" s="362"/>
+      <c r="H9" s="362"/>
+      <c r="I9" s="362"/>
+      <c r="J9" s="362"/>
+      <c r="K9" s="362"/>
+      <c r="L9" s="362"/>
+      <c r="M9" s="362"/>
+      <c r="N9" s="362"/>
+      <c r="O9" s="363"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -5932,19 +5968,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="368"/>
-      <c r="D10" s="369"/>
-      <c r="E10" s="369"/>
-      <c r="F10" s="369"/>
-      <c r="G10" s="369"/>
-      <c r="H10" s="369"/>
-      <c r="I10" s="369"/>
-      <c r="J10" s="369"/>
-      <c r="K10" s="369"/>
-      <c r="L10" s="369"/>
-      <c r="M10" s="369"/>
-      <c r="N10" s="369"/>
-      <c r="O10" s="370"/>
+      <c r="C10" s="364"/>
+      <c r="D10" s="365"/>
+      <c r="E10" s="365"/>
+      <c r="F10" s="365"/>
+      <c r="G10" s="365"/>
+      <c r="H10" s="365"/>
+      <c r="I10" s="365"/>
+      <c r="J10" s="365"/>
+      <c r="K10" s="365"/>
+      <c r="L10" s="365"/>
+      <c r="M10" s="365"/>
+      <c r="N10" s="365"/>
+      <c r="O10" s="366"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -5954,49 +5990,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="340" t="s">
+      <c r="A11" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="342" t="s">
+      <c r="B11" s="373" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="340" t="s">
+      <c r="C11" s="338" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="344" t="s">
+      <c r="D11" s="375" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="344" t="s">
+      <c r="E11" s="375" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="340" t="s">
+      <c r="F11" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="340" t="s">
+      <c r="G11" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="340" t="s">
+      <c r="H11" s="338" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="351" t="s">
+      <c r="I11" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="337" t="s">
+      <c r="J11" s="346" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="337" t="s">
+      <c r="K11" s="346" t="s">
         <v>371</v>
       </c>
-      <c r="L11" s="337" t="s">
+      <c r="L11" s="346" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="353" t="s">
+      <c r="M11" s="349" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="337" t="s">
+      <c r="N11" s="346" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="337" t="s">
+      <c r="O11" s="346" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -6008,21 +6044,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="341"/>
-      <c r="B12" s="343"/>
-      <c r="C12" s="341"/>
-      <c r="D12" s="345"/>
-      <c r="E12" s="345"/>
-      <c r="F12" s="341"/>
-      <c r="G12" s="341"/>
-      <c r="H12" s="341"/>
-      <c r="I12" s="352"/>
-      <c r="J12" s="338"/>
-      <c r="K12" s="338"/>
-      <c r="L12" s="338"/>
-      <c r="M12" s="354"/>
-      <c r="N12" s="338"/>
-      <c r="O12" s="338"/>
+      <c r="A12" s="339"/>
+      <c r="B12" s="374"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="376"/>
+      <c r="E12" s="376"/>
+      <c r="F12" s="339"/>
+      <c r="G12" s="339"/>
+      <c r="H12" s="339"/>
+      <c r="I12" s="345"/>
+      <c r="J12" s="347"/>
+      <c r="K12" s="347"/>
+      <c r="L12" s="347"/>
+      <c r="M12" s="350"/>
+      <c r="N12" s="347"/>
+      <c r="O12" s="347"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -6032,19 +6068,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="341"/>
-      <c r="B13" s="343"/>
-      <c r="C13" s="341"/>
-      <c r="D13" s="345"/>
-      <c r="E13" s="345"/>
-      <c r="F13" s="341"/>
-      <c r="G13" s="341"/>
-      <c r="H13" s="341"/>
-      <c r="I13" s="352"/>
-      <c r="J13" s="338"/>
-      <c r="K13" s="339"/>
-      <c r="L13" s="339"/>
-      <c r="M13" s="354"/>
+      <c r="A13" s="339"/>
+      <c r="B13" s="374"/>
+      <c r="C13" s="339"/>
+      <c r="D13" s="376"/>
+      <c r="E13" s="376"/>
+      <c r="F13" s="339"/>
+      <c r="G13" s="339"/>
+      <c r="H13" s="339"/>
+      <c r="I13" s="345"/>
+      <c r="J13" s="347"/>
+      <c r="K13" s="348"/>
+      <c r="L13" s="348"/>
+      <c r="M13" s="350"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/08</v>
@@ -6113,8 +6149,8 @@
       <c r="P14" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="R14" s="346"/>
-      <c r="S14" s="346"/>
+      <c r="R14" s="337"/>
+      <c r="S14" s="337"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
@@ -6163,8 +6199,8 @@
       <c r="P15" s="85" t="s">
         <v>346</v>
       </c>
-      <c r="R15" s="346"/>
-      <c r="S15" s="346"/>
+      <c r="R15" s="337"/>
+      <c r="S15" s="337"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -12840,34 +12876,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="348"/>
-      <c r="D135" s="348"/>
-      <c r="E135" s="348"/>
-      <c r="F135" s="348"/>
-      <c r="G135" s="348"/>
-      <c r="H135" s="348"/>
-      <c r="I135" s="348"/>
-      <c r="J135" s="348"/>
-      <c r="K135" s="348"/>
-      <c r="L135" s="348"/>
-      <c r="M135" s="348"/>
-      <c r="N135" s="348"/>
-      <c r="O135" s="348"/>
+      <c r="C135" s="341"/>
+      <c r="D135" s="341"/>
+      <c r="E135" s="341"/>
+      <c r="F135" s="341"/>
+      <c r="G135" s="341"/>
+      <c r="H135" s="341"/>
+      <c r="I135" s="341"/>
+      <c r="J135" s="341"/>
+      <c r="K135" s="341"/>
+      <c r="L135" s="341"/>
+      <c r="M135" s="341"/>
+      <c r="N135" s="341"/>
+      <c r="O135" s="341"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="348"/>
-      <c r="D136" s="348"/>
-      <c r="E136" s="348"/>
-      <c r="F136" s="348"/>
-      <c r="G136" s="348"/>
-      <c r="H136" s="348"/>
-      <c r="I136" s="348"/>
-      <c r="J136" s="348"/>
-      <c r="K136" s="348"/>
-      <c r="L136" s="348"/>
-      <c r="M136" s="348"/>
-      <c r="N136" s="348"/>
-      <c r="O136" s="348"/>
+      <c r="C136" s="341"/>
+      <c r="D136" s="341"/>
+      <c r="E136" s="341"/>
+      <c r="F136" s="341"/>
+      <c r="G136" s="341"/>
+      <c r="H136" s="341"/>
+      <c r="I136" s="341"/>
+      <c r="J136" s="341"/>
+      <c r="K136" s="341"/>
+      <c r="L136" s="341"/>
+      <c r="M136" s="341"/>
+      <c r="N136" s="341"/>
+      <c r="O136" s="341"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
@@ -12885,126 +12921,126 @@
       <c r="O137" s="57"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="355" t="s">
+      <c r="C138" s="351" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
-      <c r="G138" s="355"/>
-      <c r="H138" s="355"/>
-      <c r="I138" s="355"/>
-      <c r="J138" s="355"/>
-      <c r="K138" s="355"/>
-      <c r="L138" s="355"/>
-      <c r="M138" s="355"/>
-      <c r="N138" s="355"/>
-      <c r="O138" s="355"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
+      <c r="G138" s="351"/>
+      <c r="H138" s="351"/>
+      <c r="I138" s="351"/>
+      <c r="J138" s="351"/>
+      <c r="K138" s="351"/>
+      <c r="L138" s="351"/>
+      <c r="M138" s="351"/>
+      <c r="N138" s="351"/>
+      <c r="O138" s="351"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="355"/>
-      <c r="D139" s="355"/>
-      <c r="E139" s="355"/>
-      <c r="F139" s="355"/>
-      <c r="G139" s="355"/>
-      <c r="H139" s="355"/>
-      <c r="I139" s="355"/>
-      <c r="J139" s="355"/>
-      <c r="K139" s="355"/>
-      <c r="L139" s="355"/>
-      <c r="M139" s="355"/>
-      <c r="N139" s="355"/>
-      <c r="O139" s="355"/>
+      <c r="C139" s="351"/>
+      <c r="D139" s="351"/>
+      <c r="E139" s="351"/>
+      <c r="F139" s="351"/>
+      <c r="G139" s="351"/>
+      <c r="H139" s="351"/>
+      <c r="I139" s="351"/>
+      <c r="J139" s="351"/>
+      <c r="K139" s="351"/>
+      <c r="L139" s="351"/>
+      <c r="M139" s="351"/>
+      <c r="N139" s="351"/>
+      <c r="O139" s="351"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="355"/>
-      <c r="D140" s="355"/>
-      <c r="E140" s="355"/>
-      <c r="F140" s="355"/>
-      <c r="G140" s="355"/>
-      <c r="H140" s="355"/>
-      <c r="I140" s="355"/>
-      <c r="J140" s="355"/>
-      <c r="K140" s="355"/>
-      <c r="L140" s="355"/>
-      <c r="M140" s="355"/>
-      <c r="N140" s="355"/>
-      <c r="O140" s="355"/>
+      <c r="C140" s="351"/>
+      <c r="D140" s="351"/>
+      <c r="E140" s="351"/>
+      <c r="F140" s="351"/>
+      <c r="G140" s="351"/>
+      <c r="H140" s="351"/>
+      <c r="I140" s="351"/>
+      <c r="J140" s="351"/>
+      <c r="K140" s="351"/>
+      <c r="L140" s="351"/>
+      <c r="M140" s="351"/>
+      <c r="N140" s="351"/>
+      <c r="O140" s="351"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="355"/>
-      <c r="D141" s="355"/>
-      <c r="E141" s="355"/>
-      <c r="F141" s="355"/>
-      <c r="G141" s="355"/>
-      <c r="H141" s="355"/>
-      <c r="I141" s="355"/>
-      <c r="J141" s="355"/>
-      <c r="K141" s="355"/>
-      <c r="L141" s="355"/>
-      <c r="M141" s="355"/>
-      <c r="N141" s="355"/>
-      <c r="O141" s="355"/>
+      <c r="C141" s="351"/>
+      <c r="D141" s="351"/>
+      <c r="E141" s="351"/>
+      <c r="F141" s="351"/>
+      <c r="G141" s="351"/>
+      <c r="H141" s="351"/>
+      <c r="I141" s="351"/>
+      <c r="J141" s="351"/>
+      <c r="K141" s="351"/>
+      <c r="L141" s="351"/>
+      <c r="M141" s="351"/>
+      <c r="N141" s="351"/>
+      <c r="O141" s="351"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="355"/>
-      <c r="D142" s="355"/>
-      <c r="E142" s="355"/>
-      <c r="F142" s="355"/>
-      <c r="G142" s="355"/>
-      <c r="H142" s="355"/>
-      <c r="I142" s="355"/>
-      <c r="J142" s="355"/>
-      <c r="K142" s="355"/>
-      <c r="L142" s="355"/>
-      <c r="M142" s="355"/>
-      <c r="N142" s="355"/>
-      <c r="O142" s="355"/>
+      <c r="C142" s="351"/>
+      <c r="D142" s="351"/>
+      <c r="E142" s="351"/>
+      <c r="F142" s="351"/>
+      <c r="G142" s="351"/>
+      <c r="H142" s="351"/>
+      <c r="I142" s="351"/>
+      <c r="J142" s="351"/>
+      <c r="K142" s="351"/>
+      <c r="L142" s="351"/>
+      <c r="M142" s="351"/>
+      <c r="N142" s="351"/>
+      <c r="O142" s="351"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="355"/>
-      <c r="D143" s="355"/>
-      <c r="E143" s="355"/>
-      <c r="F143" s="355"/>
-      <c r="G143" s="355"/>
-      <c r="H143" s="355"/>
-      <c r="I143" s="355"/>
-      <c r="J143" s="355"/>
-      <c r="K143" s="355"/>
-      <c r="L143" s="355"/>
-      <c r="M143" s="355"/>
-      <c r="N143" s="355"/>
-      <c r="O143" s="355"/>
+      <c r="C143" s="351"/>
+      <c r="D143" s="351"/>
+      <c r="E143" s="351"/>
+      <c r="F143" s="351"/>
+      <c r="G143" s="351"/>
+      <c r="H143" s="351"/>
+      <c r="I143" s="351"/>
+      <c r="J143" s="351"/>
+      <c r="K143" s="351"/>
+      <c r="L143" s="351"/>
+      <c r="M143" s="351"/>
+      <c r="N143" s="351"/>
+      <c r="O143" s="351"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="355"/>
-      <c r="D144" s="355"/>
-      <c r="E144" s="355"/>
-      <c r="F144" s="355"/>
-      <c r="G144" s="355"/>
-      <c r="H144" s="355"/>
-      <c r="I144" s="355"/>
-      <c r="J144" s="355"/>
-      <c r="K144" s="355"/>
-      <c r="L144" s="355"/>
-      <c r="M144" s="355"/>
-      <c r="N144" s="355"/>
-      <c r="O144" s="355"/>
+      <c r="C144" s="351"/>
+      <c r="D144" s="351"/>
+      <c r="E144" s="351"/>
+      <c r="F144" s="351"/>
+      <c r="G144" s="351"/>
+      <c r="H144" s="351"/>
+      <c r="I144" s="351"/>
+      <c r="J144" s="351"/>
+      <c r="K144" s="351"/>
+      <c r="L144" s="351"/>
+      <c r="M144" s="351"/>
+      <c r="N144" s="351"/>
+      <c r="O144" s="351"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="355"/>
-      <c r="D145" s="355"/>
-      <c r="E145" s="355"/>
-      <c r="F145" s="355"/>
-      <c r="G145" s="355"/>
-      <c r="H145" s="355"/>
-      <c r="I145" s="355"/>
-      <c r="J145" s="355"/>
-      <c r="K145" s="355"/>
-      <c r="L145" s="355"/>
-      <c r="M145" s="355"/>
-      <c r="N145" s="355"/>
-      <c r="O145" s="355"/>
+      <c r="C145" s="351"/>
+      <c r="D145" s="351"/>
+      <c r="E145" s="351"/>
+      <c r="F145" s="351"/>
+      <c r="G145" s="351"/>
+      <c r="H145" s="351"/>
+      <c r="I145" s="351"/>
+      <c r="J145" s="351"/>
+      <c r="K145" s="351"/>
+      <c r="L145" s="351"/>
+      <c r="M145" s="351"/>
+      <c r="N145" s="351"/>
+      <c r="O145" s="351"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
@@ -13037,118 +13073,125 @@
       <c r="O147" s="57"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="347" t="s">
+      <c r="C148" s="340" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="347"/>
-      <c r="E148" s="347"/>
-      <c r="F148" s="347"/>
-      <c r="G148" s="347"/>
-      <c r="H148" s="347"/>
-      <c r="I148" s="347"/>
-      <c r="J148" s="347"/>
-      <c r="K148" s="347"/>
-      <c r="L148" s="347"/>
-      <c r="M148" s="347"/>
-      <c r="N148" s="347"/>
-      <c r="O148" s="347"/>
+      <c r="D148" s="340"/>
+      <c r="E148" s="340"/>
+      <c r="F148" s="340"/>
+      <c r="G148" s="340"/>
+      <c r="H148" s="340"/>
+      <c r="I148" s="340"/>
+      <c r="J148" s="340"/>
+      <c r="K148" s="340"/>
+      <c r="L148" s="340"/>
+      <c r="M148" s="340"/>
+      <c r="N148" s="340"/>
+      <c r="O148" s="340"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="347"/>
-      <c r="D149" s="347"/>
-      <c r="E149" s="347"/>
-      <c r="F149" s="347"/>
-      <c r="G149" s="347"/>
-      <c r="H149" s="347"/>
-      <c r="I149" s="347"/>
-      <c r="J149" s="347"/>
-      <c r="K149" s="347"/>
-      <c r="L149" s="347"/>
-      <c r="M149" s="347"/>
-      <c r="N149" s="347"/>
-      <c r="O149" s="347"/>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+      <c r="G149" s="340"/>
+      <c r="H149" s="340"/>
+      <c r="I149" s="340"/>
+      <c r="J149" s="340"/>
+      <c r="K149" s="340"/>
+      <c r="L149" s="340"/>
+      <c r="M149" s="340"/>
+      <c r="N149" s="340"/>
+      <c r="O149" s="340"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="347"/>
-      <c r="D150" s="347"/>
-      <c r="E150" s="347"/>
-      <c r="F150" s="347"/>
-      <c r="G150" s="347"/>
-      <c r="H150" s="347"/>
-      <c r="I150" s="347"/>
-      <c r="J150" s="347"/>
-      <c r="K150" s="347"/>
-      <c r="L150" s="347"/>
-      <c r="M150" s="347"/>
-      <c r="N150" s="347"/>
-      <c r="O150" s="347"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+      <c r="G150" s="340"/>
+      <c r="H150" s="340"/>
+      <c r="I150" s="340"/>
+      <c r="J150" s="340"/>
+      <c r="K150" s="340"/>
+      <c r="L150" s="340"/>
+      <c r="M150" s="340"/>
+      <c r="N150" s="340"/>
+      <c r="O150" s="340"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>3002976.0931200404</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="347"/>
-      <c r="D151" s="347"/>
-      <c r="E151" s="347"/>
-      <c r="F151" s="347"/>
-      <c r="G151" s="347"/>
-      <c r="H151" s="347"/>
-      <c r="I151" s="347"/>
-      <c r="J151" s="347"/>
-      <c r="K151" s="347"/>
-      <c r="L151" s="347"/>
-      <c r="M151" s="347"/>
-      <c r="N151" s="347"/>
-      <c r="O151" s="347"/>
+      <c r="C151" s="340"/>
+      <c r="D151" s="340"/>
+      <c r="E151" s="340"/>
+      <c r="F151" s="340"/>
+      <c r="G151" s="340"/>
+      <c r="H151" s="340"/>
+      <c r="I151" s="340"/>
+      <c r="J151" s="340"/>
+      <c r="K151" s="340"/>
+      <c r="L151" s="340"/>
+      <c r="M151" s="340"/>
+      <c r="N151" s="340"/>
+      <c r="O151" s="340"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="347"/>
-      <c r="D152" s="347"/>
-      <c r="E152" s="347"/>
-      <c r="F152" s="347"/>
-      <c r="G152" s="347"/>
-      <c r="H152" s="347"/>
-      <c r="I152" s="347"/>
-      <c r="J152" s="347"/>
-      <c r="K152" s="347"/>
-      <c r="L152" s="347"/>
-      <c r="M152" s="347"/>
-      <c r="N152" s="347"/>
-      <c r="O152" s="347"/>
+      <c r="C152" s="340"/>
+      <c r="D152" s="340"/>
+      <c r="E152" s="340"/>
+      <c r="F152" s="340"/>
+      <c r="G152" s="340"/>
+      <c r="H152" s="340"/>
+      <c r="I152" s="340"/>
+      <c r="J152" s="340"/>
+      <c r="K152" s="340"/>
+      <c r="L152" s="340"/>
+      <c r="M152" s="340"/>
+      <c r="N152" s="340"/>
+      <c r="O152" s="340"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="347"/>
-      <c r="D153" s="347"/>
-      <c r="E153" s="347"/>
-      <c r="F153" s="347"/>
-      <c r="G153" s="347"/>
-      <c r="H153" s="347"/>
-      <c r="I153" s="347"/>
-      <c r="J153" s="347"/>
-      <c r="K153" s="347"/>
-      <c r="L153" s="347"/>
-      <c r="M153" s="347"/>
-      <c r="N153" s="347"/>
-      <c r="O153" s="347"/>
+      <c r="C153" s="340"/>
+      <c r="D153" s="340"/>
+      <c r="E153" s="340"/>
+      <c r="F153" s="340"/>
+      <c r="G153" s="340"/>
+      <c r="H153" s="340"/>
+      <c r="I153" s="340"/>
+      <c r="J153" s="340"/>
+      <c r="K153" s="340"/>
+      <c r="L153" s="340"/>
+      <c r="M153" s="340"/>
+      <c r="N153" s="340"/>
+      <c r="O153" s="340"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="347"/>
-      <c r="D154" s="347"/>
-      <c r="E154" s="347"/>
-      <c r="F154" s="347"/>
-      <c r="G154" s="347"/>
-      <c r="H154" s="347"/>
-      <c r="I154" s="347"/>
-      <c r="J154" s="347"/>
-      <c r="K154" s="347"/>
-      <c r="L154" s="347"/>
-      <c r="M154" s="347"/>
-      <c r="N154" s="347"/>
-      <c r="O154" s="347"/>
+      <c r="C154" s="340"/>
+      <c r="D154" s="340"/>
+      <c r="E154" s="340"/>
+      <c r="F154" s="340"/>
+      <c r="G154" s="340"/>
+      <c r="H154" s="340"/>
+      <c r="I154" s="340"/>
+      <c r="J154" s="340"/>
+      <c r="K154" s="340"/>
+      <c r="L154" s="340"/>
+      <c r="M154" s="340"/>
+      <c r="N154" s="340"/>
+      <c r="O154" s="340"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13165,13 +13208,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13205,61 +13241,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="381" t="s">
+      <c r="A1" s="384" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="381"/>
-      <c r="C1" s="381"/>
-      <c r="D1" s="381"/>
-      <c r="E1" s="381"/>
-      <c r="F1" s="381"/>
-      <c r="G1" s="381"/>
-      <c r="H1" s="381"/>
-      <c r="I1" s="381"/>
-      <c r="J1" s="381"/>
-      <c r="K1" s="381"/>
-      <c r="L1" s="381"/>
-      <c r="M1" s="381"/>
-      <c r="N1" s="381"/>
-      <c r="O1" s="382"/>
+      <c r="B1" s="384"/>
+      <c r="C1" s="384"/>
+      <c r="D1" s="384"/>
+      <c r="E1" s="384"/>
+      <c r="F1" s="384"/>
+      <c r="G1" s="384"/>
+      <c r="H1" s="384"/>
+      <c r="I1" s="384"/>
+      <c r="J1" s="384"/>
+      <c r="K1" s="384"/>
+      <c r="L1" s="384"/>
+      <c r="M1" s="384"/>
+      <c r="N1" s="384"/>
+      <c r="O1" s="385"/>
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="383"/>
-      <c r="B2" s="383"/>
-      <c r="C2" s="383"/>
-      <c r="D2" s="383"/>
-      <c r="E2" s="383"/>
-      <c r="F2" s="383"/>
-      <c r="G2" s="383"/>
-      <c r="H2" s="383"/>
-      <c r="I2" s="383"/>
-      <c r="J2" s="383"/>
-      <c r="K2" s="383"/>
-      <c r="L2" s="383"/>
-      <c r="M2" s="383"/>
-      <c r="N2" s="383"/>
-      <c r="O2" s="384"/>
+      <c r="A2" s="386"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
+      <c r="G2" s="386"/>
+      <c r="H2" s="386"/>
+      <c r="I2" s="386"/>
+      <c r="J2" s="386"/>
+      <c r="K2" s="386"/>
+      <c r="L2" s="386"/>
+      <c r="M2" s="386"/>
+      <c r="N2" s="386"/>
+      <c r="O2" s="387"/>
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="381" t="s">
         <v>363</v>
       </c>
-      <c r="B3" s="379"/>
-      <c r="C3" s="379"/>
-      <c r="D3" s="379"/>
-      <c r="E3" s="379"/>
-      <c r="F3" s="379"/>
-      <c r="G3" s="379"/>
-      <c r="H3" s="379"/>
-      <c r="I3" s="379"/>
-      <c r="J3" s="379"/>
-      <c r="K3" s="379"/>
-      <c r="L3" s="379"/>
-      <c r="M3" s="379"/>
-      <c r="N3" s="379"/>
-      <c r="O3" s="380"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
+      <c r="L3" s="382"/>
+      <c r="M3" s="382"/>
+      <c r="N3" s="382"/>
+      <c r="O3" s="383"/>
       <c r="P3" s="185"/>
       <c r="Q3" s="185"/>
       <c r="R3" s="185"/>
@@ -13274,85 +13310,85 @@
       <c r="AA3" s="185"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="340" t="s">
+      <c r="A4" s="338" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="340" t="s">
+      <c r="B4" s="338" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="340" t="s">
+      <c r="C4" s="338" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="340" t="s">
+      <c r="D4" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="337" t="s">
+      <c r="E4" s="346" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="337" t="s">
+      <c r="F4" s="346" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="337" t="s">
+      <c r="G4" s="346" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="337" t="s">
+      <c r="H4" s="346" t="s">
         <v>336</v>
       </c>
-      <c r="I4" s="337" t="s">
+      <c r="I4" s="346" t="s">
         <v>344</v>
       </c>
-      <c r="J4" s="385" t="s">
+      <c r="J4" s="388" t="s">
         <v>332</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="389" t="s">
+      <c r="L4" s="377" t="s">
         <v>341</v>
       </c>
-      <c r="M4" s="337" t="s">
+      <c r="M4" s="346" t="s">
         <v>342</v>
       </c>
-      <c r="N4" s="337" t="s">
+      <c r="N4" s="346" t="s">
         <v>333</v>
       </c>
-      <c r="O4" s="337" t="s">
+      <c r="O4" s="346" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="341"/>
-      <c r="B5" s="341"/>
-      <c r="C5" s="341"/>
-      <c r="D5" s="341"/>
-      <c r="E5" s="338"/>
-      <c r="F5" s="338"/>
-      <c r="G5" s="338"/>
-      <c r="H5" s="338"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="386"/>
+      <c r="A5" s="339"/>
+      <c r="B5" s="339"/>
+      <c r="C5" s="339"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="347"/>
+      <c r="F5" s="347"/>
+      <c r="G5" s="347"/>
+      <c r="H5" s="347"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="389"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="390"/>
-      <c r="M5" s="338"/>
-      <c r="N5" s="338"/>
-      <c r="O5" s="338"/>
+      <c r="L5" s="378"/>
+      <c r="M5" s="347"/>
+      <c r="N5" s="347"/>
+      <c r="O5" s="347"/>
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="388"/>
-      <c r="B6" s="388"/>
-      <c r="C6" s="388"/>
-      <c r="D6" s="388"/>
-      <c r="E6" s="377"/>
-      <c r="F6" s="377"/>
-      <c r="G6" s="377"/>
-      <c r="H6" s="377"/>
-      <c r="I6" s="377"/>
-      <c r="J6" s="387"/>
+      <c r="A6" s="391"/>
+      <c r="B6" s="391"/>
+      <c r="C6" s="391"/>
+      <c r="D6" s="391"/>
+      <c r="E6" s="380"/>
+      <c r="F6" s="380"/>
+      <c r="G6" s="380"/>
+      <c r="H6" s="380"/>
+      <c r="I6" s="380"/>
+      <c r="J6" s="390"/>
       <c r="K6" s="154"/>
-      <c r="L6" s="391"/>
-      <c r="M6" s="377"/>
-      <c r="N6" s="377"/>
-      <c r="O6" s="377"/>
+      <c r="L6" s="379"/>
+      <c r="M6" s="380"/>
+      <c r="N6" s="380"/>
+      <c r="O6" s="380"/>
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13407,8 +13443,8 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="346"/>
-      <c r="S7" s="346"/>
+      <c r="R7" s="337"/>
+      <c r="S7" s="337"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="155" t="s">
@@ -13462,8 +13498,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="346"/>
-      <c r="S8" s="346"/>
+      <c r="R8" s="337"/>
+      <c r="S8" s="337"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="155" t="s">
@@ -17795,6 +17831,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
@@ -17811,7 +17848,6 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>

--- a/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Julio/Julio - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F18E3A-2E10-4258-985E-DE8E65501A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09229578-034A-4924-B5BB-B435401120C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$133</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1993,7 +1998,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="398">
+  <cellXfs count="402">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2379,29 +2384,17 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2443,6 +2436,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2505,14 +2504,47 @@
     <xf numFmtId="164" fontId="28" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2531,15 +2563,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2610,20 +2633,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2655,18 +2678,6 @@
     <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2694,12 +2705,14 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2781,9 +2794,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2821,9 +2834,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2856,9 +2869,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2891,9 +2921,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3068,24 +3115,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N141"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="82"/>
       <c r="B1" s="91"/>
       <c r="C1" s="98" t="s">
@@ -3099,7 +3146,7 @@
       <c r="I1" s="80"/>
       <c r="J1" s="81"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="83"/>
       <c r="B2" s="92"/>
       <c r="C2" s="92" t="s">
@@ -3113,7 +3160,7 @@
       <c r="I2" s="93"/>
       <c r="J2" s="79"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="83"/>
       <c r="B3" s="92"/>
       <c r="C3" s="92" t="s">
@@ -3129,7 +3176,7 @@
       <c r="I3" s="93"/>
       <c r="J3" s="79"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="83"/>
       <c r="B4" s="92"/>
       <c r="C4" s="92" t="s">
@@ -3143,7 +3190,7 @@
       <c r="I4" s="93"/>
       <c r="J4" s="79"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="87"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92" t="s">
@@ -3159,7 +3206,7 @@
       <c r="I5" s="92"/>
       <c r="J5" s="88"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="87"/>
       <c r="B6" s="92"/>
       <c r="C6" s="92" t="s">
@@ -3173,7 +3220,7 @@
       <c r="I6" s="92"/>
       <c r="J6" s="88"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="89"/>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -3185,118 +3232,118 @@
       <c r="I7" s="90"/>
       <c r="J7" s="94"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="289" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="331" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="289"/>
-      <c r="C14" s="289"/>
-      <c r="D14" s="289"/>
-      <c r="E14" s="289"/>
-      <c r="F14" s="289"/>
-      <c r="G14" s="289"/>
-      <c r="H14" s="289"/>
-      <c r="I14" s="289"/>
-      <c r="J14" s="289"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="289"/>
-      <c r="B15" s="289"/>
-      <c r="C15" s="289"/>
-      <c r="D15" s="289"/>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="289"/>
-      <c r="I15" s="289"/>
-      <c r="J15" s="289"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="289"/>
-      <c r="B16" s="289"/>
-      <c r="C16" s="289"/>
-      <c r="D16" s="289"/>
-      <c r="E16" s="289"/>
-      <c r="F16" s="289"/>
-      <c r="G16" s="289"/>
-      <c r="H16" s="289"/>
-      <c r="I16" s="289"/>
-      <c r="J16" s="289"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="289"/>
-      <c r="B17" s="289"/>
-      <c r="C17" s="289"/>
-      <c r="D17" s="289"/>
-      <c r="E17" s="289"/>
-      <c r="F17" s="289"/>
-      <c r="G17" s="289"/>
-      <c r="H17" s="289"/>
-      <c r="I17" s="289"/>
-      <c r="J17" s="289"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="289"/>
-      <c r="B18" s="289"/>
-      <c r="C18" s="289"/>
-      <c r="D18" s="289"/>
-      <c r="E18" s="289"/>
-      <c r="F18" s="289"/>
-      <c r="G18" s="289"/>
-      <c r="H18" s="289"/>
-      <c r="I18" s="289"/>
-      <c r="J18" s="289"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="331"/>
+      <c r="C14" s="331"/>
+      <c r="D14" s="331"/>
+      <c r="E14" s="331"/>
+      <c r="F14" s="331"/>
+      <c r="G14" s="331"/>
+      <c r="H14" s="331"/>
+      <c r="I14" s="331"/>
+      <c r="J14" s="331"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="331"/>
+      <c r="B15" s="331"/>
+      <c r="C15" s="331"/>
+      <c r="D15" s="331"/>
+      <c r="E15" s="331"/>
+      <c r="F15" s="331"/>
+      <c r="G15" s="331"/>
+      <c r="H15" s="331"/>
+      <c r="I15" s="331"/>
+      <c r="J15" s="331"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="331"/>
+      <c r="B16" s="331"/>
+      <c r="C16" s="331"/>
+      <c r="D16" s="331"/>
+      <c r="E16" s="331"/>
+      <c r="F16" s="331"/>
+      <c r="G16" s="331"/>
+      <c r="H16" s="331"/>
+      <c r="I16" s="331"/>
+      <c r="J16" s="331"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="331"/>
+      <c r="B17" s="331"/>
+      <c r="C17" s="331"/>
+      <c r="D17" s="331"/>
+      <c r="E17" s="331"/>
+      <c r="F17" s="331"/>
+      <c r="G17" s="331"/>
+      <c r="H17" s="331"/>
+      <c r="I17" s="331"/>
+      <c r="J17" s="331"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="331"/>
+      <c r="B18" s="331"/>
+      <c r="C18" s="331"/>
+      <c r="D18" s="331"/>
+      <c r="E18" s="331"/>
+      <c r="F18" s="331"/>
+      <c r="G18" s="331"/>
+      <c r="H18" s="331"/>
+      <c r="I18" s="331"/>
+      <c r="J18" s="331"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="290" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="332" t="s">
         <v>373</v>
       </c>
-      <c r="B20" s="290"/>
-      <c r="C20" s="290"/>
-      <c r="D20" s="290"/>
-      <c r="E20" s="290"/>
-      <c r="F20" s="290"/>
-      <c r="G20" s="290"/>
-      <c r="H20" s="290"/>
-      <c r="I20" s="290"/>
-      <c r="J20" s="290"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="290"/>
-      <c r="B21" s="290"/>
-      <c r="C21" s="290"/>
-      <c r="D21" s="290"/>
-      <c r="E21" s="290"/>
-      <c r="F21" s="290"/>
-      <c r="G21" s="290"/>
-      <c r="H21" s="290"/>
-      <c r="I21" s="290"/>
-      <c r="J21" s="290"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="290"/>
-      <c r="B22" s="290"/>
-      <c r="C22" s="290"/>
-      <c r="D22" s="290"/>
-      <c r="E22" s="290"/>
-      <c r="F22" s="290"/>
-      <c r="G22" s="290"/>
-      <c r="H22" s="290"/>
-      <c r="I22" s="290"/>
-      <c r="J22" s="290"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="332"/>
+      <c r="C20" s="332"/>
+      <c r="D20" s="332"/>
+      <c r="E20" s="332"/>
+      <c r="F20" s="332"/>
+      <c r="G20" s="332"/>
+      <c r="H20" s="332"/>
+      <c r="I20" s="332"/>
+      <c r="J20" s="332"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="332"/>
+      <c r="B21" s="332"/>
+      <c r="C21" s="332"/>
+      <c r="D21" s="332"/>
+      <c r="E21" s="332"/>
+      <c r="F21" s="332"/>
+      <c r="G21" s="332"/>
+      <c r="H21" s="332"/>
+      <c r="I21" s="332"/>
+      <c r="J21" s="332"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="332"/>
+      <c r="B22" s="332"/>
+      <c r="C22" s="332"/>
+      <c r="D22" s="332"/>
+      <c r="E22" s="332"/>
+      <c r="F22" s="332"/>
+      <c r="G22" s="332"/>
+      <c r="H22" s="332"/>
+      <c r="I22" s="332"/>
+      <c r="J22" s="332"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="198" t="s">
         <v>18</v>
       </c>
@@ -3322,7 +3369,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="203" t="s">
         <v>335</v>
       </c>
@@ -3337,7 +3384,7 @@
       <c r="J25" s="44"/>
       <c r="L25" s="50"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="205" t="s">
         <v>359</v>
       </c>
@@ -3358,7 +3405,7 @@
       <c r="J26" s="3"/>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="206" t="s">
         <v>35</v>
       </c>
@@ -3401,7 +3448,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="205" t="s">
         <v>232</v>
       </c>
@@ -3416,7 +3463,7 @@
       <c r="J28" s="44"/>
       <c r="L28" s="50"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="205"/>
       <c r="B29" s="175"/>
       <c r="C29" s="175"/>
@@ -3429,7 +3476,7 @@
       <c r="J29" s="44"/>
       <c r="L29" s="50"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="206" t="s">
         <v>16</v>
       </c>
@@ -3457,7 +3504,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="205" t="s">
         <v>228</v>
       </c>
@@ -3472,7 +3519,7 @@
       <c r="J31" s="38"/>
       <c r="L31" s="50"/>
     </row>
-    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="136" t="s">
         <v>351</v>
       </c>
@@ -3493,7 +3540,7 @@
       <c r="J32" s="38"/>
       <c r="L32" s="50"/>
     </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="136" t="s">
         <v>231</v>
       </c>
@@ -3514,7 +3561,7 @@
       <c r="J33" s="38"/>
       <c r="L33" s="50"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="136"/>
       <c r="B34" s="136"/>
       <c r="C34" s="136"/>
@@ -3527,7 +3574,7 @@
       <c r="J34" s="38"/>
       <c r="L34" s="50"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="206" t="s">
         <v>230</v>
       </c>
@@ -3570,7 +3617,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="205" t="s">
         <v>1</v>
       </c>
@@ -3585,7 +3632,7 @@
       <c r="J36" s="3"/>
       <c r="L36" s="50"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="175"/>
       <c r="B37" s="175"/>
       <c r="C37" s="175"/>
@@ -3598,7 +3645,7 @@
       <c r="J37" s="3"/>
       <c r="L37" s="50"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="175"/>
       <c r="B38" s="175"/>
       <c r="C38" s="175"/>
@@ -3611,7 +3658,7 @@
       <c r="J38" s="3"/>
       <c r="L38" s="50"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="175"/>
       <c r="B39" s="175"/>
       <c r="C39" s="211"/>
@@ -3624,7 +3671,7 @@
       <c r="J39" s="3"/>
       <c r="L39" s="50"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="206" t="s">
         <v>229</v>
       </c>
@@ -3667,7 +3714,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="205" t="s">
         <v>221</v>
       </c>
@@ -3682,7 +3729,7 @@
       <c r="J41" s="25"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="175" t="s">
         <v>225</v>
       </c>
@@ -3723,9 +3770,9 @@
       </c>
       <c r="L42" s="50"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="291"/>
-      <c r="B43" s="292"/>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="309"/>
+      <c r="B43" s="310"/>
       <c r="C43" s="175"/>
       <c r="D43" s="33"/>
       <c r="E43" s="204"/>
@@ -3737,7 +3784,7 @@
       <c r="K43" s="32"/>
       <c r="L43" s="50"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="206" t="s">
         <v>2</v>
       </c>
@@ -3780,7 +3827,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="205" t="s">
         <v>3</v>
       </c>
@@ -3795,7 +3842,7 @@
       <c r="J45" s="3"/>
       <c r="L45" s="50"/>
     </row>
-    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="215" t="s">
         <v>398</v>
       </c>
@@ -3841,7 +3888,7 @@
       <c r="M46" s="64"/>
       <c r="N46" s="64"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="175" t="s">
         <v>226</v>
       </c>
@@ -3888,7 +3935,7 @@
       <c r="M47" s="64"/>
       <c r="N47" s="64"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="175" t="s">
         <v>227</v>
       </c>
@@ -3925,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="175" t="s">
         <v>383</v>
       </c>
@@ -3956,7 +4003,7 @@
       <c r="M49" s="64"/>
       <c r="N49" s="64"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="215" t="s">
         <v>402</v>
       </c>
@@ -3984,7 +4031,7 @@
       <c r="M50" s="64"/>
       <c r="N50" s="64"/>
     </row>
-    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="215" t="s">
         <v>394</v>
       </c>
@@ -4015,11 +4062,11 @@
       <c r="M51" s="64"/>
       <c r="N51" s="64"/>
     </row>
-    <row r="52" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="287" t="s">
+    <row r="52" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="293" t="s">
         <v>377</v>
       </c>
-      <c r="B52" s="288"/>
+      <c r="B52" s="294"/>
       <c r="C52" s="273" t="s">
         <v>393</v>
       </c>
@@ -4052,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="136" t="s">
         <v>257</v>
       </c>
@@ -4083,7 +4130,7 @@
       <c r="M53" s="64"/>
       <c r="N53" s="64"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="136" t="s">
         <v>258</v>
       </c>
@@ -4135,7 +4182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="217" t="s">
         <v>256</v>
       </c>
@@ -4172,7 +4219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="206" t="s">
         <v>4</v>
       </c>
@@ -4219,7 +4266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="175"/>
       <c r="B57" s="175"/>
       <c r="C57" s="175"/>
@@ -4232,7 +4279,7 @@
       <c r="J57" s="3"/>
       <c r="L57" s="50"/>
     </row>
-    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="175"/>
       <c r="B58" s="175"/>
       <c r="C58" s="175"/>
@@ -4245,7 +4292,7 @@
       <c r="J58" s="3"/>
       <c r="L58" s="50"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="205" t="s">
         <v>222</v>
       </c>
@@ -4260,7 +4307,7 @@
       <c r="J59" s="3"/>
       <c r="L59" s="50"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="209" t="s">
         <v>334</v>
       </c>
@@ -4289,11 +4336,11 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="293" t="s">
+    <row r="61" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="333" t="s">
         <v>386</v>
       </c>
-      <c r="B61" s="294"/>
+      <c r="B61" s="334"/>
       <c r="C61" s="136" t="s">
         <v>387</v>
       </c>
@@ -4333,11 +4380,11 @@
         <v>175700</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="293" t="s">
+    <row r="62" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="333" t="s">
         <v>388</v>
       </c>
-      <c r="B62" s="294"/>
+      <c r="B62" s="334"/>
       <c r="C62" s="136" t="s">
         <v>387</v>
       </c>
@@ -4377,11 +4424,11 @@
         <v>205999.99999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="287" t="s">
+    <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="293" t="s">
         <v>385</v>
       </c>
-      <c r="B63" s="288"/>
+      <c r="B63" s="294"/>
       <c r="C63" s="273" t="s">
         <v>399</v>
       </c>
@@ -4421,11 +4468,11 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="287" t="s">
+    <row r="64" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="293" t="s">
         <v>389</v>
       </c>
-      <c r="B64" s="288"/>
+      <c r="B64" s="294"/>
       <c r="C64" s="273" t="s">
         <v>390</v>
       </c>
@@ -4465,7 +4512,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="271" t="s">
         <v>382</v>
       </c>
@@ -4509,7 +4556,7 @@
         <v>242000</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="272" t="s">
         <v>384</v>
       </c>
@@ -4538,11 +4585,11 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="287" t="s">
+    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="293" t="s">
         <v>403</v>
       </c>
-      <c r="B67" s="288"/>
+      <c r="B67" s="294"/>
       <c r="C67" s="273" t="s">
         <v>404</v>
       </c>
@@ -4582,11 +4629,11 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="291" t="s">
+    <row r="68" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="309" t="s">
         <v>380</v>
       </c>
-      <c r="B68" s="292"/>
+      <c r="B68" s="310"/>
       <c r="C68" s="273" t="s">
         <v>381</v>
       </c>
@@ -4626,7 +4673,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="242" t="s">
         <v>371</v>
       </c>
@@ -4664,7 +4711,7 @@
       <c r="K69" s="32"/>
       <c r="L69" s="54"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="206" t="s">
         <v>223</v>
       </c>
@@ -4708,7 +4755,7 @@
       </c>
       <c r="N70" s="32"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="205" t="s">
         <v>5</v>
       </c>
@@ -4723,7 +4770,7 @@
       <c r="J71" s="3"/>
       <c r="L71" s="50"/>
     </row>
-    <row r="72" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="220" t="s">
         <v>6</v>
       </c>
@@ -4765,7 +4812,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="295" t="s">
         <v>405</v>
       </c>
@@ -4801,7 +4848,7 @@
       <c r="L73" s="50"/>
       <c r="N73" s="33"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="175"/>
       <c r="B74" s="175"/>
       <c r="C74" s="175"/>
@@ -4815,7 +4862,7 @@
       <c r="L74" s="50"/>
       <c r="N74" s="32"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="206" t="s">
         <v>7</v>
       </c>
@@ -4859,7 +4906,7 @@
       </c>
       <c r="N75" s="32"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="175" t="s">
         <v>26</v>
       </c>
@@ -4894,7 +4941,7 @@
       </c>
       <c r="L76" s="50"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="175" t="s">
         <v>27</v>
       </c>
@@ -4929,7 +4976,7 @@
       </c>
       <c r="L77" s="50"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="206" t="s">
         <v>224</v>
       </c>
@@ -4972,7 +5019,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="73"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -4985,7 +5032,7 @@
       <c r="J79" s="72"/>
       <c r="L79" s="50"/>
     </row>
-    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="224" t="s">
         <v>412</v>
       </c>
@@ -5027,7 +5074,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="227"/>
       <c r="B81" s="228"/>
       <c r="C81" s="228"/>
@@ -5041,7 +5088,7 @@
       <c r="K81" s="32"/>
       <c r="L81" s="50"/>
     </row>
-    <row r="82" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="229" t="s">
         <v>28</v>
       </c>
@@ -5088,7 +5135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="65"/>
       <c r="B83" s="65"/>
       <c r="C83" s="65"/>
@@ -5099,7 +5146,7 @@
       <c r="H83" s="32"/>
       <c r="I83" s="32"/>
     </row>
-    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="233" t="s">
         <v>36</v>
       </c>
@@ -5112,7 +5159,7 @@
       <c r="H84" s="32"/>
       <c r="I84" s="32"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="235" t="s">
         <v>397</v>
       </c>
@@ -5127,7 +5174,7 @@
       <c r="H85" s="32"/>
       <c r="I85" s="32"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="235"/>
       <c r="B86" s="65"/>
       <c r="C86" s="245"/>
@@ -5138,7 +5185,7 @@
       <c r="H86" s="32"/>
       <c r="I86" s="32"/>
     </row>
-    <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="235"/>
       <c r="B87" s="65"/>
       <c r="C87" s="245"/>
@@ -5149,7 +5196,7 @@
       <c r="H87" s="32"/>
       <c r="I87" s="32"/>
     </row>
-    <row r="88" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="235"/>
       <c r="B88" s="65"/>
       <c r="C88" s="245"/>
@@ -5160,7 +5207,7 @@
       <c r="H88" s="32"/>
       <c r="I88" s="32"/>
     </row>
-    <row r="89" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="236" t="s">
         <v>16</v>
       </c>
@@ -5176,7 +5223,7 @@
       <c r="H89" s="32"/>
       <c r="I89" s="32"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="65"/>
       <c r="B90" s="65"/>
       <c r="C90" s="65"/>
@@ -5187,7 +5234,7 @@
       <c r="H90" s="32"/>
       <c r="I90" s="32"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="65"/>
       <c r="B91" s="65"/>
       <c r="C91" s="65"/>
@@ -5198,13 +5245,13 @@
       <c r="H91" s="46"/>
       <c r="I91" s="46"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="316" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="318" t="s">
         <v>32</v>
       </c>
-      <c r="B92" s="317"/>
-      <c r="C92" s="317"/>
-      <c r="D92" s="317"/>
+      <c r="B92" s="319"/>
+      <c r="C92" s="319"/>
+      <c r="D92" s="319"/>
       <c r="E92" s="60" t="s">
         <v>10</v>
       </c>
@@ -5224,8 +5271,8 @@
         <v>169</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="287"/>
+    <row r="93" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="293"/>
       <c r="B93" s="298"/>
       <c r="C93" s="240"/>
       <c r="D93" s="33"/>
@@ -5239,9 +5286,9 @@
       <c r="I93" s="49"/>
       <c r="J93" s="44"/>
     </row>
-    <row r="94" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="318"/>
-      <c r="B94" s="319"/>
+    <row r="94" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="320"/>
+      <c r="B94" s="321"/>
       <c r="C94" s="62"/>
       <c r="D94" s="33"/>
       <c r="E94" s="49"/>
@@ -5251,12 +5298,12 @@
       <c r="I94" s="49"/>
       <c r="J94" s="44"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A95" s="313" t="s">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="315" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="314"/>
-      <c r="C95" s="315"/>
+      <c r="B95" s="316"/>
+      <c r="C95" s="317"/>
       <c r="D95" s="59">
         <f>SUM(D93:D94)</f>
         <v>0</v>
@@ -5282,14 +5329,14 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="32"/>
       <c r="F97" s="32"/>
       <c r="G97" s="32"/>
       <c r="H97" s="32"/>
       <c r="I97" s="32"/>
     </row>
-    <row r="98" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="27" t="s">
         <v>29</v>
       </c>
@@ -5298,7 +5345,7 @@
         <v>21566802.780000001</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="29" t="s">
         <v>31</v>
       </c>
@@ -5315,7 +5362,7 @@
       <c r="H99" s="299"/>
       <c r="I99" s="299"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D100" s="299"/>
       <c r="E100" s="299"/>
       <c r="F100" s="299"/>
@@ -5323,7 +5370,7 @@
       <c r="H100" s="299"/>
       <c r="I100" s="299"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D101" s="299"/>
       <c r="E101" s="299"/>
       <c r="F101" s="299"/>
@@ -5331,7 +5378,7 @@
       <c r="H101" s="299"/>
       <c r="I101" s="299"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>19</v>
       </c>
@@ -5344,7 +5391,7 @@
       <c r="H102" s="299"/>
       <c r="I102" s="299"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>20</v>
       </c>
@@ -5359,7 +5406,7 @@
       <c r="H103" s="299"/>
       <c r="I103" s="299"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>21</v>
       </c>
@@ -5377,7 +5424,7 @@
       <c r="H104" s="299"/>
       <c r="I104" s="299"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
         <v>338</v>
       </c>
@@ -5393,7 +5440,7 @@
       <c r="H105" s="299"/>
       <c r="I105" s="299"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
         <v>34</v>
       </c>
@@ -5410,7 +5457,7 @@
       <c r="I106" s="299"/>
       <c r="K106" s="33"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>33</v>
       </c>
@@ -5427,7 +5474,7 @@
       <c r="I107" s="299"/>
       <c r="K107" s="39"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>272</v>
       </c>
@@ -5444,7 +5491,7 @@
       <c r="I108" s="299"/>
       <c r="K108" s="39"/>
     </row>
-    <row r="109" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="274" t="s">
         <v>410</v>
       </c>
@@ -5460,7 +5507,7 @@
       <c r="I109" s="299"/>
       <c r="K109" s="39"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
         <v>30</v>
       </c>
@@ -5476,7 +5523,7 @@
       <c r="H110" s="299"/>
       <c r="I110" s="299"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
         <v>36</v>
       </c>
@@ -5492,7 +5539,7 @@
       <c r="H111" s="299"/>
       <c r="I111" s="299"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>23</v>
       </c>
@@ -5508,7 +5555,7 @@
       <c r="H112" s="299"/>
       <c r="I112" s="299"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="14"/>
       <c r="C113" s="10"/>
       <c r="D113" s="299"/>
@@ -5518,7 +5565,7 @@
       <c r="H113" s="299"/>
       <c r="I113" s="299"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>271</v>
       </c>
@@ -5531,7 +5578,7 @@
       <c r="H114" s="299"/>
       <c r="I114" s="299"/>
     </row>
-    <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="195"/>
       <c r="B115" s="22">
         <v>0</v>
@@ -5540,7 +5587,7 @@
       <c r="D115" s="17"/>
       <c r="E115" s="17"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="25" t="s">
         <v>16</v>
       </c>
@@ -5551,17 +5598,17 @@
       <c r="C116" s="10"/>
       <c r="E116" s="17"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="14"/>
       <c r="C117" s="10"/>
       <c r="D117" s="17"/>
     </row>
-    <row r="118" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="14"/>
       <c r="C118" s="10"/>
       <c r="D118" s="17"/>
     </row>
-    <row r="119" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>19</v>
       </c>
@@ -5569,38 +5616,38 @@
         <v>-25817.72</v>
       </c>
       <c r="C119" s="10"/>
-      <c r="D119" s="320" t="s">
+      <c r="D119" s="322" t="s">
         <v>370</v>
       </c>
-      <c r="E119" s="321"/>
-      <c r="F119" s="321"/>
-      <c r="G119" s="321"/>
-      <c r="H119" s="321"/>
-      <c r="I119" s="322"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E119" s="323"/>
+      <c r="F119" s="323"/>
+      <c r="G119" s="323"/>
+      <c r="H119" s="323"/>
+      <c r="I119" s="324"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="11"/>
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>
-      <c r="D120" s="323"/>
-      <c r="E120" s="324"/>
-      <c r="F120" s="324"/>
-      <c r="G120" s="324"/>
-      <c r="H120" s="324"/>
-      <c r="I120" s="325"/>
-    </row>
-    <row r="121" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D120" s="325"/>
+      <c r="E120" s="326"/>
+      <c r="F120" s="326"/>
+      <c r="G120" s="326"/>
+      <c r="H120" s="326"/>
+      <c r="I120" s="327"/>
+    </row>
+    <row r="121" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="197"/>
       <c r="B121" s="23"/>
       <c r="C121" s="10"/>
-      <c r="D121" s="323"/>
-      <c r="E121" s="324"/>
-      <c r="F121" s="324"/>
-      <c r="G121" s="324"/>
-      <c r="H121" s="324"/>
-      <c r="I121" s="325"/>
-    </row>
-    <row r="122" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D121" s="325"/>
+      <c r="E121" s="326"/>
+      <c r="F121" s="326"/>
+      <c r="G121" s="326"/>
+      <c r="H121" s="326"/>
+      <c r="I121" s="327"/>
+    </row>
+    <row r="122" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="25" t="s">
         <v>16</v>
       </c>
@@ -5609,31 +5656,31 @@
         <v>-25817.72</v>
       </c>
       <c r="C122" s="10"/>
-      <c r="D122" s="326"/>
-      <c r="E122" s="327"/>
-      <c r="F122" s="327"/>
-      <c r="G122" s="327"/>
-      <c r="H122" s="327"/>
-      <c r="I122" s="328"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D122" s="328"/>
+      <c r="E122" s="329"/>
+      <c r="F122" s="329"/>
+      <c r="G122" s="329"/>
+      <c r="H122" s="329"/>
+      <c r="I122" s="330"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="14"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="14"/>
       <c r="F124" s="53"/>
       <c r="G124" s="53"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="14"/>
       <c r="F125" s="53"/>
       <c r="G125" s="53"/>
     </row>
-    <row r="126" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H126" s="64"/>
       <c r="I126" s="64"/>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>355</v>
       </c>
@@ -5651,7 +5698,7 @@
       <c r="I127" s="301"/>
       <c r="J127" s="302"/>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>238</v>
       </c>
@@ -5667,7 +5714,7 @@
       <c r="I128" s="304"/>
       <c r="J128" s="305"/>
     </row>
-    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>411</v>
       </c>
@@ -5683,7 +5730,7 @@
       <c r="I129" s="304"/>
       <c r="J129" s="305"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="25" t="s">
         <v>16</v>
       </c>
@@ -5700,7 +5747,7 @@
       <c r="I130" s="304"/>
       <c r="J130" s="305"/>
     </row>
-    <row r="131" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C131" s="17"/>
       <c r="D131" s="303"/>
       <c r="E131" s="304"/>
@@ -5710,11 +5757,11 @@
       <c r="I131" s="304"/>
       <c r="J131" s="305"/>
     </row>
-    <row r="132" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="309" t="s">
+    <row r="132" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="311" t="s">
         <v>356</v>
       </c>
-      <c r="B132" s="311">
+      <c r="B132" s="313">
         <f>B130+B112+B122</f>
         <v>2235682.8703661053</v>
       </c>
@@ -5727,9 +5774,9 @@
       <c r="I132" s="304"/>
       <c r="J132" s="305"/>
     </row>
-    <row r="133" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="310"/>
-      <c r="B133" s="312"/>
+    <row r="133" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="312"/>
+      <c r="B133" s="314"/>
       <c r="D133" s="306"/>
       <c r="E133" s="307"/>
       <c r="F133" s="307"/>
@@ -5738,14 +5785,14 @@
       <c r="I133" s="307"/>
       <c r="J133" s="308"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D139" s="53"/>
       <c r="E139" s="53"/>
       <c r="F139" s="53"/>
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D140" s="246" t="s">
         <v>372</v>
       </c>
@@ -5754,7 +5801,7 @@
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D141" s="246"/>
       <c r="E141" s="53"/>
       <c r="F141" s="53"/>
@@ -5763,6 +5810,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="A93:B93"/>
@@ -5775,14 +5830,6 @@
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="D119:I122"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5793,37 +5840,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="358" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="368" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="359"/>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="359"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="369"/>
+      <c r="D1" s="369"/>
+      <c r="E1" s="369"/>
       <c r="F1" s="120" t="s">
         <v>274</v>
       </c>
@@ -5835,20 +5882,20 @@
       <c r="L1" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="334">
+      <c r="M1" s="347">
         <f>RESUMEN!D82-N3</f>
         <v>21530482.66</v>
       </c>
-      <c r="N1" s="335"/>
+      <c r="N1" s="348"/>
       <c r="O1" s="121"/>
       <c r="P1" s="45"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="360"/>
-      <c r="B2" s="361"/>
-      <c r="C2" s="361"/>
-      <c r="D2" s="361"/>
-      <c r="E2" s="361"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="370"/>
+      <c r="B2" s="371"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5867,12 +5914,12 @@
       <c r="O2" s="122"/>
       <c r="P2" s="45"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="360"/>
-      <c r="B3" s="361"/>
-      <c r="C3" s="361"/>
-      <c r="D3" s="361"/>
-      <c r="E3" s="361"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="370"/>
+      <c r="B3" s="371"/>
+      <c r="C3" s="371"/>
+      <c r="D3" s="371"/>
+      <c r="E3" s="371"/>
       <c r="F3" s="4" t="s">
         <v>275</v>
       </c>
@@ -5891,12 +5938,12 @@
       <c r="O3" s="124"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="362"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="372"/>
+      <c r="B4" s="373"/>
+      <c r="C4" s="373"/>
+      <c r="D4" s="373"/>
+      <c r="E4" s="373"/>
       <c r="F4" s="125"/>
       <c r="G4" s="125"/>
       <c r="H4" s="125"/>
@@ -5909,98 +5956,98 @@
       <c r="O4" s="128"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="343" t="s">
+      <c r="C5" s="353" t="s">
         <v>368</v>
       </c>
-      <c r="D5" s="344"/>
-      <c r="E5" s="344"/>
-      <c r="F5" s="344"/>
-      <c r="G5" s="344"/>
-      <c r="H5" s="344"/>
-      <c r="I5" s="344"/>
-      <c r="J5" s="344"/>
-      <c r="K5" s="344"/>
-      <c r="L5" s="344"/>
-      <c r="M5" s="344"/>
-      <c r="N5" s="344"/>
-      <c r="O5" s="345"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="354"/>
+      <c r="H5" s="354"/>
+      <c r="I5" s="354"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="354"/>
+      <c r="L5" s="354"/>
+      <c r="M5" s="354"/>
+      <c r="N5" s="354"/>
+      <c r="O5" s="355"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="346"/>
-      <c r="D6" s="347"/>
-      <c r="E6" s="347"/>
-      <c r="F6" s="347"/>
-      <c r="G6" s="347"/>
-      <c r="H6" s="347"/>
-      <c r="I6" s="347"/>
-      <c r="J6" s="347"/>
-      <c r="K6" s="347"/>
-      <c r="L6" s="347"/>
-      <c r="M6" s="347"/>
-      <c r="N6" s="347"/>
-      <c r="O6" s="348"/>
+      <c r="C6" s="356"/>
+      <c r="D6" s="357"/>
+      <c r="E6" s="357"/>
+      <c r="F6" s="357"/>
+      <c r="G6" s="357"/>
+      <c r="H6" s="357"/>
+      <c r="I6" s="357"/>
+      <c r="J6" s="357"/>
+      <c r="K6" s="357"/>
+      <c r="L6" s="357"/>
+      <c r="M6" s="357"/>
+      <c r="N6" s="357"/>
+      <c r="O6" s="358"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="346"/>
-      <c r="D7" s="347"/>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
-      <c r="G7" s="347"/>
-      <c r="H7" s="347"/>
-      <c r="I7" s="347"/>
-      <c r="J7" s="347"/>
-      <c r="K7" s="347"/>
-      <c r="L7" s="347"/>
-      <c r="M7" s="347"/>
-      <c r="N7" s="347"/>
-      <c r="O7" s="348"/>
+      <c r="C7" s="356"/>
+      <c r="D7" s="357"/>
+      <c r="E7" s="357"/>
+      <c r="F7" s="357"/>
+      <c r="G7" s="357"/>
+      <c r="H7" s="357"/>
+      <c r="I7" s="357"/>
+      <c r="J7" s="357"/>
+      <c r="K7" s="357"/>
+      <c r="L7" s="357"/>
+      <c r="M7" s="357"/>
+      <c r="N7" s="357"/>
+      <c r="O7" s="358"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="349"/>
-      <c r="D8" s="350"/>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
-      <c r="G8" s="350"/>
-      <c r="H8" s="350"/>
-      <c r="I8" s="350"/>
-      <c r="J8" s="350"/>
-      <c r="K8" s="350"/>
-      <c r="L8" s="350"/>
-      <c r="M8" s="350"/>
-      <c r="N8" s="350"/>
-      <c r="O8" s="351"/>
+      <c r="C8" s="359"/>
+      <c r="D8" s="360"/>
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="G8" s="360"/>
+      <c r="H8" s="360"/>
+      <c r="I8" s="360"/>
+      <c r="J8" s="360"/>
+      <c r="K8" s="360"/>
+      <c r="L8" s="360"/>
+      <c r="M8" s="360"/>
+      <c r="N8" s="360"/>
+      <c r="O8" s="361"/>
       <c r="Q8" s="64"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="352" t="s">
+      <c r="C9" s="362" t="s">
         <v>286</v>
       </c>
-      <c r="D9" s="353"/>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="G9" s="353"/>
-      <c r="H9" s="353"/>
-      <c r="I9" s="353"/>
-      <c r="J9" s="353"/>
-      <c r="K9" s="353"/>
-      <c r="L9" s="353"/>
-      <c r="M9" s="353"/>
-      <c r="N9" s="353"/>
-      <c r="O9" s="354"/>
+      <c r="D9" s="363"/>
+      <c r="E9" s="363"/>
+      <c r="F9" s="363"/>
+      <c r="G9" s="363"/>
+      <c r="H9" s="363"/>
+      <c r="I9" s="363"/>
+      <c r="J9" s="363"/>
+      <c r="K9" s="363"/>
+      <c r="L9" s="363"/>
+      <c r="M9" s="363"/>
+      <c r="N9" s="363"/>
+      <c r="O9" s="364"/>
       <c r="Q9" t="s">
         <v>233</v>
       </c>
@@ -6009,22 +6056,22 @@
         <v>217653.69664800004</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="355"/>
-      <c r="D10" s="356"/>
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
-      <c r="G10" s="356"/>
-      <c r="H10" s="356"/>
-      <c r="I10" s="356"/>
-      <c r="J10" s="356"/>
-      <c r="K10" s="356"/>
-      <c r="L10" s="356"/>
-      <c r="M10" s="356"/>
-      <c r="N10" s="356"/>
-      <c r="O10" s="357"/>
+      <c r="C10" s="365"/>
+      <c r="D10" s="366"/>
+      <c r="E10" s="366"/>
+      <c r="F10" s="366"/>
+      <c r="G10" s="366"/>
+      <c r="H10" s="366"/>
+      <c r="I10" s="366"/>
+      <c r="J10" s="366"/>
+      <c r="K10" s="366"/>
+      <c r="L10" s="366"/>
+      <c r="M10" s="366"/>
+      <c r="N10" s="366"/>
+      <c r="O10" s="367"/>
       <c r="Q10" t="s">
         <v>234</v>
       </c>
@@ -6033,50 +6080,50 @@
         <v>257959.93676800004</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="330" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="364" t="s">
+      <c r="B11" s="340" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="330" t="s">
+      <c r="C11" s="338" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="366" t="s">
+      <c r="D11" s="342" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="366" t="s">
+      <c r="E11" s="342" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="330" t="s">
+      <c r="F11" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="330" t="s">
+      <c r="G11" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="330" t="s">
+      <c r="H11" s="338" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="336" t="s">
+      <c r="I11" s="349" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="338" t="s">
+      <c r="J11" s="335" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="338" t="s">
+      <c r="K11" s="335" t="s">
         <v>366</v>
       </c>
-      <c r="L11" s="338" t="s">
+      <c r="L11" s="335" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="341" t="s">
+      <c r="M11" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="338" t="s">
+      <c r="N11" s="335" t="s">
         <v>260</v>
       </c>
-      <c r="O11" s="338" t="s">
+      <c r="O11" s="335" t="s">
         <v>259</v>
       </c>
       <c r="Q11" t="s">
@@ -6087,22 +6134,22 @@
         <v>243852.75272600001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="331"/>
-      <c r="B12" s="365"/>
-      <c r="C12" s="331"/>
-      <c r="D12" s="367"/>
-      <c r="E12" s="367"/>
-      <c r="F12" s="331"/>
-      <c r="G12" s="331"/>
-      <c r="H12" s="331"/>
-      <c r="I12" s="337"/>
-      <c r="J12" s="339"/>
-      <c r="K12" s="339"/>
-      <c r="L12" s="339"/>
-      <c r="M12" s="342"/>
-      <c r="N12" s="339"/>
-      <c r="O12" s="339"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="339"/>
+      <c r="B12" s="341"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="343"/>
+      <c r="E12" s="343"/>
+      <c r="F12" s="339"/>
+      <c r="G12" s="339"/>
+      <c r="H12" s="339"/>
+      <c r="I12" s="350"/>
+      <c r="J12" s="336"/>
+      <c r="K12" s="336"/>
+      <c r="L12" s="336"/>
+      <c r="M12" s="352"/>
+      <c r="N12" s="336"/>
+      <c r="O12" s="336"/>
       <c r="Q12" t="s">
         <v>236</v>
       </c>
@@ -6111,20 +6158,20 @@
         <v>300281.48889400001</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="331"/>
-      <c r="B13" s="365"/>
-      <c r="C13" s="331"/>
-      <c r="D13" s="367"/>
-      <c r="E13" s="367"/>
-      <c r="F13" s="331"/>
-      <c r="G13" s="331"/>
-      <c r="H13" s="331"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="339"/>
-      <c r="K13" s="340"/>
-      <c r="L13" s="340"/>
-      <c r="M13" s="342"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="339"/>
+      <c r="B13" s="341"/>
+      <c r="C13" s="339"/>
+      <c r="D13" s="343"/>
+      <c r="E13" s="343"/>
+      <c r="F13" s="339"/>
+      <c r="G13" s="339"/>
+      <c r="H13" s="339"/>
+      <c r="I13" s="350"/>
+      <c r="J13" s="336"/>
+      <c r="K13" s="337"/>
+      <c r="L13" s="337"/>
+      <c r="M13" s="352"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/08</v>
@@ -6141,7 +6188,7 @@
         <v>350664.28904400003</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="194" t="s">
         <v>114</v>
       </c>
@@ -6192,10 +6239,13 @@
       <c r="P14" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="R14" s="329"/>
-      <c r="S14" s="329"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R14" s="399">
+        <f>SUM(R9:R13)</f>
+        <v>1370412.16408</v>
+      </c>
+      <c r="S14" s="398"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="24" t="s">
@@ -6242,10 +6292,10 @@
       <c r="P15" s="85" t="s">
         <v>341</v>
       </c>
-      <c r="R15" s="329"/>
-      <c r="S15" s="329"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R15" s="398"/>
+      <c r="S15" s="398"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -6296,7 +6346,7 @@
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6342,7 +6392,7 @@
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6387,10 +6437,13 @@
         <f t="shared" si="2"/>
         <v>1373932.9365556398</v>
       </c>
-      <c r="P18" s="85"/>
+      <c r="P18" s="142">
+        <f>SUM(L14:L18)</f>
+        <v>1370412.16408</v>
+      </c>
       <c r="S18" s="32"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
         <v>116</v>
       </c>
@@ -6443,7 +6496,7 @@
       </c>
       <c r="S19" s="32"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
         <v>117</v>
       </c>
@@ -6497,7 +6550,7 @@
       </c>
       <c r="S20" s="32"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>116</v>
       </c>
@@ -6550,7 +6603,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>118</v>
       </c>
@@ -6608,7 +6661,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>118</v>
       </c>
@@ -6662,7 +6715,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>118</v>
       </c>
@@ -6716,7 +6769,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>116</v>
       </c>
@@ -6771,7 +6824,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
         <v>117</v>
       </c>
@@ -6823,7 +6876,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="78" t="s">
         <v>116</v>
       </c>
@@ -6875,7 +6928,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="78" t="s">
         <v>118</v>
       </c>
@@ -6928,7 +6981,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="78" t="s">
         <v>118</v>
       </c>
@@ -6981,7 +7034,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="78" t="s">
         <v>118</v>
       </c>
@@ -7031,7 +7084,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="78" t="s">
         <v>116</v>
       </c>
@@ -7084,7 +7137,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>117</v>
       </c>
@@ -7138,7 +7191,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>116</v>
       </c>
@@ -7191,7 +7244,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A34" s="108" t="s">
         <v>118</v>
       </c>
@@ -7247,7 +7300,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>118</v>
       </c>
@@ -7301,7 +7354,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>118</v>
       </c>
@@ -7351,7 +7404,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>116</v>
       </c>
@@ -7409,7 +7462,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>117</v>
       </c>
@@ -7462,7 +7515,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78" t="s">
         <v>116</v>
       </c>
@@ -7615,7 +7668,7 @@
       <c r="DI39" s="53"/>
       <c r="DJ39" s="53"/>
     </row>
-    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78" t="s">
         <v>118</v>
       </c>
@@ -7767,7 +7820,7 @@
       <c r="DI40" s="53"/>
       <c r="DJ40" s="53"/>
     </row>
-    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="78" t="s">
         <v>118</v>
       </c>
@@ -7920,7 +7973,7 @@
       <c r="DI41" s="53"/>
       <c r="DJ41" s="53"/>
     </row>
-    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="78" t="s">
         <v>118</v>
       </c>
@@ -8070,7 +8123,7 @@
       <c r="DI42" s="53"/>
       <c r="DJ42" s="53"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
         <v>116</v>
       </c>
@@ -8123,7 +8176,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
         <v>117</v>
       </c>
@@ -8178,7 +8231,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>116</v>
       </c>
@@ -8237,7 +8290,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="132" t="s">
         <v>118</v>
       </c>
@@ -8290,7 +8343,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
         <v>118</v>
       </c>
@@ -8345,7 +8398,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
         <v>118</v>
       </c>
@@ -8398,7 +8451,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
         <v>116</v>
       </c>
@@ -8451,7 +8504,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
         <v>117</v>
       </c>
@@ -8505,7 +8558,7 @@
       </c>
       <c r="Q50" s="32"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="43" t="s">
         <v>116</v>
       </c>
@@ -8559,7 +8612,7 @@
       </c>
       <c r="Q51" s="32"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>118</v>
       </c>
@@ -8617,7 +8670,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>118</v>
       </c>
@@ -8670,7 +8723,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="78" t="s">
         <v>118</v>
       </c>
@@ -8723,7 +8776,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>116</v>
       </c>
@@ -8777,7 +8830,7 @@
       </c>
       <c r="R55" s="45"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="43" t="s">
         <v>117</v>
       </c>
@@ -8832,7 +8885,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>116</v>
       </c>
@@ -8885,7 +8938,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>118</v>
       </c>
@@ -8940,7 +8993,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="78" t="s">
         <v>118</v>
       </c>
@@ -8996,7 +9049,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="78" t="s">
         <v>118</v>
       </c>
@@ -9052,7 +9105,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="78" t="s">
         <v>116</v>
       </c>
@@ -9105,7 +9158,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
         <v>117</v>
       </c>
@@ -9158,7 +9211,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>116</v>
       </c>
@@ -9211,7 +9264,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>118</v>
       </c>
@@ -9265,7 +9318,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>118</v>
       </c>
@@ -9318,7 +9371,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>118</v>
       </c>
@@ -9371,7 +9424,7 @@
       </c>
       <c r="S66" s="142"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>116</v>
       </c>
@@ -9425,7 +9478,7 @@
       </c>
       <c r="S67" s="32"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="108" t="s">
         <v>117</v>
       </c>
@@ -9478,7 +9531,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>116</v>
       </c>
@@ -9530,7 +9583,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>118</v>
       </c>
@@ -9583,7 +9636,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>118</v>
       </c>
@@ -9637,7 +9690,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>118</v>
       </c>
@@ -9687,7 +9740,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>119</v>
       </c>
@@ -9741,7 +9794,7 @@
       </c>
       <c r="Q73" s="53"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
         <v>116</v>
       </c>
@@ -9794,7 +9847,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
         <v>118</v>
       </c>
@@ -9847,7 +9900,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>118</v>
       </c>
@@ -9902,7 +9955,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="78" t="s">
         <v>118</v>
       </c>
@@ -9955,7 +10008,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="78" t="s">
         <v>119</v>
       </c>
@@ -10007,7 +10060,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>116</v>
       </c>
@@ -10060,7 +10113,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
         <v>118</v>
       </c>
@@ -10110,7 +10163,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
         <v>118</v>
       </c>
@@ -10164,7 +10217,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>118</v>
       </c>
@@ -10172,7 +10225,7 @@
       <c r="C82" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="D82" s="397" t="s">
+      <c r="D82" s="292" t="s">
         <v>212</v>
       </c>
       <c r="E82" s="104"/>
@@ -10220,7 +10273,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="43" t="s">
         <v>119</v>
       </c>
@@ -10273,7 +10326,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>116</v>
       </c>
@@ -10326,7 +10379,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>118</v>
       </c>
@@ -10379,7 +10432,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>118</v>
       </c>
@@ -10432,7 +10485,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="78" t="s">
         <v>118</v>
       </c>
@@ -10485,7 +10538,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="78"/>
       <c r="B88" s="24"/>
       <c r="C88" s="24" t="s">
@@ -10537,7 +10590,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="78"/>
       <c r="B89" s="24"/>
       <c r="C89" s="24" t="s">
@@ -10589,7 +10642,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="78"/>
       <c r="B90" s="24"/>
       <c r="C90" s="24" t="s">
@@ -10641,7 +10694,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="78"/>
       <c r="B91" s="24"/>
       <c r="C91" s="24" t="s">
@@ -10693,7 +10746,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="78"/>
       <c r="B92" s="24"/>
       <c r="C92" s="136" t="s">
@@ -10748,7 +10801,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="78"/>
       <c r="B93" s="24"/>
       <c r="C93" s="24" t="s">
@@ -10800,7 +10853,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="78"/>
       <c r="B94" s="24"/>
       <c r="C94" s="24" t="s">
@@ -10852,7 +10905,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="78"/>
       <c r="B95" s="24"/>
       <c r="C95" s="24" t="s">
@@ -10904,7 +10957,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="78"/>
       <c r="B96" s="24"/>
       <c r="C96" s="24" t="s">
@@ -10956,7 +11009,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="78"/>
       <c r="B97" s="24"/>
       <c r="C97" s="256" t="s">
@@ -11005,7 +11058,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="78"/>
       <c r="B98" s="24"/>
       <c r="C98" s="24" t="s">
@@ -11057,7 +11110,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="78"/>
       <c r="B99" s="24"/>
       <c r="C99" s="24" t="s">
@@ -11109,7 +11162,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="78"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24" t="s">
@@ -11161,7 +11214,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="78"/>
       <c r="B101" s="24"/>
       <c r="C101" s="24" t="s">
@@ -11213,7 +11266,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="78"/>
       <c r="B102" s="24"/>
       <c r="C102" s="24" t="s">
@@ -11265,7 +11318,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="78"/>
       <c r="B103" s="24"/>
       <c r="C103" s="24" t="s">
@@ -11317,7 +11370,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="78"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24" t="s">
@@ -11369,7 +11422,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="78"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24" t="s">
@@ -11421,7 +11474,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="78"/>
       <c r="B106" s="24"/>
       <c r="C106" s="24" t="s">
@@ -11473,7 +11526,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="78"/>
       <c r="B107" s="24"/>
       <c r="C107" s="24" t="s">
@@ -11524,7 +11577,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="78"/>
       <c r="B108" s="24"/>
       <c r="C108" s="24" t="s">
@@ -11576,7 +11629,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="78"/>
       <c r="B109" s="24"/>
       <c r="C109" s="24" t="s">
@@ -11628,7 +11681,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="78"/>
       <c r="B110" s="24"/>
       <c r="C110" s="256" t="s">
@@ -11679,7 +11732,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="78"/>
       <c r="B111" s="24"/>
       <c r="C111" s="24" t="s">
@@ -11731,7 +11784,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="78"/>
       <c r="B112" s="24"/>
       <c r="C112" s="24" t="s">
@@ -11783,7 +11836,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="78"/>
       <c r="B113" s="24"/>
       <c r="C113" s="24" t="s">
@@ -11835,7 +11888,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="78"/>
       <c r="B114" s="24"/>
       <c r="C114" s="24" t="s">
@@ -11887,7 +11940,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="78"/>
       <c r="B115" s="24"/>
       <c r="C115" s="24" t="s">
@@ -11939,7 +11992,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="78"/>
       <c r="B116" s="24"/>
       <c r="C116" s="24" t="s">
@@ -11993,7 +12046,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="78"/>
       <c r="B117" s="24"/>
       <c r="C117" s="24" t="s">
@@ -12044,7 +12097,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="78"/>
       <c r="B118" s="24"/>
       <c r="C118" s="24" t="s">
@@ -12101,7 +12154,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="97"/>
       <c r="B119" s="24"/>
       <c r="C119" s="24" t="s">
@@ -12153,7 +12206,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="97"/>
       <c r="B120" s="24"/>
       <c r="C120" s="24" t="s">
@@ -12205,7 +12258,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="97"/>
       <c r="B121" s="24"/>
       <c r="C121" s="24" t="s">
@@ -12259,7 +12312,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="97"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
@@ -12311,7 +12364,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="97"/>
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
@@ -12363,7 +12416,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="97"/>
       <c r="B124" s="24"/>
       <c r="C124" s="24" t="s">
@@ -12418,7 +12471,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="135"/>
       <c r="B125" s="130"/>
       <c r="C125" s="24" t="s">
@@ -12471,7 +12524,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="135"/>
       <c r="B126" s="130"/>
       <c r="C126" s="24" t="s">
@@ -12522,7 +12575,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="97"/>
       <c r="B127" s="24"/>
       <c r="C127" s="24" t="s">
@@ -12573,7 +12626,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="97"/>
       <c r="B128" s="24"/>
       <c r="C128" s="24" t="s">
@@ -12625,7 +12678,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="97"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24" t="s">
@@ -12677,7 +12730,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="97" t="s">
         <v>24</v>
       </c>
@@ -12731,7 +12784,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="97" t="s">
         <v>24</v>
       </c>
@@ -12785,7 +12838,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="40" t="s">
         <v>24</v>
       </c>
@@ -12804,7 +12857,7 @@
       <c r="N132" s="2"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -12849,43 +12902,43 @@
       </c>
       <c r="Q133" s="45"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L134" s="47">
         <f>L133-M1</f>
         <v>-4093431.9739200063</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="333"/>
-      <c r="D135" s="333"/>
-      <c r="E135" s="333"/>
-      <c r="F135" s="333"/>
-      <c r="G135" s="333"/>
-      <c r="H135" s="333"/>
-      <c r="I135" s="333"/>
-      <c r="J135" s="333"/>
-      <c r="K135" s="333"/>
-      <c r="L135" s="333"/>
-      <c r="M135" s="333"/>
-      <c r="N135" s="333"/>
-      <c r="O135" s="333"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="333"/>
-      <c r="D136" s="333"/>
-      <c r="E136" s="333"/>
-      <c r="F136" s="333"/>
-      <c r="G136" s="333"/>
-      <c r="H136" s="333"/>
-      <c r="I136" s="333"/>
-      <c r="J136" s="333"/>
-      <c r="K136" s="333"/>
-      <c r="L136" s="333"/>
-      <c r="M136" s="333"/>
-      <c r="N136" s="333"/>
-      <c r="O136" s="333"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="346"/>
+      <c r="D135" s="346"/>
+      <c r="E135" s="346"/>
+      <c r="F135" s="346"/>
+      <c r="G135" s="346"/>
+      <c r="H135" s="346"/>
+      <c r="I135" s="346"/>
+      <c r="J135" s="346"/>
+      <c r="K135" s="346"/>
+      <c r="L135" s="346"/>
+      <c r="M135" s="346"/>
+      <c r="N135" s="346"/>
+      <c r="O135" s="346"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="346"/>
+      <c r="D136" s="346"/>
+      <c r="E136" s="346"/>
+      <c r="F136" s="346"/>
+      <c r="G136" s="346"/>
+      <c r="H136" s="346"/>
+      <c r="I136" s="346"/>
+      <c r="J136" s="346"/>
+      <c r="K136" s="346"/>
+      <c r="L136" s="346"/>
+      <c r="M136" s="346"/>
+      <c r="N136" s="346"/>
+      <c r="O136" s="346"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
       <c r="D137" s="57"/>
       <c r="E137" s="57"/>
@@ -12900,7 +12953,7 @@
       <c r="N137" s="57"/>
       <c r="O137" s="57"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C138" s="299" t="s">
         <v>243</v>
       </c>
@@ -12917,7 +12970,7 @@
       <c r="N138" s="299"/>
       <c r="O138" s="299"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C139" s="299"/>
       <c r="D139" s="299"/>
       <c r="E139" s="299"/>
@@ -12932,7 +12985,7 @@
       <c r="N139" s="299"/>
       <c r="O139" s="299"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C140" s="299"/>
       <c r="D140" s="299"/>
       <c r="E140" s="299"/>
@@ -12947,7 +13000,7 @@
       <c r="N140" s="299"/>
       <c r="O140" s="299"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C141" s="299"/>
       <c r="D141" s="299"/>
       <c r="E141" s="299"/>
@@ -12962,7 +13015,7 @@
       <c r="N141" s="299"/>
       <c r="O141" s="299"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C142" s="299"/>
       <c r="D142" s="299"/>
       <c r="E142" s="299"/>
@@ -12977,7 +13030,7 @@
       <c r="N142" s="299"/>
       <c r="O142" s="299"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C143" s="299"/>
       <c r="D143" s="299"/>
       <c r="E143" s="299"/>
@@ -12992,7 +13045,7 @@
       <c r="N143" s="299"/>
       <c r="O143" s="299"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C144" s="299"/>
       <c r="D144" s="299"/>
       <c r="E144" s="299"/>
@@ -13007,7 +13060,7 @@
       <c r="N144" s="299"/>
       <c r="O144" s="299"/>
     </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C145" s="299"/>
       <c r="D145" s="299"/>
       <c r="E145" s="299"/>
@@ -13022,7 +13075,7 @@
       <c r="N145" s="299"/>
       <c r="O145" s="299"/>
     </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="E146" s="57"/>
@@ -13037,7 +13090,7 @@
       <c r="N146" s="57"/>
       <c r="O146" s="57"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="57"/>
       <c r="D147" s="57"/>
       <c r="E147" s="57"/>
@@ -13052,127 +13105,119 @@
       <c r="N147" s="57"/>
       <c r="O147" s="57"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C148" s="332" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C148" s="345" t="s">
         <v>242</v>
       </c>
-      <c r="D148" s="332"/>
-      <c r="E148" s="332"/>
-      <c r="F148" s="332"/>
-      <c r="G148" s="332"/>
-      <c r="H148" s="332"/>
-      <c r="I148" s="332"/>
-      <c r="J148" s="332"/>
-      <c r="K148" s="332"/>
-      <c r="L148" s="332"/>
-      <c r="M148" s="332"/>
-      <c r="N148" s="332"/>
-      <c r="O148" s="332"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="332"/>
-      <c r="D149" s="332"/>
-      <c r="E149" s="332"/>
-      <c r="F149" s="332"/>
-      <c r="G149" s="332"/>
-      <c r="H149" s="332"/>
-      <c r="I149" s="332"/>
-      <c r="J149" s="332"/>
-      <c r="K149" s="332"/>
-      <c r="L149" s="332"/>
-      <c r="M149" s="332"/>
-      <c r="N149" s="332"/>
-      <c r="O149" s="332"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="332"/>
-      <c r="D150" s="332"/>
-      <c r="E150" s="332"/>
-      <c r="F150" s="332"/>
-      <c r="G150" s="332"/>
-      <c r="H150" s="332"/>
-      <c r="I150" s="332"/>
-      <c r="J150" s="332"/>
-      <c r="K150" s="332"/>
-      <c r="L150" s="332"/>
-      <c r="M150" s="332"/>
-      <c r="N150" s="332"/>
-      <c r="O150" s="332"/>
+      <c r="D148" s="345"/>
+      <c r="E148" s="345"/>
+      <c r="F148" s="345"/>
+      <c r="G148" s="345"/>
+      <c r="H148" s="345"/>
+      <c r="I148" s="345"/>
+      <c r="J148" s="345"/>
+      <c r="K148" s="345"/>
+      <c r="L148" s="345"/>
+      <c r="M148" s="345"/>
+      <c r="N148" s="345"/>
+      <c r="O148" s="345"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C149" s="345"/>
+      <c r="D149" s="345"/>
+      <c r="E149" s="345"/>
+      <c r="F149" s="345"/>
+      <c r="G149" s="345"/>
+      <c r="H149" s="345"/>
+      <c r="I149" s="345"/>
+      <c r="J149" s="345"/>
+      <c r="K149" s="345"/>
+      <c r="L149" s="345"/>
+      <c r="M149" s="345"/>
+      <c r="N149" s="345"/>
+      <c r="O149" s="345"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C150" s="345"/>
+      <c r="D150" s="345"/>
+      <c r="E150" s="345"/>
+      <c r="F150" s="345"/>
+      <c r="G150" s="345"/>
+      <c r="H150" s="345"/>
+      <c r="I150" s="345"/>
+      <c r="J150" s="345"/>
+      <c r="K150" s="345"/>
+      <c r="L150" s="345"/>
+      <c r="M150" s="345"/>
+      <c r="N150" s="345"/>
+      <c r="O150" s="345"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>4093431.9739200063</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="332"/>
-      <c r="D151" s="332"/>
-      <c r="E151" s="332"/>
-      <c r="F151" s="332"/>
-      <c r="G151" s="332"/>
-      <c r="H151" s="332"/>
-      <c r="I151" s="332"/>
-      <c r="J151" s="332"/>
-      <c r="K151" s="332"/>
-      <c r="L151" s="332"/>
-      <c r="M151" s="332"/>
-      <c r="N151" s="332"/>
-      <c r="O151" s="332"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="332"/>
-      <c r="D152" s="332"/>
-      <c r="E152" s="332"/>
-      <c r="F152" s="332"/>
-      <c r="G152" s="332"/>
-      <c r="H152" s="332"/>
-      <c r="I152" s="332"/>
-      <c r="J152" s="332"/>
-      <c r="K152" s="332"/>
-      <c r="L152" s="332"/>
-      <c r="M152" s="332"/>
-      <c r="N152" s="332"/>
-      <c r="O152" s="332"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="332"/>
-      <c r="D153" s="332"/>
-      <c r="E153" s="332"/>
-      <c r="F153" s="332"/>
-      <c r="G153" s="332"/>
-      <c r="H153" s="332"/>
-      <c r="I153" s="332"/>
-      <c r="J153" s="332"/>
-      <c r="K153" s="332"/>
-      <c r="L153" s="332"/>
-      <c r="M153" s="332"/>
-      <c r="N153" s="332"/>
-      <c r="O153" s="332"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="332"/>
-      <c r="D154" s="332"/>
-      <c r="E154" s="332"/>
-      <c r="F154" s="332"/>
-      <c r="G154" s="332"/>
-      <c r="H154" s="332"/>
-      <c r="I154" s="332"/>
-      <c r="J154" s="332"/>
-      <c r="K154" s="332"/>
-      <c r="L154" s="332"/>
-      <c r="M154" s="332"/>
-      <c r="N154" s="332"/>
-      <c r="O154" s="332"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="345"/>
+      <c r="D151" s="345"/>
+      <c r="E151" s="345"/>
+      <c r="F151" s="345"/>
+      <c r="G151" s="345"/>
+      <c r="H151" s="345"/>
+      <c r="I151" s="345"/>
+      <c r="J151" s="345"/>
+      <c r="K151" s="345"/>
+      <c r="L151" s="345"/>
+      <c r="M151" s="345"/>
+      <c r="N151" s="345"/>
+      <c r="O151" s="345"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="345"/>
+      <c r="D152" s="345"/>
+      <c r="E152" s="345"/>
+      <c r="F152" s="345"/>
+      <c r="G152" s="345"/>
+      <c r="H152" s="345"/>
+      <c r="I152" s="345"/>
+      <c r="J152" s="345"/>
+      <c r="K152" s="345"/>
+      <c r="L152" s="345"/>
+      <c r="M152" s="345"/>
+      <c r="N152" s="345"/>
+      <c r="O152" s="345"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="345"/>
+      <c r="D153" s="345"/>
+      <c r="E153" s="345"/>
+      <c r="F153" s="345"/>
+      <c r="G153" s="345"/>
+      <c r="H153" s="345"/>
+      <c r="I153" s="345"/>
+      <c r="J153" s="345"/>
+      <c r="K153" s="345"/>
+      <c r="L153" s="345"/>
+      <c r="M153" s="345"/>
+      <c r="N153" s="345"/>
+      <c r="O153" s="345"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="345"/>
+      <c r="D154" s="345"/>
+      <c r="E154" s="345"/>
+      <c r="F154" s="345"/>
+      <c r="G154" s="345"/>
+      <c r="H154" s="345"/>
+      <c r="I154" s="345"/>
+      <c r="J154" s="345"/>
+      <c r="K154" s="345"/>
+      <c r="L154" s="345"/>
+      <c r="M154" s="345"/>
+      <c r="N154" s="345"/>
+      <c r="O154" s="345"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="R14:S15"/>
+  <mergeCells count="22">
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
     <mergeCell ref="C135:O136"/>
@@ -13188,6 +13233,13 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13198,84 +13250,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
-    <col min="15" max="15" width="19.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="375" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="385" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="375"/>
-      <c r="C1" s="375"/>
-      <c r="D1" s="375"/>
-      <c r="E1" s="375"/>
-      <c r="F1" s="375"/>
-      <c r="G1" s="375"/>
-      <c r="H1" s="375"/>
-      <c r="I1" s="375"/>
-      <c r="J1" s="375"/>
-      <c r="K1" s="375"/>
-      <c r="L1" s="375"/>
-      <c r="M1" s="375"/>
-      <c r="N1" s="375"/>
-      <c r="O1" s="376"/>
+      <c r="B1" s="385"/>
+      <c r="C1" s="385"/>
+      <c r="D1" s="385"/>
+      <c r="E1" s="385"/>
+      <c r="F1" s="385"/>
+      <c r="G1" s="385"/>
+      <c r="H1" s="385"/>
+      <c r="I1" s="385"/>
+      <c r="J1" s="385"/>
+      <c r="K1" s="385"/>
+      <c r="L1" s="385"/>
+      <c r="M1" s="385"/>
+      <c r="N1" s="385"/>
+      <c r="O1" s="386"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="377"/>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
-      <c r="L2" s="377"/>
-      <c r="M2" s="377"/>
-      <c r="N2" s="377"/>
-      <c r="O2" s="378"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="387"/>
+      <c r="B2" s="387"/>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+      <c r="F2" s="387"/>
+      <c r="G2" s="387"/>
+      <c r="H2" s="387"/>
+      <c r="I2" s="387"/>
+      <c r="J2" s="387"/>
+      <c r="K2" s="387"/>
+      <c r="L2" s="387"/>
+      <c r="M2" s="387"/>
+      <c r="N2" s="387"/>
+      <c r="O2" s="388"/>
       <c r="R2" s="32"/>
     </row>
-    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="372" t="s">
+    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="382" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="373"/>
-      <c r="C3" s="373"/>
-      <c r="D3" s="373"/>
-      <c r="E3" s="373"/>
-      <c r="F3" s="373"/>
-      <c r="G3" s="373"/>
-      <c r="H3" s="373"/>
-      <c r="I3" s="373"/>
-      <c r="J3" s="373"/>
-      <c r="K3" s="373"/>
-      <c r="L3" s="373"/>
-      <c r="M3" s="373"/>
-      <c r="N3" s="373"/>
-      <c r="O3" s="374"/>
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="383"/>
+      <c r="E3" s="383"/>
+      <c r="F3" s="383"/>
+      <c r="G3" s="383"/>
+      <c r="H3" s="383"/>
+      <c r="I3" s="383"/>
+      <c r="J3" s="383"/>
+      <c r="K3" s="383"/>
+      <c r="L3" s="383"/>
+      <c r="M3" s="383"/>
+      <c r="N3" s="383"/>
+      <c r="O3" s="384"/>
       <c r="P3" s="185"/>
       <c r="Q3" s="185"/>
       <c r="R3" s="185"/>
@@ -13289,89 +13341,89 @@
       <c r="Z3" s="185"/>
       <c r="AA3" s="185"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="330" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="338" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="330" t="s">
+      <c r="B4" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="330" t="s">
+      <c r="C4" s="338" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="330" t="s">
+      <c r="D4" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="338" t="s">
+      <c r="E4" s="335" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="338" t="s">
+      <c r="F4" s="335" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="338" t="s">
+      <c r="G4" s="335" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="338" t="s">
+      <c r="H4" s="335" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="338" t="s">
+      <c r="I4" s="335" t="s">
         <v>339</v>
       </c>
-      <c r="J4" s="379" t="s">
+      <c r="J4" s="374" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="369" t="s">
+      <c r="L4" s="379" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="338" t="s">
+      <c r="M4" s="335" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="338" t="s">
+      <c r="N4" s="335" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="338" t="s">
+      <c r="O4" s="335" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="331"/>
-      <c r="B5" s="331"/>
-      <c r="C5" s="331"/>
-      <c r="D5" s="331"/>
-      <c r="E5" s="339"/>
-      <c r="F5" s="339"/>
-      <c r="G5" s="339"/>
-      <c r="H5" s="339"/>
-      <c r="I5" s="339"/>
-      <c r="J5" s="380"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="339"/>
+      <c r="B5" s="339"/>
+      <c r="C5" s="339"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="336"/>
+      <c r="F5" s="336"/>
+      <c r="G5" s="336"/>
+      <c r="H5" s="336"/>
+      <c r="I5" s="336"/>
+      <c r="J5" s="375"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="370"/>
-      <c r="M5" s="339"/>
-      <c r="N5" s="339"/>
-      <c r="O5" s="339"/>
+      <c r="L5" s="380"/>
+      <c r="M5" s="336"/>
+      <c r="N5" s="336"/>
+      <c r="O5" s="336"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="382"/>
-      <c r="B6" s="382"/>
-      <c r="C6" s="382"/>
-      <c r="D6" s="382"/>
-      <c r="E6" s="368"/>
-      <c r="F6" s="368"/>
-      <c r="G6" s="368"/>
-      <c r="H6" s="368"/>
-      <c r="I6" s="368"/>
-      <c r="J6" s="381"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="378"/>
+      <c r="B6" s="378"/>
+      <c r="C6" s="378"/>
+      <c r="D6" s="378"/>
+      <c r="E6" s="377"/>
+      <c r="F6" s="377"/>
+      <c r="G6" s="377"/>
+      <c r="H6" s="377"/>
+      <c r="I6" s="377"/>
+      <c r="J6" s="376"/>
       <c r="K6" s="154"/>
-      <c r="L6" s="371"/>
-      <c r="M6" s="368"/>
-      <c r="N6" s="368"/>
-      <c r="O6" s="368"/>
+      <c r="L6" s="381"/>
+      <c r="M6" s="377"/>
+      <c r="N6" s="377"/>
+      <c r="O6" s="377"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="155" t="s">
         <v>109</v>
       </c>
@@ -13423,10 +13475,10 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R7" s="344"/>
+      <c r="S7" s="344"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="155" t="s">
         <v>308</v>
       </c>
@@ -13480,10 +13532,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="329"/>
-      <c r="S8" s="329"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R8" s="344"/>
+      <c r="S8" s="344"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="155" t="s">
         <v>110</v>
       </c>
@@ -13539,7 +13591,7 @@
       </c>
       <c r="S9" s="32"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="155" t="s">
         <v>111</v>
       </c>
@@ -13594,7 +13646,7 @@
       </c>
       <c r="S10" s="32"/>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="159" t="s">
         <v>112</v>
       </c>
@@ -13649,7 +13701,7 @@
       </c>
       <c r="S11" s="32"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="162" t="s">
         <v>40</v>
       </c>
@@ -13705,7 +13757,7 @@
       </c>
       <c r="S12" s="32"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="155" t="s">
         <v>41</v>
       </c>
@@ -13760,7 +13812,7 @@
       </c>
       <c r="S13" s="32"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="155" t="s">
         <v>42</v>
       </c>
@@ -13816,7 +13868,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="155" t="s">
         <v>43</v>
       </c>
@@ -13872,7 +13924,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="155" t="s">
         <v>44</v>
       </c>
@@ -13926,7 +13978,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A17" s="155" t="s">
         <v>45</v>
       </c>
@@ -13982,7 +14034,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A18" s="155" t="s">
         <v>46</v>
       </c>
@@ -14038,7 +14090,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A19" s="155" t="s">
         <v>47</v>
       </c>
@@ -14092,7 +14144,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A20" s="155" t="s">
         <v>48</v>
       </c>
@@ -14146,7 +14198,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A21" s="155" t="s">
         <v>49</v>
       </c>
@@ -14200,7 +14252,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A22" s="155" t="s">
         <v>50</v>
       </c>
@@ -14254,7 +14306,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A23" s="155" t="s">
         <v>51</v>
       </c>
@@ -14308,7 +14360,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A24" s="155" t="s">
         <v>52</v>
       </c>
@@ -14362,7 +14414,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A25" s="155" t="s">
         <v>53</v>
       </c>
@@ -14416,7 +14468,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A26" s="155" t="s">
         <v>54</v>
       </c>
@@ -14472,7 +14524,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A27" s="155" t="s">
         <v>55</v>
       </c>
@@ -14530,7 +14582,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A28" s="155" t="s">
         <v>56</v>
       </c>
@@ -14584,7 +14636,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A29" s="155" t="s">
         <v>57</v>
       </c>
@@ -14636,7 +14688,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A30" s="155" t="s">
         <v>58</v>
       </c>
@@ -14693,7 +14745,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A31" s="155" t="s">
         <v>59</v>
       </c>
@@ -14749,7 +14801,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="155" t="s">
         <v>60</v>
       </c>
@@ -14904,7 +14956,7 @@
       <c r="DI32" s="53"/>
       <c r="DJ32" s="53"/>
     </row>
-    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="155" t="s">
         <v>61</v>
       </c>
@@ -15058,7 +15110,7 @@
       <c r="DI33" s="53"/>
       <c r="DJ33" s="53"/>
     </row>
-    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="155" t="s">
         <v>62</v>
       </c>
@@ -15214,7 +15266,7 @@
       <c r="DI34" s="53"/>
       <c r="DJ34" s="53"/>
     </row>
-    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="155" t="s">
         <v>63</v>
       </c>
@@ -15364,7 +15416,7 @@
       <c r="DI35" s="53"/>
       <c r="DJ35" s="53"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="155" t="s">
         <v>64</v>
       </c>
@@ -15420,7 +15472,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="155" t="s">
         <v>65</v>
       </c>
@@ -15474,7 +15526,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="155" t="s">
         <v>66</v>
       </c>
@@ -15536,7 +15588,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A39" s="155" t="s">
         <v>67</v>
       </c>
@@ -15592,7 +15644,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A40" s="155" t="s">
         <v>68</v>
       </c>
@@ -15646,7 +15698,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A41" s="155" t="s">
         <v>69</v>
       </c>
@@ -15700,7 +15752,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A42" s="155" t="s">
         <v>70</v>
       </c>
@@ -15756,7 +15808,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="155" t="s">
         <v>71</v>
       </c>
@@ -15813,7 +15865,7 @@
       </c>
       <c r="Q43" s="32"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="155" t="s">
         <v>72</v>
       </c>
@@ -15870,7 +15922,7 @@
       </c>
       <c r="Q44" s="32"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="155" t="s">
         <v>73</v>
       </c>
@@ -15927,7 +15979,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="155" t="s">
         <v>74</v>
       </c>
@@ -15981,7 +16033,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="155" t="s">
         <v>75</v>
       </c>
@@ -16035,7 +16087,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="155" t="s">
         <v>76</v>
       </c>
@@ -16092,7 +16144,7 @@
       </c>
       <c r="R48" s="45"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="155" t="s">
         <v>77</v>
       </c>
@@ -16146,7 +16198,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="155" t="s">
         <v>78</v>
       </c>
@@ -16203,7 +16255,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="155" t="s">
         <v>79</v>
       </c>
@@ -16257,7 +16309,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="155" t="s">
         <v>80</v>
       </c>
@@ -16314,7 +16366,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="155" t="s">
         <v>81</v>
       </c>
@@ -16373,7 +16425,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="155" t="s">
         <v>82</v>
       </c>
@@ -16429,7 +16481,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="155" t="s">
         <v>83</v>
       </c>
@@ -16483,7 +16535,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="155" t="s">
         <v>84</v>
       </c>
@@ -16539,7 +16591,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="278" t="s">
         <v>85</v>
       </c>
@@ -16595,7 +16647,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="155" t="s">
         <v>86</v>
       </c>
@@ -16651,7 +16703,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="155" t="s">
         <v>87</v>
       </c>
@@ -16708,7 +16760,7 @@
       </c>
       <c r="S59" s="142"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="155" t="s">
         <v>88</v>
       </c>
@@ -16765,7 +16817,7 @@
       </c>
       <c r="S60" s="32"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="155" t="s">
         <v>89</v>
       </c>
@@ -16820,7 +16872,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="155" t="s">
         <v>90</v>
       </c>
@@ -16876,7 +16928,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="155" t="s">
         <v>91</v>
       </c>
@@ -16930,7 +16982,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="155" t="s">
         <v>92</v>
       </c>
@@ -16987,7 +17039,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="155" t="s">
         <v>93</v>
       </c>
@@ -17044,7 +17096,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="155" t="s">
         <v>94</v>
       </c>
@@ -17101,7 +17153,7 @@
       </c>
       <c r="Q66" s="53"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="155" t="s">
         <v>95</v>
       </c>
@@ -17157,7 +17209,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="155" t="s">
         <v>96</v>
       </c>
@@ -17203,7 +17255,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="155" t="s">
         <v>97</v>
       </c>
@@ -17258,7 +17310,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="155" t="s">
         <v>98</v>
       </c>
@@ -17314,7 +17366,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="155" t="s">
         <v>99</v>
       </c>
@@ -17370,7 +17422,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="155" t="s">
         <v>100</v>
       </c>
@@ -17426,7 +17478,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="155" t="s">
         <v>101</v>
       </c>
@@ -17481,7 +17533,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="155" t="s">
         <v>102</v>
       </c>
@@ -17537,7 +17589,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="155" t="s">
         <v>103</v>
       </c>
@@ -17591,7 +17643,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="155" t="s">
         <v>104</v>
       </c>
@@ -17647,7 +17699,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="155" t="s">
         <v>105</v>
       </c>
@@ -17704,7 +17756,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="155" t="s">
         <v>106</v>
       </c>
@@ -17760,7 +17812,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="155" t="s">
         <v>107</v>
       </c>
@@ -17816,7 +17868,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="155" t="s">
         <v>108</v>
       </c>
@@ -17872,7 +17924,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="24"/>
       <c r="B81" s="24"/>
       <c r="C81" s="78"/>
@@ -17889,7 +17941,7 @@
       <c r="N81" s="113"/>
       <c r="O81" s="114"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -17930,6 +17982,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17945,8 +17999,6 @@
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17956,14 +18008,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="C1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K1" s="53"/>
       <c r="L1" s="53"/>
       <c r="M1" s="53"/>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C2" s="281" t="s">
         <v>343</v>
       </c>
@@ -17980,7 +18032,7 @@
       <c r="L2" s="53"/>
       <c r="M2" s="53"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C3" s="283" t="s">
         <v>344</v>
       </c>
@@ -17995,11 +18047,11 @@
       <c r="H3" s="190"/>
       <c r="I3" s="191"/>
       <c r="J3" s="192"/>
-      <c r="K3" s="286"/>
-      <c r="L3" s="286"/>
+      <c r="K3" s="400"/>
+      <c r="L3" s="400"/>
       <c r="M3" s="286"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" s="283" t="s">
         <v>346</v>
       </c>
@@ -18018,11 +18070,11 @@
       </c>
       <c r="I4" s="191"/>
       <c r="J4" s="192"/>
-      <c r="K4" s="286"/>
-      <c r="L4" s="286"/>
+      <c r="K4" s="400"/>
+      <c r="L4" s="400"/>
       <c r="M4" s="286"/>
     </row>
-    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="186" t="s">
         <v>350</v>
       </c>
@@ -18033,81 +18085,81 @@
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
       <c r="J5" s="193"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="286"/>
+      <c r="K5" s="400"/>
+      <c r="L5" s="400"/>
       <c r="M5" s="286"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="383" t="s">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="389" t="s">
         <v>414</v>
       </c>
-      <c r="D6" s="384"/>
-      <c r="E6" s="384"/>
-      <c r="F6" s="384"/>
-      <c r="G6" s="384"/>
-      <c r="H6" s="384"/>
-      <c r="I6" s="384"/>
-      <c r="J6" s="385"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
+      <c r="D6" s="390"/>
+      <c r="E6" s="390"/>
+      <c r="F6" s="390"/>
+      <c r="G6" s="390"/>
+      <c r="H6" s="390"/>
+      <c r="I6" s="390"/>
+      <c r="J6" s="391"/>
+      <c r="K6" s="401"/>
+      <c r="L6" s="401"/>
       <c r="M6" s="53"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="386"/>
-      <c r="D7" s="387"/>
-      <c r="E7" s="387"/>
-      <c r="F7" s="387"/>
-      <c r="G7" s="387"/>
-      <c r="H7" s="387"/>
-      <c r="I7" s="387"/>
-      <c r="J7" s="388"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="392"/>
+      <c r="D7" s="393"/>
+      <c r="E7" s="393"/>
+      <c r="F7" s="393"/>
+      <c r="G7" s="393"/>
+      <c r="H7" s="393"/>
+      <c r="I7" s="393"/>
+      <c r="J7" s="394"/>
+      <c r="K7" s="401"/>
+      <c r="L7" s="401"/>
       <c r="M7" s="53"/>
     </row>
-    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="389"/>
-      <c r="D8" s="390"/>
-      <c r="E8" s="390"/>
-      <c r="F8" s="390"/>
-      <c r="G8" s="390"/>
-      <c r="H8" s="390"/>
-      <c r="I8" s="390"/>
-      <c r="J8" s="391"/>
+    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="395"/>
+      <c r="D8" s="396"/>
+      <c r="E8" s="396"/>
+      <c r="F8" s="396"/>
+      <c r="G8" s="396"/>
+      <c r="H8" s="396"/>
+      <c r="I8" s="396"/>
+      <c r="J8" s="397"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="K9" s="53"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
     </row>
-    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K10" s="53"/>
       <c r="L10" s="53"/>
       <c r="M10" s="53"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C11" s="392" t="s">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C11" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="393">
+      <c r="D11" s="288">
         <v>1</v>
       </c>
-      <c r="E11" s="393"/>
+      <c r="E11" s="288"/>
       <c r="F11" s="188"/>
       <c r="G11" s="188"/>
       <c r="H11" s="188"/>
       <c r="I11" s="188"/>
       <c r="J11" s="189"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C12" s="394" t="s">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="289" t="s">
         <v>344</v>
       </c>
-      <c r="D12" s="395"/>
-      <c r="E12" s="396">
+      <c r="D12" s="290"/>
+      <c r="E12" s="291">
         <v>0</v>
       </c>
       <c r="F12" s="53"/>
@@ -18119,15 +18171,18 @@
       </c>
       <c r="I12" s="191"/>
       <c r="J12" s="192"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C13" s="394" t="s">
+      <c r="K12" s="401"/>
+      <c r="L12" s="401"/>
+      <c r="M12" s="401"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="289" t="s">
         <v>346</v>
       </c>
-      <c r="D13" s="395" t="s">
+      <c r="D13" s="290" t="s">
         <v>347</v>
       </c>
-      <c r="E13" s="395" t="s">
+      <c r="E13" s="290" t="s">
         <v>348</v>
       </c>
       <c r="F13" s="53"/>
@@ -18139,8 +18194,11 @@
       </c>
       <c r="I13" s="191"/>
       <c r="J13" s="192"/>
-    </row>
-    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K13" s="401"/>
+      <c r="L13" s="401"/>
+      <c r="M13" s="401"/>
+    </row>
+    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="186" t="s">
         <v>350</v>
       </c>
@@ -18151,38 +18209,47 @@
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="J14" s="193"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="383" t="s">
+      <c r="K14" s="401"/>
+      <c r="L14" s="401"/>
+      <c r="M14" s="401"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="389" t="s">
         <v>417</v>
       </c>
-      <c r="D15" s="384"/>
-      <c r="E15" s="384"/>
-      <c r="F15" s="384"/>
-      <c r="G15" s="384"/>
-      <c r="H15" s="384"/>
-      <c r="I15" s="384"/>
-      <c r="J15" s="385"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="386"/>
-      <c r="D16" s="387"/>
-      <c r="E16" s="387"/>
-      <c r="F16" s="387"/>
-      <c r="G16" s="387"/>
-      <c r="H16" s="387"/>
-      <c r="I16" s="387"/>
-      <c r="J16" s="388"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="389"/>
-      <c r="D17" s="390"/>
-      <c r="E17" s="390"/>
-      <c r="F17" s="390"/>
-      <c r="G17" s="390"/>
-      <c r="H17" s="390"/>
-      <c r="I17" s="390"/>
-      <c r="J17" s="391"/>
+      <c r="D15" s="390"/>
+      <c r="E15" s="390"/>
+      <c r="F15" s="390"/>
+      <c r="G15" s="390"/>
+      <c r="H15" s="390"/>
+      <c r="I15" s="390"/>
+      <c r="J15" s="391"/>
+      <c r="K15" s="401"/>
+      <c r="L15" s="401"/>
+      <c r="M15" s="401"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="392"/>
+      <c r="D16" s="393"/>
+      <c r="E16" s="393"/>
+      <c r="F16" s="393"/>
+      <c r="G16" s="393"/>
+      <c r="H16" s="393"/>
+      <c r="I16" s="393"/>
+      <c r="J16" s="394"/>
+      <c r="K16" s="401"/>
+      <c r="L16" s="401"/>
+      <c r="M16" s="401"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="395"/>
+      <c r="D17" s="396"/>
+      <c r="E17" s="396"/>
+      <c r="F17" s="396"/>
+      <c r="G17" s="396"/>
+      <c r="H17" s="396"/>
+      <c r="I17" s="396"/>
+      <c r="J17" s="397"/>
     </row>
   </sheetData>
   <mergeCells count="2">
